--- a/data/total_latest.xlsx
+++ b/data/total_latest.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I869"/>
+  <dimension ref="A1:I876"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -25064,10 +25064,10 @@
         <v>46142</v>
       </c>
       <c r="B850" t="n">
-        <v>21014</v>
+        <v>21013</v>
       </c>
       <c r="C850" t="n">
-        <v>8574</v>
+        <v>8573</v>
       </c>
       <c r="D850" t="n">
         <v>9804</v>
@@ -25082,7 +25082,7 @@
         <v>1486</v>
       </c>
       <c r="H850" t="n">
-        <v>18378</v>
+        <v>18377</v>
       </c>
       <c r="I850" t="n">
         <v>22</v>
@@ -25528,7 +25528,7 @@
         <v>46158</v>
       </c>
       <c r="B866" t="n">
-        <v>15617</v>
+        <v>15616</v>
       </c>
       <c r="C866" t="n">
         <v>7543</v>
@@ -25543,13 +25543,13 @@
         <v>0</v>
       </c>
       <c r="G866" t="n">
-        <v>772</v>
+        <v>771</v>
       </c>
       <c r="H866" t="n">
         <v>14497</v>
       </c>
       <c r="I866" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="867">
@@ -25586,25 +25586,25 @@
         <v>46160</v>
       </c>
       <c r="B868" t="n">
-        <v>23810</v>
+        <v>23728</v>
       </c>
       <c r="C868" t="n">
         <v>8213</v>
       </c>
       <c r="D868" t="n">
-        <v>7964</v>
+        <v>7963</v>
       </c>
       <c r="E868" t="n">
-        <v>1773</v>
+        <v>1703</v>
       </c>
       <c r="F868" t="n">
         <v>1114</v>
       </c>
       <c r="G868" t="n">
-        <v>4746</v>
+        <v>4735</v>
       </c>
       <c r="H868" t="n">
-        <v>16177</v>
+        <v>16176</v>
       </c>
       <c r="I868" t="n">
         <v>23</v>
@@ -25615,28 +25615,231 @@
         <v>46161</v>
       </c>
       <c r="B869" t="n">
-        <v>23189</v>
+        <v>23091</v>
       </c>
       <c r="C869" t="n">
         <v>8054</v>
       </c>
       <c r="D869" t="n">
-        <v>9311</v>
+        <v>9309</v>
       </c>
       <c r="E869" t="n">
-        <v>1127</v>
+        <v>1043</v>
       </c>
       <c r="F869" t="n">
         <v>542</v>
       </c>
       <c r="G869" t="n">
-        <v>4155</v>
+        <v>4143</v>
       </c>
       <c r="H869" t="n">
-        <v>17365</v>
+        <v>17363</v>
       </c>
       <c r="I869" t="n">
         <v>25</v>
+      </c>
+    </row>
+    <row r="870">
+      <c r="A870" s="1" t="n">
+        <v>46162</v>
+      </c>
+      <c r="B870" t="n">
+        <v>21985</v>
+      </c>
+      <c r="C870" t="n">
+        <v>8171</v>
+      </c>
+      <c r="D870" t="n">
+        <v>9268</v>
+      </c>
+      <c r="E870" t="n">
+        <v>1023</v>
+      </c>
+      <c r="F870" t="n">
+        <v>463</v>
+      </c>
+      <c r="G870" t="n">
+        <v>3060</v>
+      </c>
+      <c r="H870" t="n">
+        <v>17439</v>
+      </c>
+      <c r="I870" t="n">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="871">
+      <c r="A871" s="1" t="n">
+        <v>46163</v>
+      </c>
+      <c r="B871" t="n">
+        <v>23700</v>
+      </c>
+      <c r="C871" t="n">
+        <v>9139</v>
+      </c>
+      <c r="D871" t="n">
+        <v>10441</v>
+      </c>
+      <c r="E871" t="n">
+        <v>1003</v>
+      </c>
+      <c r="F871" t="n">
+        <v>293</v>
+      </c>
+      <c r="G871" t="n">
+        <v>2824</v>
+      </c>
+      <c r="H871" t="n">
+        <v>19580</v>
+      </c>
+      <c r="I871" t="n">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="872">
+      <c r="A872" s="1" t="n">
+        <v>46164</v>
+      </c>
+      <c r="B872" t="n">
+        <v>23222</v>
+      </c>
+      <c r="C872" t="n">
+        <v>8983</v>
+      </c>
+      <c r="D872" t="n">
+        <v>10651</v>
+      </c>
+      <c r="E872" t="n">
+        <v>709</v>
+      </c>
+      <c r="F872" t="n">
+        <v>295</v>
+      </c>
+      <c r="G872" t="n">
+        <v>2584</v>
+      </c>
+      <c r="H872" t="n">
+        <v>19634</v>
+      </c>
+      <c r="I872" t="n">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="873">
+      <c r="A873" s="1" t="n">
+        <v>46165</v>
+      </c>
+      <c r="B873" t="n">
+        <v>16511</v>
+      </c>
+      <c r="C873" t="n">
+        <v>7479</v>
+      </c>
+      <c r="D873" t="n">
+        <v>7896</v>
+      </c>
+      <c r="E873" t="n">
+        <v>224</v>
+      </c>
+      <c r="F873" t="n">
+        <v>2</v>
+      </c>
+      <c r="G873" t="n">
+        <v>910</v>
+      </c>
+      <c r="H873" t="n">
+        <v>15375</v>
+      </c>
+      <c r="I873" t="n">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="874">
+      <c r="A874" s="1" t="n">
+        <v>46166</v>
+      </c>
+      <c r="B874" t="n">
+        <v>13110</v>
+      </c>
+      <c r="C874" t="n">
+        <v>6828</v>
+      </c>
+      <c r="D874" t="n">
+        <v>6155</v>
+      </c>
+      <c r="E874" t="n">
+        <v>0</v>
+      </c>
+      <c r="F874" t="n">
+        <v>1</v>
+      </c>
+      <c r="G874" t="n">
+        <v>126</v>
+      </c>
+      <c r="H874" t="n">
+        <v>12983</v>
+      </c>
+      <c r="I874" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="875">
+      <c r="A875" s="1" t="n">
+        <v>46167</v>
+      </c>
+      <c r="B875" t="n">
+        <v>14816</v>
+      </c>
+      <c r="C875" t="n">
+        <v>7463</v>
+      </c>
+      <c r="D875" t="n">
+        <v>6955</v>
+      </c>
+      <c r="E875" t="n">
+        <v>270</v>
+      </c>
+      <c r="F875" t="n">
+        <v>1</v>
+      </c>
+      <c r="G875" t="n">
+        <v>127</v>
+      </c>
+      <c r="H875" t="n">
+        <v>14418</v>
+      </c>
+      <c r="I875" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="876">
+      <c r="A876" s="1" t="n">
+        <v>46168</v>
+      </c>
+      <c r="B876" t="n">
+        <v>23965</v>
+      </c>
+      <c r="C876" t="n">
+        <v>8115</v>
+      </c>
+      <c r="D876" t="n">
+        <v>7818</v>
+      </c>
+      <c r="E876" t="n">
+        <v>1556</v>
+      </c>
+      <c r="F876" t="n">
+        <v>1272</v>
+      </c>
+      <c r="G876" t="n">
+        <v>5204</v>
+      </c>
+      <c r="H876" t="n">
+        <v>15933</v>
+      </c>
+      <c r="I876" t="n">
+        <v>23</v>
       </c>
     </row>
   </sheetData>

--- a/data/total_latest.xlsx
+++ b/data/total_latest.xlsx
@@ -20,13 +20,16 @@
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
   </numFmts>
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -37,7 +40,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -45,12 +48,21 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
@@ -417,58 +429,58 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I876"/>
+  <dimension ref="A1:I897"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>날짜</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>총 물량</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>지그재그_당일</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>지그재그_익일</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>카카오모빌리티</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>부스터스</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>순수_기타물량</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>지그재그 당일배송</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>셀러수</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="1" t="n">
+      <c r="A2" s="2" t="n">
         <v>45293</v>
       </c>
       <c r="B2" t="n">
@@ -497,7 +509,7 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="1" t="n">
+      <c r="A3" s="2" t="n">
         <v>45294</v>
       </c>
       <c r="B3" t="n">
@@ -526,7 +538,7 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="1" t="n">
+      <c r="A4" s="2" t="n">
         <v>45295</v>
       </c>
       <c r="B4" t="n">
@@ -555,7 +567,7 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="1" t="n">
+      <c r="A5" s="2" t="n">
         <v>45296</v>
       </c>
       <c r="B5" t="n">
@@ -584,7 +596,7 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="n">
+      <c r="A6" s="2" t="n">
         <v>45297</v>
       </c>
       <c r="B6" t="n">
@@ -613,7 +625,7 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="1" t="n">
+      <c r="A7" s="2" t="n">
         <v>45298</v>
       </c>
       <c r="B7" t="n">
@@ -642,7 +654,7 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="n">
+      <c r="A8" s="2" t="n">
         <v>45299</v>
       </c>
       <c r="B8" t="n">
@@ -671,7 +683,7 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="1" t="n">
+      <c r="A9" s="2" t="n">
         <v>45300</v>
       </c>
       <c r="B9" t="n">
@@ -700,7 +712,7 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="1" t="n">
+      <c r="A10" s="2" t="n">
         <v>45301</v>
       </c>
       <c r="B10" t="n">
@@ -729,7 +741,7 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="1" t="n">
+      <c r="A11" s="2" t="n">
         <v>45302</v>
       </c>
       <c r="B11" t="n">
@@ -758,7 +770,7 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="n">
+      <c r="A12" s="2" t="n">
         <v>45303</v>
       </c>
       <c r="B12" t="n">
@@ -787,7 +799,7 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="1" t="n">
+      <c r="A13" s="2" t="n">
         <v>45304</v>
       </c>
       <c r="B13" t="n">
@@ -816,7 +828,7 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="1" t="n">
+      <c r="A14" s="2" t="n">
         <v>45305</v>
       </c>
       <c r="B14" t="n">
@@ -845,7 +857,7 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="1" t="n">
+      <c r="A15" s="2" t="n">
         <v>45306</v>
       </c>
       <c r="B15" t="n">
@@ -874,7 +886,7 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="1" t="n">
+      <c r="A16" s="2" t="n">
         <v>45307</v>
       </c>
       <c r="B16" t="n">
@@ -903,7 +915,7 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="1" t="n">
+      <c r="A17" s="2" t="n">
         <v>45308</v>
       </c>
       <c r="B17" t="n">
@@ -932,7 +944,7 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="1" t="n">
+      <c r="A18" s="2" t="n">
         <v>45309</v>
       </c>
       <c r="B18" t="n">
@@ -961,7 +973,7 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="1" t="n">
+      <c r="A19" s="2" t="n">
         <v>45310</v>
       </c>
       <c r="B19" t="n">
@@ -990,7 +1002,7 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="1" t="n">
+      <c r="A20" s="2" t="n">
         <v>45311</v>
       </c>
       <c r="B20" t="n">
@@ -1019,7 +1031,7 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="1" t="n">
+      <c r="A21" s="2" t="n">
         <v>45312</v>
       </c>
       <c r="B21" t="n">
@@ -1048,7 +1060,7 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="1" t="n">
+      <c r="A22" s="2" t="n">
         <v>45313</v>
       </c>
       <c r="B22" t="n">
@@ -1077,7 +1089,7 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="1" t="n">
+      <c r="A23" s="2" t="n">
         <v>45314</v>
       </c>
       <c r="B23" t="n">
@@ -1106,7 +1118,7 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="1" t="n">
+      <c r="A24" s="2" t="n">
         <v>45315</v>
       </c>
       <c r="B24" t="n">
@@ -1135,7 +1147,7 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="1" t="n">
+      <c r="A25" s="2" t="n">
         <v>45316</v>
       </c>
       <c r="B25" t="n">
@@ -1164,7 +1176,7 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="1" t="n">
+      <c r="A26" s="2" t="n">
         <v>45317</v>
       </c>
       <c r="B26" t="n">
@@ -1193,7 +1205,7 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="1" t="n">
+      <c r="A27" s="2" t="n">
         <v>45318</v>
       </c>
       <c r="B27" t="n">
@@ -1222,7 +1234,7 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="1" t="n">
+      <c r="A28" s="2" t="n">
         <v>45319</v>
       </c>
       <c r="B28" t="n">
@@ -1251,7 +1263,7 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="1" t="n">
+      <c r="A29" s="2" t="n">
         <v>45320</v>
       </c>
       <c r="B29" t="n">
@@ -1280,7 +1292,7 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="1" t="n">
+      <c r="A30" s="2" t="n">
         <v>45321</v>
       </c>
       <c r="B30" t="n">
@@ -1309,7 +1321,7 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="1" t="n">
+      <c r="A31" s="2" t="n">
         <v>45322</v>
       </c>
       <c r="B31" t="n">
@@ -1338,7 +1350,7 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="1" t="n">
+      <c r="A32" s="2" t="n">
         <v>45323</v>
       </c>
       <c r="B32" t="n">
@@ -1367,7 +1379,7 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="1" t="n">
+      <c r="A33" s="2" t="n">
         <v>45324</v>
       </c>
       <c r="B33" t="n">
@@ -1396,7 +1408,7 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="1" t="n">
+      <c r="A34" s="2" t="n">
         <v>45325</v>
       </c>
       <c r="B34" t="n">
@@ -1425,7 +1437,7 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="1" t="n">
+      <c r="A35" s="2" t="n">
         <v>45326</v>
       </c>
       <c r="B35" t="n">
@@ -1454,7 +1466,7 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="1" t="n">
+      <c r="A36" s="2" t="n">
         <v>45327</v>
       </c>
       <c r="B36" t="n">
@@ -1483,7 +1495,7 @@
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="1" t="n">
+      <c r="A37" s="2" t="n">
         <v>45328</v>
       </c>
       <c r="B37" t="n">
@@ -1512,7 +1524,7 @@
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="1" t="n">
+      <c r="A38" s="2" t="n">
         <v>45329</v>
       </c>
       <c r="B38" t="n">
@@ -1541,7 +1553,7 @@
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="1" t="n">
+      <c r="A39" s="2" t="n">
         <v>45330</v>
       </c>
       <c r="B39" t="n">
@@ -1570,7 +1582,7 @@
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="1" t="n">
+      <c r="A40" s="2" t="n">
         <v>45331</v>
       </c>
       <c r="B40" t="n">
@@ -1599,7 +1611,7 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="1" t="n">
+      <c r="A41" s="2" t="n">
         <v>45332</v>
       </c>
       <c r="B41" t="n">
@@ -1628,7 +1640,7 @@
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="1" t="n">
+      <c r="A42" s="2" t="n">
         <v>45333</v>
       </c>
       <c r="B42" t="n">
@@ -1657,7 +1669,7 @@
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="1" t="n">
+      <c r="A43" s="2" t="n">
         <v>45334</v>
       </c>
       <c r="B43" t="n">
@@ -1686,7 +1698,7 @@
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="1" t="n">
+      <c r="A44" s="2" t="n">
         <v>45335</v>
       </c>
       <c r="B44" t="n">
@@ -1715,7 +1727,7 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="1" t="n">
+      <c r="A45" s="2" t="n">
         <v>45336</v>
       </c>
       <c r="B45" t="n">
@@ -1744,7 +1756,7 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="1" t="n">
+      <c r="A46" s="2" t="n">
         <v>45337</v>
       </c>
       <c r="B46" t="n">
@@ -1773,7 +1785,7 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="1" t="n">
+      <c r="A47" s="2" t="n">
         <v>45338</v>
       </c>
       <c r="B47" t="n">
@@ -1802,7 +1814,7 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="1" t="n">
+      <c r="A48" s="2" t="n">
         <v>45339</v>
       </c>
       <c r="B48" t="n">
@@ -1831,7 +1843,7 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="1" t="n">
+      <c r="A49" s="2" t="n">
         <v>45340</v>
       </c>
       <c r="B49" t="n">
@@ -1860,7 +1872,7 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="1" t="n">
+      <c r="A50" s="2" t="n">
         <v>45341</v>
       </c>
       <c r="B50" t="n">
@@ -1889,7 +1901,7 @@
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="1" t="n">
+      <c r="A51" s="2" t="n">
         <v>45342</v>
       </c>
       <c r="B51" t="n">
@@ -1918,7 +1930,7 @@
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="1" t="n">
+      <c r="A52" s="2" t="n">
         <v>45343</v>
       </c>
       <c r="B52" t="n">
@@ -1947,7 +1959,7 @@
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="1" t="n">
+      <c r="A53" s="2" t="n">
         <v>45344</v>
       </c>
       <c r="B53" t="n">
@@ -1976,7 +1988,7 @@
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="1" t="n">
+      <c r="A54" s="2" t="n">
         <v>45345</v>
       </c>
       <c r="B54" t="n">
@@ -2005,7 +2017,7 @@
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="1" t="n">
+      <c r="A55" s="2" t="n">
         <v>45346</v>
       </c>
       <c r="B55" t="n">
@@ -2034,7 +2046,7 @@
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="1" t="n">
+      <c r="A56" s="2" t="n">
         <v>45347</v>
       </c>
       <c r="B56" t="n">
@@ -2063,7 +2075,7 @@
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="1" t="n">
+      <c r="A57" s="2" t="n">
         <v>45348</v>
       </c>
       <c r="B57" t="n">
@@ -2092,7 +2104,7 @@
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="1" t="n">
+      <c r="A58" s="2" t="n">
         <v>45349</v>
       </c>
       <c r="B58" t="n">
@@ -2121,7 +2133,7 @@
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="1" t="n">
+      <c r="A59" s="2" t="n">
         <v>45350</v>
       </c>
       <c r="B59" t="n">
@@ -2150,7 +2162,7 @@
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="1" t="n">
+      <c r="A60" s="2" t="n">
         <v>45351</v>
       </c>
       <c r="B60" t="n">
@@ -2179,7 +2191,7 @@
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="1" t="n">
+      <c r="A61" s="2" t="n">
         <v>45352</v>
       </c>
       <c r="B61" t="n">
@@ -2208,7 +2220,7 @@
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="1" t="n">
+      <c r="A62" s="2" t="n">
         <v>45353</v>
       </c>
       <c r="B62" t="n">
@@ -2237,7 +2249,7 @@
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="1" t="n">
+      <c r="A63" s="2" t="n">
         <v>45354</v>
       </c>
       <c r="B63" t="n">
@@ -2266,7 +2278,7 @@
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="1" t="n">
+      <c r="A64" s="2" t="n">
         <v>45355</v>
       </c>
       <c r="B64" t="n">
@@ -2295,7 +2307,7 @@
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="1" t="n">
+      <c r="A65" s="2" t="n">
         <v>45356</v>
       </c>
       <c r="B65" t="n">
@@ -2324,7 +2336,7 @@
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="1" t="n">
+      <c r="A66" s="2" t="n">
         <v>45357</v>
       </c>
       <c r="B66" t="n">
@@ -2353,7 +2365,7 @@
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="1" t="n">
+      <c r="A67" s="2" t="n">
         <v>45358</v>
       </c>
       <c r="B67" t="n">
@@ -2382,7 +2394,7 @@
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="1" t="n">
+      <c r="A68" s="2" t="n">
         <v>45359</v>
       </c>
       <c r="B68" t="n">
@@ -2411,7 +2423,7 @@
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="1" t="n">
+      <c r="A69" s="2" t="n">
         <v>45360</v>
       </c>
       <c r="B69" t="n">
@@ -2440,7 +2452,7 @@
       </c>
     </row>
     <row r="70">
-      <c r="A70" s="1" t="n">
+      <c r="A70" s="2" t="n">
         <v>45361</v>
       </c>
       <c r="B70" t="n">
@@ -2469,7 +2481,7 @@
       </c>
     </row>
     <row r="71">
-      <c r="A71" s="1" t="n">
+      <c r="A71" s="2" t="n">
         <v>45362</v>
       </c>
       <c r="B71" t="n">
@@ -2498,7 +2510,7 @@
       </c>
     </row>
     <row r="72">
-      <c r="A72" s="1" t="n">
+      <c r="A72" s="2" t="n">
         <v>45363</v>
       </c>
       <c r="B72" t="n">
@@ -2527,7 +2539,7 @@
       </c>
     </row>
     <row r="73">
-      <c r="A73" s="1" t="n">
+      <c r="A73" s="2" t="n">
         <v>45364</v>
       </c>
       <c r="B73" t="n">
@@ -2556,7 +2568,7 @@
       </c>
     </row>
     <row r="74">
-      <c r="A74" s="1" t="n">
+      <c r="A74" s="2" t="n">
         <v>45365</v>
       </c>
       <c r="B74" t="n">
@@ -2585,7 +2597,7 @@
       </c>
     </row>
     <row r="75">
-      <c r="A75" s="1" t="n">
+      <c r="A75" s="2" t="n">
         <v>45366</v>
       </c>
       <c r="B75" t="n">
@@ -2614,7 +2626,7 @@
       </c>
     </row>
     <row r="76">
-      <c r="A76" s="1" t="n">
+      <c r="A76" s="2" t="n">
         <v>45367</v>
       </c>
       <c r="B76" t="n">
@@ -2643,7 +2655,7 @@
       </c>
     </row>
     <row r="77">
-      <c r="A77" s="1" t="n">
+      <c r="A77" s="2" t="n">
         <v>45368</v>
       </c>
       <c r="B77" t="n">
@@ -2672,7 +2684,7 @@
       </c>
     </row>
     <row r="78">
-      <c r="A78" s="1" t="n">
+      <c r="A78" s="2" t="n">
         <v>45369</v>
       </c>
       <c r="B78" t="n">
@@ -2701,7 +2713,7 @@
       </c>
     </row>
     <row r="79">
-      <c r="A79" s="1" t="n">
+      <c r="A79" s="2" t="n">
         <v>45370</v>
       </c>
       <c r="B79" t="n">
@@ -2730,7 +2742,7 @@
       </c>
     </row>
     <row r="80">
-      <c r="A80" s="1" t="n">
+      <c r="A80" s="2" t="n">
         <v>45371</v>
       </c>
       <c r="B80" t="n">
@@ -2759,7 +2771,7 @@
       </c>
     </row>
     <row r="81">
-      <c r="A81" s="1" t="n">
+      <c r="A81" s="2" t="n">
         <v>45372</v>
       </c>
       <c r="B81" t="n">
@@ -2788,7 +2800,7 @@
       </c>
     </row>
     <row r="82">
-      <c r="A82" s="1" t="n">
+      <c r="A82" s="2" t="n">
         <v>45373</v>
       </c>
       <c r="B82" t="n">
@@ -2817,7 +2829,7 @@
       </c>
     </row>
     <row r="83">
-      <c r="A83" s="1" t="n">
+      <c r="A83" s="2" t="n">
         <v>45374</v>
       </c>
       <c r="B83" t="n">
@@ -2846,7 +2858,7 @@
       </c>
     </row>
     <row r="84">
-      <c r="A84" s="1" t="n">
+      <c r="A84" s="2" t="n">
         <v>45375</v>
       </c>
       <c r="B84" t="n">
@@ -2875,7 +2887,7 @@
       </c>
     </row>
     <row r="85">
-      <c r="A85" s="1" t="n">
+      <c r="A85" s="2" t="n">
         <v>45376</v>
       </c>
       <c r="B85" t="n">
@@ -2904,7 +2916,7 @@
       </c>
     </row>
     <row r="86">
-      <c r="A86" s="1" t="n">
+      <c r="A86" s="2" t="n">
         <v>45377</v>
       </c>
       <c r="B86" t="n">
@@ -2933,7 +2945,7 @@
       </c>
     </row>
     <row r="87">
-      <c r="A87" s="1" t="n">
+      <c r="A87" s="2" t="n">
         <v>45378</v>
       </c>
       <c r="B87" t="n">
@@ -2962,7 +2974,7 @@
       </c>
     </row>
     <row r="88">
-      <c r="A88" s="1" t="n">
+      <c r="A88" s="2" t="n">
         <v>45379</v>
       </c>
       <c r="B88" t="n">
@@ -2991,7 +3003,7 @@
       </c>
     </row>
     <row r="89">
-      <c r="A89" s="1" t="n">
+      <c r="A89" s="2" t="n">
         <v>45380</v>
       </c>
       <c r="B89" t="n">
@@ -3020,7 +3032,7 @@
       </c>
     </row>
     <row r="90">
-      <c r="A90" s="1" t="n">
+      <c r="A90" s="2" t="n">
         <v>45381</v>
       </c>
       <c r="B90" t="n">
@@ -3049,7 +3061,7 @@
       </c>
     </row>
     <row r="91">
-      <c r="A91" s="1" t="n">
+      <c r="A91" s="2" t="n">
         <v>45382</v>
       </c>
       <c r="B91" t="n">
@@ -3078,7 +3090,7 @@
       </c>
     </row>
     <row r="92">
-      <c r="A92" s="1" t="n">
+      <c r="A92" s="2" t="n">
         <v>45383</v>
       </c>
       <c r="B92" t="n">
@@ -3107,7 +3119,7 @@
       </c>
     </row>
     <row r="93">
-      <c r="A93" s="1" t="n">
+      <c r="A93" s="2" t="n">
         <v>45384</v>
       </c>
       <c r="B93" t="n">
@@ -3136,7 +3148,7 @@
       </c>
     </row>
     <row r="94">
-      <c r="A94" s="1" t="n">
+      <c r="A94" s="2" t="n">
         <v>45385</v>
       </c>
       <c r="B94" t="n">
@@ -3165,7 +3177,7 @@
       </c>
     </row>
     <row r="95">
-      <c r="A95" s="1" t="n">
+      <c r="A95" s="2" t="n">
         <v>45386</v>
       </c>
       <c r="B95" t="n">
@@ -3194,7 +3206,7 @@
       </c>
     </row>
     <row r="96">
-      <c r="A96" s="1" t="n">
+      <c r="A96" s="2" t="n">
         <v>45387</v>
       </c>
       <c r="B96" t="n">
@@ -3223,7 +3235,7 @@
       </c>
     </row>
     <row r="97">
-      <c r="A97" s="1" t="n">
+      <c r="A97" s="2" t="n">
         <v>45388</v>
       </c>
       <c r="B97" t="n">
@@ -3252,7 +3264,7 @@
       </c>
     </row>
     <row r="98">
-      <c r="A98" s="1" t="n">
+      <c r="A98" s="2" t="n">
         <v>45389</v>
       </c>
       <c r="B98" t="n">
@@ -3281,7 +3293,7 @@
       </c>
     </row>
     <row r="99">
-      <c r="A99" s="1" t="n">
+      <c r="A99" s="2" t="n">
         <v>45390</v>
       </c>
       <c r="B99" t="n">
@@ -3310,7 +3322,7 @@
       </c>
     </row>
     <row r="100">
-      <c r="A100" s="1" t="n">
+      <c r="A100" s="2" t="n">
         <v>45391</v>
       </c>
       <c r="B100" t="n">
@@ -3339,7 +3351,7 @@
       </c>
     </row>
     <row r="101">
-      <c r="A101" s="1" t="n">
+      <c r="A101" s="2" t="n">
         <v>45392</v>
       </c>
       <c r="B101" t="n">
@@ -3368,7 +3380,7 @@
       </c>
     </row>
     <row r="102">
-      <c r="A102" s="1" t="n">
+      <c r="A102" s="2" t="n">
         <v>45393</v>
       </c>
       <c r="B102" t="n">
@@ -3397,7 +3409,7 @@
       </c>
     </row>
     <row r="103">
-      <c r="A103" s="1" t="n">
+      <c r="A103" s="2" t="n">
         <v>45394</v>
       </c>
       <c r="B103" t="n">
@@ -3426,7 +3438,7 @@
       </c>
     </row>
     <row r="104">
-      <c r="A104" s="1" t="n">
+      <c r="A104" s="2" t="n">
         <v>45395</v>
       </c>
       <c r="B104" t="n">
@@ -3455,7 +3467,7 @@
       </c>
     </row>
     <row r="105">
-      <c r="A105" s="1" t="n">
+      <c r="A105" s="2" t="n">
         <v>45396</v>
       </c>
       <c r="B105" t="n">
@@ -3484,7 +3496,7 @@
       </c>
     </row>
     <row r="106">
-      <c r="A106" s="1" t="n">
+      <c r="A106" s="2" t="n">
         <v>45397</v>
       </c>
       <c r="B106" t="n">
@@ -3513,7 +3525,7 @@
       </c>
     </row>
     <row r="107">
-      <c r="A107" s="1" t="n">
+      <c r="A107" s="2" t="n">
         <v>45398</v>
       </c>
       <c r="B107" t="n">
@@ -3542,7 +3554,7 @@
       </c>
     </row>
     <row r="108">
-      <c r="A108" s="1" t="n">
+      <c r="A108" s="2" t="n">
         <v>45399</v>
       </c>
       <c r="B108" t="n">
@@ -3571,7 +3583,7 @@
       </c>
     </row>
     <row r="109">
-      <c r="A109" s="1" t="n">
+      <c r="A109" s="2" t="n">
         <v>45400</v>
       </c>
       <c r="B109" t="n">
@@ -3600,7 +3612,7 @@
       </c>
     </row>
     <row r="110">
-      <c r="A110" s="1" t="n">
+      <c r="A110" s="2" t="n">
         <v>45401</v>
       </c>
       <c r="B110" t="n">
@@ -3629,7 +3641,7 @@
       </c>
     </row>
     <row r="111">
-      <c r="A111" s="1" t="n">
+      <c r="A111" s="2" t="n">
         <v>45402</v>
       </c>
       <c r="B111" t="n">
@@ -3658,7 +3670,7 @@
       </c>
     </row>
     <row r="112">
-      <c r="A112" s="1" t="n">
+      <c r="A112" s="2" t="n">
         <v>45403</v>
       </c>
       <c r="B112" t="n">
@@ -3687,7 +3699,7 @@
       </c>
     </row>
     <row r="113">
-      <c r="A113" s="1" t="n">
+      <c r="A113" s="2" t="n">
         <v>45404</v>
       </c>
       <c r="B113" t="n">
@@ -3716,7 +3728,7 @@
       </c>
     </row>
     <row r="114">
-      <c r="A114" s="1" t="n">
+      <c r="A114" s="2" t="n">
         <v>45405</v>
       </c>
       <c r="B114" t="n">
@@ -3745,7 +3757,7 @@
       </c>
     </row>
     <row r="115">
-      <c r="A115" s="1" t="n">
+      <c r="A115" s="2" t="n">
         <v>45406</v>
       </c>
       <c r="B115" t="n">
@@ -3774,7 +3786,7 @@
       </c>
     </row>
     <row r="116">
-      <c r="A116" s="1" t="n">
+      <c r="A116" s="2" t="n">
         <v>45407</v>
       </c>
       <c r="B116" t="n">
@@ -3803,7 +3815,7 @@
       </c>
     </row>
     <row r="117">
-      <c r="A117" s="1" t="n">
+      <c r="A117" s="2" t="n">
         <v>45408</v>
       </c>
       <c r="B117" t="n">
@@ -3832,7 +3844,7 @@
       </c>
     </row>
     <row r="118">
-      <c r="A118" s="1" t="n">
+      <c r="A118" s="2" t="n">
         <v>45409</v>
       </c>
       <c r="B118" t="n">
@@ -3861,7 +3873,7 @@
       </c>
     </row>
     <row r="119">
-      <c r="A119" s="1" t="n">
+      <c r="A119" s="2" t="n">
         <v>45410</v>
       </c>
       <c r="B119" t="n">
@@ -3890,7 +3902,7 @@
       </c>
     </row>
     <row r="120">
-      <c r="A120" s="1" t="n">
+      <c r="A120" s="2" t="n">
         <v>45411</v>
       </c>
       <c r="B120" t="n">
@@ -3919,7 +3931,7 @@
       </c>
     </row>
     <row r="121">
-      <c r="A121" s="1" t="n">
+      <c r="A121" s="2" t="n">
         <v>45412</v>
       </c>
       <c r="B121" t="n">
@@ -3948,7 +3960,7 @@
       </c>
     </row>
     <row r="122">
-      <c r="A122" s="1" t="n">
+      <c r="A122" s="2" t="n">
         <v>45413</v>
       </c>
       <c r="B122" t="n">
@@ -3977,7 +3989,7 @@
       </c>
     </row>
     <row r="123">
-      <c r="A123" s="1" t="n">
+      <c r="A123" s="2" t="n">
         <v>45414</v>
       </c>
       <c r="B123" t="n">
@@ -4006,7 +4018,7 @@
       </c>
     </row>
     <row r="124">
-      <c r="A124" s="1" t="n">
+      <c r="A124" s="2" t="n">
         <v>45415</v>
       </c>
       <c r="B124" t="n">
@@ -4035,7 +4047,7 @@
       </c>
     </row>
     <row r="125">
-      <c r="A125" s="1" t="n">
+      <c r="A125" s="2" t="n">
         <v>45416</v>
       </c>
       <c r="B125" t="n">
@@ -4064,7 +4076,7 @@
       </c>
     </row>
     <row r="126">
-      <c r="A126" s="1" t="n">
+      <c r="A126" s="2" t="n">
         <v>45417</v>
       </c>
       <c r="B126" t="n">
@@ -4093,7 +4105,7 @@
       </c>
     </row>
     <row r="127">
-      <c r="A127" s="1" t="n">
+      <c r="A127" s="2" t="n">
         <v>45418</v>
       </c>
       <c r="B127" t="n">
@@ -4122,7 +4134,7 @@
       </c>
     </row>
     <row r="128">
-      <c r="A128" s="1" t="n">
+      <c r="A128" s="2" t="n">
         <v>45419</v>
       </c>
       <c r="B128" t="n">
@@ -4151,7 +4163,7 @@
       </c>
     </row>
     <row r="129">
-      <c r="A129" s="1" t="n">
+      <c r="A129" s="2" t="n">
         <v>45420</v>
       </c>
       <c r="B129" t="n">
@@ -4180,7 +4192,7 @@
       </c>
     </row>
     <row r="130">
-      <c r="A130" s="1" t="n">
+      <c r="A130" s="2" t="n">
         <v>45421</v>
       </c>
       <c r="B130" t="n">
@@ -4209,7 +4221,7 @@
       </c>
     </row>
     <row r="131">
-      <c r="A131" s="1" t="n">
+      <c r="A131" s="2" t="n">
         <v>45422</v>
       </c>
       <c r="B131" t="n">
@@ -4238,7 +4250,7 @@
       </c>
     </row>
     <row r="132">
-      <c r="A132" s="1" t="n">
+      <c r="A132" s="2" t="n">
         <v>45423</v>
       </c>
       <c r="B132" t="n">
@@ -4267,7 +4279,7 @@
       </c>
     </row>
     <row r="133">
-      <c r="A133" s="1" t="n">
+      <c r="A133" s="2" t="n">
         <v>45424</v>
       </c>
       <c r="B133" t="n">
@@ -4296,7 +4308,7 @@
       </c>
     </row>
     <row r="134">
-      <c r="A134" s="1" t="n">
+      <c r="A134" s="2" t="n">
         <v>45425</v>
       </c>
       <c r="B134" t="n">
@@ -4325,7 +4337,7 @@
       </c>
     </row>
     <row r="135">
-      <c r="A135" s="1" t="n">
+      <c r="A135" s="2" t="n">
         <v>45426</v>
       </c>
       <c r="B135" t="n">
@@ -4354,7 +4366,7 @@
       </c>
     </row>
     <row r="136">
-      <c r="A136" s="1" t="n">
+      <c r="A136" s="2" t="n">
         <v>45427</v>
       </c>
       <c r="B136" t="n">
@@ -4383,7 +4395,7 @@
       </c>
     </row>
     <row r="137">
-      <c r="A137" s="1" t="n">
+      <c r="A137" s="2" t="n">
         <v>45428</v>
       </c>
       <c r="B137" t="n">
@@ -4412,7 +4424,7 @@
       </c>
     </row>
     <row r="138">
-      <c r="A138" s="1" t="n">
+      <c r="A138" s="2" t="n">
         <v>45429</v>
       </c>
       <c r="B138" t="n">
@@ -4441,7 +4453,7 @@
       </c>
     </row>
     <row r="139">
-      <c r="A139" s="1" t="n">
+      <c r="A139" s="2" t="n">
         <v>45430</v>
       </c>
       <c r="B139" t="n">
@@ -4470,7 +4482,7 @@
       </c>
     </row>
     <row r="140">
-      <c r="A140" s="1" t="n">
+      <c r="A140" s="2" t="n">
         <v>45431</v>
       </c>
       <c r="B140" t="n">
@@ -4499,7 +4511,7 @@
       </c>
     </row>
     <row r="141">
-      <c r="A141" s="1" t="n">
+      <c r="A141" s="2" t="n">
         <v>45432</v>
       </c>
       <c r="B141" t="n">
@@ -4528,7 +4540,7 @@
       </c>
     </row>
     <row r="142">
-      <c r="A142" s="1" t="n">
+      <c r="A142" s="2" t="n">
         <v>45433</v>
       </c>
       <c r="B142" t="n">
@@ -4557,7 +4569,7 @@
       </c>
     </row>
     <row r="143">
-      <c r="A143" s="1" t="n">
+      <c r="A143" s="2" t="n">
         <v>45434</v>
       </c>
       <c r="B143" t="n">
@@ -4586,7 +4598,7 @@
       </c>
     </row>
     <row r="144">
-      <c r="A144" s="1" t="n">
+      <c r="A144" s="2" t="n">
         <v>45435</v>
       </c>
       <c r="B144" t="n">
@@ -4615,7 +4627,7 @@
       </c>
     </row>
     <row r="145">
-      <c r="A145" s="1" t="n">
+      <c r="A145" s="2" t="n">
         <v>45436</v>
       </c>
       <c r="B145" t="n">
@@ -4644,7 +4656,7 @@
       </c>
     </row>
     <row r="146">
-      <c r="A146" s="1" t="n">
+      <c r="A146" s="2" t="n">
         <v>45437</v>
       </c>
       <c r="B146" t="n">
@@ -4673,7 +4685,7 @@
       </c>
     </row>
     <row r="147">
-      <c r="A147" s="1" t="n">
+      <c r="A147" s="2" t="n">
         <v>45438</v>
       </c>
       <c r="B147" t="n">
@@ -4702,7 +4714,7 @@
       </c>
     </row>
     <row r="148">
-      <c r="A148" s="1" t="n">
+      <c r="A148" s="2" t="n">
         <v>45439</v>
       </c>
       <c r="B148" t="n">
@@ -4731,7 +4743,7 @@
       </c>
     </row>
     <row r="149">
-      <c r="A149" s="1" t="n">
+      <c r="A149" s="2" t="n">
         <v>45440</v>
       </c>
       <c r="B149" t="n">
@@ -4760,7 +4772,7 @@
       </c>
     </row>
     <row r="150">
-      <c r="A150" s="1" t="n">
+      <c r="A150" s="2" t="n">
         <v>45441</v>
       </c>
       <c r="B150" t="n">
@@ -4789,7 +4801,7 @@
       </c>
     </row>
     <row r="151">
-      <c r="A151" s="1" t="n">
+      <c r="A151" s="2" t="n">
         <v>45442</v>
       </c>
       <c r="B151" t="n">
@@ -4818,7 +4830,7 @@
       </c>
     </row>
     <row r="152">
-      <c r="A152" s="1" t="n">
+      <c r="A152" s="2" t="n">
         <v>45443</v>
       </c>
       <c r="B152" t="n">
@@ -4847,7 +4859,7 @@
       </c>
     </row>
     <row r="153">
-      <c r="A153" s="1" t="n">
+      <c r="A153" s="2" t="n">
         <v>45444</v>
       </c>
       <c r="B153" t="n">
@@ -4876,7 +4888,7 @@
       </c>
     </row>
     <row r="154">
-      <c r="A154" s="1" t="n">
+      <c r="A154" s="2" t="n">
         <v>45445</v>
       </c>
       <c r="B154" t="n">
@@ -4905,7 +4917,7 @@
       </c>
     </row>
     <row r="155">
-      <c r="A155" s="1" t="n">
+      <c r="A155" s="2" t="n">
         <v>45446</v>
       </c>
       <c r="B155" t="n">
@@ -4934,7 +4946,7 @@
       </c>
     </row>
     <row r="156">
-      <c r="A156" s="1" t="n">
+      <c r="A156" s="2" t="n">
         <v>45447</v>
       </c>
       <c r="B156" t="n">
@@ -4963,7 +4975,7 @@
       </c>
     </row>
     <row r="157">
-      <c r="A157" s="1" t="n">
+      <c r="A157" s="2" t="n">
         <v>45448</v>
       </c>
       <c r="B157" t="n">
@@ -4992,7 +5004,7 @@
       </c>
     </row>
     <row r="158">
-      <c r="A158" s="1" t="n">
+      <c r="A158" s="2" t="n">
         <v>45449</v>
       </c>
       <c r="B158" t="n">
@@ -5021,7 +5033,7 @@
       </c>
     </row>
     <row r="159">
-      <c r="A159" s="1" t="n">
+      <c r="A159" s="2" t="n">
         <v>45450</v>
       </c>
       <c r="B159" t="n">
@@ -5050,7 +5062,7 @@
       </c>
     </row>
     <row r="160">
-      <c r="A160" s="1" t="n">
+      <c r="A160" s="2" t="n">
         <v>45451</v>
       </c>
       <c r="B160" t="n">
@@ -5079,7 +5091,7 @@
       </c>
     </row>
     <row r="161">
-      <c r="A161" s="1" t="n">
+      <c r="A161" s="2" t="n">
         <v>45452</v>
       </c>
       <c r="B161" t="n">
@@ -5108,7 +5120,7 @@
       </c>
     </row>
     <row r="162">
-      <c r="A162" s="1" t="n">
+      <c r="A162" s="2" t="n">
         <v>45453</v>
       </c>
       <c r="B162" t="n">
@@ -5137,7 +5149,7 @@
       </c>
     </row>
     <row r="163">
-      <c r="A163" s="1" t="n">
+      <c r="A163" s="2" t="n">
         <v>45454</v>
       </c>
       <c r="B163" t="n">
@@ -5166,7 +5178,7 @@
       </c>
     </row>
     <row r="164">
-      <c r="A164" s="1" t="n">
+      <c r="A164" s="2" t="n">
         <v>45455</v>
       </c>
       <c r="B164" t="n">
@@ -5195,7 +5207,7 @@
       </c>
     </row>
     <row r="165">
-      <c r="A165" s="1" t="n">
+      <c r="A165" s="2" t="n">
         <v>45456</v>
       </c>
       <c r="B165" t="n">
@@ -5224,7 +5236,7 @@
       </c>
     </row>
     <row r="166">
-      <c r="A166" s="1" t="n">
+      <c r="A166" s="2" t="n">
         <v>45457</v>
       </c>
       <c r="B166" t="n">
@@ -5253,7 +5265,7 @@
       </c>
     </row>
     <row r="167">
-      <c r="A167" s="1" t="n">
+      <c r="A167" s="2" t="n">
         <v>45458</v>
       </c>
       <c r="B167" t="n">
@@ -5282,7 +5294,7 @@
       </c>
     </row>
     <row r="168">
-      <c r="A168" s="1" t="n">
+      <c r="A168" s="2" t="n">
         <v>45459</v>
       </c>
       <c r="B168" t="n">
@@ -5311,7 +5323,7 @@
       </c>
     </row>
     <row r="169">
-      <c r="A169" s="1" t="n">
+      <c r="A169" s="2" t="n">
         <v>45460</v>
       </c>
       <c r="B169" t="n">
@@ -5340,7 +5352,7 @@
       </c>
     </row>
     <row r="170">
-      <c r="A170" s="1" t="n">
+      <c r="A170" s="2" t="n">
         <v>45461</v>
       </c>
       <c r="B170" t="n">
@@ -5369,7 +5381,7 @@
       </c>
     </row>
     <row r="171">
-      <c r="A171" s="1" t="n">
+      <c r="A171" s="2" t="n">
         <v>45462</v>
       </c>
       <c r="B171" t="n">
@@ -5398,7 +5410,7 @@
       </c>
     </row>
     <row r="172">
-      <c r="A172" s="1" t="n">
+      <c r="A172" s="2" t="n">
         <v>45463</v>
       </c>
       <c r="B172" t="n">
@@ -5427,7 +5439,7 @@
       </c>
     </row>
     <row r="173">
-      <c r="A173" s="1" t="n">
+      <c r="A173" s="2" t="n">
         <v>45464</v>
       </c>
       <c r="B173" t="n">
@@ -5456,7 +5468,7 @@
       </c>
     </row>
     <row r="174">
-      <c r="A174" s="1" t="n">
+      <c r="A174" s="2" t="n">
         <v>45465</v>
       </c>
       <c r="B174" t="n">
@@ -5485,7 +5497,7 @@
       </c>
     </row>
     <row r="175">
-      <c r="A175" s="1" t="n">
+      <c r="A175" s="2" t="n">
         <v>45466</v>
       </c>
       <c r="B175" t="n">
@@ -5514,7 +5526,7 @@
       </c>
     </row>
     <row r="176">
-      <c r="A176" s="1" t="n">
+      <c r="A176" s="2" t="n">
         <v>45467</v>
       </c>
       <c r="B176" t="n">
@@ -5543,7 +5555,7 @@
       </c>
     </row>
     <row r="177">
-      <c r="A177" s="1" t="n">
+      <c r="A177" s="2" t="n">
         <v>45468</v>
       </c>
       <c r="B177" t="n">
@@ -5572,7 +5584,7 @@
       </c>
     </row>
     <row r="178">
-      <c r="A178" s="1" t="n">
+      <c r="A178" s="2" t="n">
         <v>45469</v>
       </c>
       <c r="B178" t="n">
@@ -5601,7 +5613,7 @@
       </c>
     </row>
     <row r="179">
-      <c r="A179" s="1" t="n">
+      <c r="A179" s="2" t="n">
         <v>45470</v>
       </c>
       <c r="B179" t="n">
@@ -5630,7 +5642,7 @@
       </c>
     </row>
     <row r="180">
-      <c r="A180" s="1" t="n">
+      <c r="A180" s="2" t="n">
         <v>45471</v>
       </c>
       <c r="B180" t="n">
@@ -5659,7 +5671,7 @@
       </c>
     </row>
     <row r="181">
-      <c r="A181" s="1" t="n">
+      <c r="A181" s="2" t="n">
         <v>45472</v>
       </c>
       <c r="B181" t="n">
@@ -5688,7 +5700,7 @@
       </c>
     </row>
     <row r="182">
-      <c r="A182" s="1" t="n">
+      <c r="A182" s="2" t="n">
         <v>45473</v>
       </c>
       <c r="B182" t="n">
@@ -5717,7 +5729,7 @@
       </c>
     </row>
     <row r="183">
-      <c r="A183" s="1" t="n">
+      <c r="A183" s="2" t="n">
         <v>45474</v>
       </c>
       <c r="B183" t="n">
@@ -5746,7 +5758,7 @@
       </c>
     </row>
     <row r="184">
-      <c r="A184" s="1" t="n">
+      <c r="A184" s="2" t="n">
         <v>45475</v>
       </c>
       <c r="B184" t="n">
@@ -5775,7 +5787,7 @@
       </c>
     </row>
     <row r="185">
-      <c r="A185" s="1" t="n">
+      <c r="A185" s="2" t="n">
         <v>45476</v>
       </c>
       <c r="B185" t="n">
@@ -5804,7 +5816,7 @@
       </c>
     </row>
     <row r="186">
-      <c r="A186" s="1" t="n">
+      <c r="A186" s="2" t="n">
         <v>45477</v>
       </c>
       <c r="B186" t="n">
@@ -5833,7 +5845,7 @@
       </c>
     </row>
     <row r="187">
-      <c r="A187" s="1" t="n">
+      <c r="A187" s="2" t="n">
         <v>45478</v>
       </c>
       <c r="B187" t="n">
@@ -5862,7 +5874,7 @@
       </c>
     </row>
     <row r="188">
-      <c r="A188" s="1" t="n">
+      <c r="A188" s="2" t="n">
         <v>45479</v>
       </c>
       <c r="B188" t="n">
@@ -5891,7 +5903,7 @@
       </c>
     </row>
     <row r="189">
-      <c r="A189" s="1" t="n">
+      <c r="A189" s="2" t="n">
         <v>45480</v>
       </c>
       <c r="B189" t="n">
@@ -5920,7 +5932,7 @@
       </c>
     </row>
     <row r="190">
-      <c r="A190" s="1" t="n">
+      <c r="A190" s="2" t="n">
         <v>45481</v>
       </c>
       <c r="B190" t="n">
@@ -5949,7 +5961,7 @@
       </c>
     </row>
     <row r="191">
-      <c r="A191" s="1" t="n">
+      <c r="A191" s="2" t="n">
         <v>45482</v>
       </c>
       <c r="B191" t="n">
@@ -5978,7 +5990,7 @@
       </c>
     </row>
     <row r="192">
-      <c r="A192" s="1" t="n">
+      <c r="A192" s="2" t="n">
         <v>45483</v>
       </c>
       <c r="B192" t="n">
@@ -6007,7 +6019,7 @@
       </c>
     </row>
     <row r="193">
-      <c r="A193" s="1" t="n">
+      <c r="A193" s="2" t="n">
         <v>45484</v>
       </c>
       <c r="B193" t="n">
@@ -6036,7 +6048,7 @@
       </c>
     </row>
     <row r="194">
-      <c r="A194" s="1" t="n">
+      <c r="A194" s="2" t="n">
         <v>45485</v>
       </c>
       <c r="B194" t="n">
@@ -6065,7 +6077,7 @@
       </c>
     </row>
     <row r="195">
-      <c r="A195" s="1" t="n">
+      <c r="A195" s="2" t="n">
         <v>45486</v>
       </c>
       <c r="B195" t="n">
@@ -6094,7 +6106,7 @@
       </c>
     </row>
     <row r="196">
-      <c r="A196" s="1" t="n">
+      <c r="A196" s="2" t="n">
         <v>45487</v>
       </c>
       <c r="B196" t="n">
@@ -6123,7 +6135,7 @@
       </c>
     </row>
     <row r="197">
-      <c r="A197" s="1" t="n">
+      <c r="A197" s="2" t="n">
         <v>45488</v>
       </c>
       <c r="B197" t="n">
@@ -6152,7 +6164,7 @@
       </c>
     </row>
     <row r="198">
-      <c r="A198" s="1" t="n">
+      <c r="A198" s="2" t="n">
         <v>45489</v>
       </c>
       <c r="B198" t="n">
@@ -6181,7 +6193,7 @@
       </c>
     </row>
     <row r="199">
-      <c r="A199" s="1" t="n">
+      <c r="A199" s="2" t="n">
         <v>45490</v>
       </c>
       <c r="B199" t="n">
@@ -6210,7 +6222,7 @@
       </c>
     </row>
     <row r="200">
-      <c r="A200" s="1" t="n">
+      <c r="A200" s="2" t="n">
         <v>45491</v>
       </c>
       <c r="B200" t="n">
@@ -6239,7 +6251,7 @@
       </c>
     </row>
     <row r="201">
-      <c r="A201" s="1" t="n">
+      <c r="A201" s="2" t="n">
         <v>45492</v>
       </c>
       <c r="B201" t="n">
@@ -6268,7 +6280,7 @@
       </c>
     </row>
     <row r="202">
-      <c r="A202" s="1" t="n">
+      <c r="A202" s="2" t="n">
         <v>45493</v>
       </c>
       <c r="B202" t="n">
@@ -6297,7 +6309,7 @@
       </c>
     </row>
     <row r="203">
-      <c r="A203" s="1" t="n">
+      <c r="A203" s="2" t="n">
         <v>45494</v>
       </c>
       <c r="B203" t="n">
@@ -6326,7 +6338,7 @@
       </c>
     </row>
     <row r="204">
-      <c r="A204" s="1" t="n">
+      <c r="A204" s="2" t="n">
         <v>45495</v>
       </c>
       <c r="B204" t="n">
@@ -6355,7 +6367,7 @@
       </c>
     </row>
     <row r="205">
-      <c r="A205" s="1" t="n">
+      <c r="A205" s="2" t="n">
         <v>45496</v>
       </c>
       <c r="B205" t="n">
@@ -6384,7 +6396,7 @@
       </c>
     </row>
     <row r="206">
-      <c r="A206" s="1" t="n">
+      <c r="A206" s="2" t="n">
         <v>45497</v>
       </c>
       <c r="B206" t="n">
@@ -6413,7 +6425,7 @@
       </c>
     </row>
     <row r="207">
-      <c r="A207" s="1" t="n">
+      <c r="A207" s="2" t="n">
         <v>45498</v>
       </c>
       <c r="B207" t="n">
@@ -6442,7 +6454,7 @@
       </c>
     </row>
     <row r="208">
-      <c r="A208" s="1" t="n">
+      <c r="A208" s="2" t="n">
         <v>45499</v>
       </c>
       <c r="B208" t="n">
@@ -6471,7 +6483,7 @@
       </c>
     </row>
     <row r="209">
-      <c r="A209" s="1" t="n">
+      <c r="A209" s="2" t="n">
         <v>45500</v>
       </c>
       <c r="B209" t="n">
@@ -6500,7 +6512,7 @@
       </c>
     </row>
     <row r="210">
-      <c r="A210" s="1" t="n">
+      <c r="A210" s="2" t="n">
         <v>45501</v>
       </c>
       <c r="B210" t="n">
@@ -6529,7 +6541,7 @@
       </c>
     </row>
     <row r="211">
-      <c r="A211" s="1" t="n">
+      <c r="A211" s="2" t="n">
         <v>45502</v>
       </c>
       <c r="B211" t="n">
@@ -6558,7 +6570,7 @@
       </c>
     </row>
     <row r="212">
-      <c r="A212" s="1" t="n">
+      <c r="A212" s="2" t="n">
         <v>45503</v>
       </c>
       <c r="B212" t="n">
@@ -6587,7 +6599,7 @@
       </c>
     </row>
     <row r="213">
-      <c r="A213" s="1" t="n">
+      <c r="A213" s="2" t="n">
         <v>45504</v>
       </c>
       <c r="B213" t="n">
@@ -6616,7 +6628,7 @@
       </c>
     </row>
     <row r="214">
-      <c r="A214" s="1" t="n">
+      <c r="A214" s="2" t="n">
         <v>45505</v>
       </c>
       <c r="B214" t="n">
@@ -6645,7 +6657,7 @@
       </c>
     </row>
     <row r="215">
-      <c r="A215" s="1" t="n">
+      <c r="A215" s="2" t="n">
         <v>45506</v>
       </c>
       <c r="B215" t="n">
@@ -6674,7 +6686,7 @@
       </c>
     </row>
     <row r="216">
-      <c r="A216" s="1" t="n">
+      <c r="A216" s="2" t="n">
         <v>45507</v>
       </c>
       <c r="B216" t="n">
@@ -6703,7 +6715,7 @@
       </c>
     </row>
     <row r="217">
-      <c r="A217" s="1" t="n">
+      <c r="A217" s="2" t="n">
         <v>45508</v>
       </c>
       <c r="B217" t="n">
@@ -6732,7 +6744,7 @@
       </c>
     </row>
     <row r="218">
-      <c r="A218" s="1" t="n">
+      <c r="A218" s="2" t="n">
         <v>45509</v>
       </c>
       <c r="B218" t="n">
@@ -6761,7 +6773,7 @@
       </c>
     </row>
     <row r="219">
-      <c r="A219" s="1" t="n">
+      <c r="A219" s="2" t="n">
         <v>45510</v>
       </c>
       <c r="B219" t="n">
@@ -6790,7 +6802,7 @@
       </c>
     </row>
     <row r="220">
-      <c r="A220" s="1" t="n">
+      <c r="A220" s="2" t="n">
         <v>45511</v>
       </c>
       <c r="B220" t="n">
@@ -6819,7 +6831,7 @@
       </c>
     </row>
     <row r="221">
-      <c r="A221" s="1" t="n">
+      <c r="A221" s="2" t="n">
         <v>45512</v>
       </c>
       <c r="B221" t="n">
@@ -6848,7 +6860,7 @@
       </c>
     </row>
     <row r="222">
-      <c r="A222" s="1" t="n">
+      <c r="A222" s="2" t="n">
         <v>45513</v>
       </c>
       <c r="B222" t="n">
@@ -6877,7 +6889,7 @@
       </c>
     </row>
     <row r="223">
-      <c r="A223" s="1" t="n">
+      <c r="A223" s="2" t="n">
         <v>45514</v>
       </c>
       <c r="B223" t="n">
@@ -6906,7 +6918,7 @@
       </c>
     </row>
     <row r="224">
-      <c r="A224" s="1" t="n">
+      <c r="A224" s="2" t="n">
         <v>45515</v>
       </c>
       <c r="B224" t="n">
@@ -6935,7 +6947,7 @@
       </c>
     </row>
     <row r="225">
-      <c r="A225" s="1" t="n">
+      <c r="A225" s="2" t="n">
         <v>45516</v>
       </c>
       <c r="B225" t="n">
@@ -6964,7 +6976,7 @@
       </c>
     </row>
     <row r="226">
-      <c r="A226" s="1" t="n">
+      <c r="A226" s="2" t="n">
         <v>45517</v>
       </c>
       <c r="B226" t="n">
@@ -6993,7 +7005,7 @@
       </c>
     </row>
     <row r="227">
-      <c r="A227" s="1" t="n">
+      <c r="A227" s="2" t="n">
         <v>45518</v>
       </c>
       <c r="B227" t="n">
@@ -7022,7 +7034,7 @@
       </c>
     </row>
     <row r="228">
-      <c r="A228" s="1" t="n">
+      <c r="A228" s="2" t="n">
         <v>45519</v>
       </c>
       <c r="B228" t="n">
@@ -7051,7 +7063,7 @@
       </c>
     </row>
     <row r="229">
-      <c r="A229" s="1" t="n">
+      <c r="A229" s="2" t="n">
         <v>45520</v>
       </c>
       <c r="B229" t="n">
@@ -7080,7 +7092,7 @@
       </c>
     </row>
     <row r="230">
-      <c r="A230" s="1" t="n">
+      <c r="A230" s="2" t="n">
         <v>45521</v>
       </c>
       <c r="B230" t="n">
@@ -7109,7 +7121,7 @@
       </c>
     </row>
     <row r="231">
-      <c r="A231" s="1" t="n">
+      <c r="A231" s="2" t="n">
         <v>45522</v>
       </c>
       <c r="B231" t="n">
@@ -7138,7 +7150,7 @@
       </c>
     </row>
     <row r="232">
-      <c r="A232" s="1" t="n">
+      <c r="A232" s="2" t="n">
         <v>45523</v>
       </c>
       <c r="B232" t="n">
@@ -7167,7 +7179,7 @@
       </c>
     </row>
     <row r="233">
-      <c r="A233" s="1" t="n">
+      <c r="A233" s="2" t="n">
         <v>45524</v>
       </c>
       <c r="B233" t="n">
@@ -7196,7 +7208,7 @@
       </c>
     </row>
     <row r="234">
-      <c r="A234" s="1" t="n">
+      <c r="A234" s="2" t="n">
         <v>45525</v>
       </c>
       <c r="B234" t="n">
@@ -7225,7 +7237,7 @@
       </c>
     </row>
     <row r="235">
-      <c r="A235" s="1" t="n">
+      <c r="A235" s="2" t="n">
         <v>45526</v>
       </c>
       <c r="B235" t="n">
@@ -7254,7 +7266,7 @@
       </c>
     </row>
     <row r="236">
-      <c r="A236" s="1" t="n">
+      <c r="A236" s="2" t="n">
         <v>45527</v>
       </c>
       <c r="B236" t="n">
@@ -7283,7 +7295,7 @@
       </c>
     </row>
     <row r="237">
-      <c r="A237" s="1" t="n">
+      <c r="A237" s="2" t="n">
         <v>45528</v>
       </c>
       <c r="B237" t="n">
@@ -7312,7 +7324,7 @@
       </c>
     </row>
     <row r="238">
-      <c r="A238" s="1" t="n">
+      <c r="A238" s="2" t="n">
         <v>45529</v>
       </c>
       <c r="B238" t="n">
@@ -7341,7 +7353,7 @@
       </c>
     </row>
     <row r="239">
-      <c r="A239" s="1" t="n">
+      <c r="A239" s="2" t="n">
         <v>45530</v>
       </c>
       <c r="B239" t="n">
@@ -7370,7 +7382,7 @@
       </c>
     </row>
     <row r="240">
-      <c r="A240" s="1" t="n">
+      <c r="A240" s="2" t="n">
         <v>45531</v>
       </c>
       <c r="B240" t="n">
@@ -7399,7 +7411,7 @@
       </c>
     </row>
     <row r="241">
-      <c r="A241" s="1" t="n">
+      <c r="A241" s="2" t="n">
         <v>45532</v>
       </c>
       <c r="B241" t="n">
@@ -7428,7 +7440,7 @@
       </c>
     </row>
     <row r="242">
-      <c r="A242" s="1" t="n">
+      <c r="A242" s="2" t="n">
         <v>45533</v>
       </c>
       <c r="B242" t="n">
@@ -7457,7 +7469,7 @@
       </c>
     </row>
     <row r="243">
-      <c r="A243" s="1" t="n">
+      <c r="A243" s="2" t="n">
         <v>45534</v>
       </c>
       <c r="B243" t="n">
@@ -7486,7 +7498,7 @@
       </c>
     </row>
     <row r="244">
-      <c r="A244" s="1" t="n">
+      <c r="A244" s="2" t="n">
         <v>45535</v>
       </c>
       <c r="B244" t="n">
@@ -7515,7 +7527,7 @@
       </c>
     </row>
     <row r="245">
-      <c r="A245" s="1" t="n">
+      <c r="A245" s="2" t="n">
         <v>45536</v>
       </c>
       <c r="B245" t="n">
@@ -7544,7 +7556,7 @@
       </c>
     </row>
     <row r="246">
-      <c r="A246" s="1" t="n">
+      <c r="A246" s="2" t="n">
         <v>45537</v>
       </c>
       <c r="B246" t="n">
@@ -7573,7 +7585,7 @@
       </c>
     </row>
     <row r="247">
-      <c r="A247" s="1" t="n">
+      <c r="A247" s="2" t="n">
         <v>45538</v>
       </c>
       <c r="B247" t="n">
@@ -7602,7 +7614,7 @@
       </c>
     </row>
     <row r="248">
-      <c r="A248" s="1" t="n">
+      <c r="A248" s="2" t="n">
         <v>45539</v>
       </c>
       <c r="B248" t="n">
@@ -7631,7 +7643,7 @@
       </c>
     </row>
     <row r="249">
-      <c r="A249" s="1" t="n">
+      <c r="A249" s="2" t="n">
         <v>45540</v>
       </c>
       <c r="B249" t="n">
@@ -7660,7 +7672,7 @@
       </c>
     </row>
     <row r="250">
-      <c r="A250" s="1" t="n">
+      <c r="A250" s="2" t="n">
         <v>45541</v>
       </c>
       <c r="B250" t="n">
@@ -7689,7 +7701,7 @@
       </c>
     </row>
     <row r="251">
-      <c r="A251" s="1" t="n">
+      <c r="A251" s="2" t="n">
         <v>45542</v>
       </c>
       <c r="B251" t="n">
@@ -7718,7 +7730,7 @@
       </c>
     </row>
     <row r="252">
-      <c r="A252" s="1" t="n">
+      <c r="A252" s="2" t="n">
         <v>45543</v>
       </c>
       <c r="B252" t="n">
@@ -7747,7 +7759,7 @@
       </c>
     </row>
     <row r="253">
-      <c r="A253" s="1" t="n">
+      <c r="A253" s="2" t="n">
         <v>45544</v>
       </c>
       <c r="B253" t="n">
@@ -7776,7 +7788,7 @@
       </c>
     </row>
     <row r="254">
-      <c r="A254" s="1" t="n">
+      <c r="A254" s="2" t="n">
         <v>45545</v>
       </c>
       <c r="B254" t="n">
@@ -7805,7 +7817,7 @@
       </c>
     </row>
     <row r="255">
-      <c r="A255" s="1" t="n">
+      <c r="A255" s="2" t="n">
         <v>45546</v>
       </c>
       <c r="B255" t="n">
@@ -7834,7 +7846,7 @@
       </c>
     </row>
     <row r="256">
-      <c r="A256" s="1" t="n">
+      <c r="A256" s="2" t="n">
         <v>45547</v>
       </c>
       <c r="B256" t="n">
@@ -7863,7 +7875,7 @@
       </c>
     </row>
     <row r="257">
-      <c r="A257" s="1" t="n">
+      <c r="A257" s="2" t="n">
         <v>45548</v>
       </c>
       <c r="B257" t="n">
@@ -7892,7 +7904,7 @@
       </c>
     </row>
     <row r="258">
-      <c r="A258" s="1" t="n">
+      <c r="A258" s="2" t="n">
         <v>45549</v>
       </c>
       <c r="B258" t="n">
@@ -7921,7 +7933,7 @@
       </c>
     </row>
     <row r="259">
-      <c r="A259" s="1" t="n">
+      <c r="A259" s="2" t="n">
         <v>45550</v>
       </c>
       <c r="B259" t="n">
@@ -7950,7 +7962,7 @@
       </c>
     </row>
     <row r="260">
-      <c r="A260" s="1" t="n">
+      <c r="A260" s="2" t="n">
         <v>45551</v>
       </c>
       <c r="B260" t="n">
@@ -7979,7 +7991,7 @@
       </c>
     </row>
     <row r="261">
-      <c r="A261" s="1" t="n">
+      <c r="A261" s="2" t="n">
         <v>45552</v>
       </c>
       <c r="B261" t="n">
@@ -8008,7 +8020,7 @@
       </c>
     </row>
     <row r="262">
-      <c r="A262" s="1" t="n">
+      <c r="A262" s="2" t="n">
         <v>45553</v>
       </c>
       <c r="B262" t="n">
@@ -8037,7 +8049,7 @@
       </c>
     </row>
     <row r="263">
-      <c r="A263" s="1" t="n">
+      <c r="A263" s="2" t="n">
         <v>45554</v>
       </c>
       <c r="B263" t="n">
@@ -8066,7 +8078,7 @@
       </c>
     </row>
     <row r="264">
-      <c r="A264" s="1" t="n">
+      <c r="A264" s="2" t="n">
         <v>45555</v>
       </c>
       <c r="B264" t="n">
@@ -8095,7 +8107,7 @@
       </c>
     </row>
     <row r="265">
-      <c r="A265" s="1" t="n">
+      <c r="A265" s="2" t="n">
         <v>45556</v>
       </c>
       <c r="B265" t="n">
@@ -8124,7 +8136,7 @@
       </c>
     </row>
     <row r="266">
-      <c r="A266" s="1" t="n">
+      <c r="A266" s="2" t="n">
         <v>45557</v>
       </c>
       <c r="B266" t="n">
@@ -8153,7 +8165,7 @@
       </c>
     </row>
     <row r="267">
-      <c r="A267" s="1" t="n">
+      <c r="A267" s="2" t="n">
         <v>45558</v>
       </c>
       <c r="B267" t="n">
@@ -8182,7 +8194,7 @@
       </c>
     </row>
     <row r="268">
-      <c r="A268" s="1" t="n">
+      <c r="A268" s="2" t="n">
         <v>45559</v>
       </c>
       <c r="B268" t="n">
@@ -8211,7 +8223,7 @@
       </c>
     </row>
     <row r="269">
-      <c r="A269" s="1" t="n">
+      <c r="A269" s="2" t="n">
         <v>45560</v>
       </c>
       <c r="B269" t="n">
@@ -8240,7 +8252,7 @@
       </c>
     </row>
     <row r="270">
-      <c r="A270" s="1" t="n">
+      <c r="A270" s="2" t="n">
         <v>45561</v>
       </c>
       <c r="B270" t="n">
@@ -8269,7 +8281,7 @@
       </c>
     </row>
     <row r="271">
-      <c r="A271" s="1" t="n">
+      <c r="A271" s="2" t="n">
         <v>45562</v>
       </c>
       <c r="B271" t="n">
@@ -8298,7 +8310,7 @@
       </c>
     </row>
     <row r="272">
-      <c r="A272" s="1" t="n">
+      <c r="A272" s="2" t="n">
         <v>45563</v>
       </c>
       <c r="B272" t="n">
@@ -8327,7 +8339,7 @@
       </c>
     </row>
     <row r="273">
-      <c r="A273" s="1" t="n">
+      <c r="A273" s="2" t="n">
         <v>45564</v>
       </c>
       <c r="B273" t="n">
@@ -8356,7 +8368,7 @@
       </c>
     </row>
     <row r="274">
-      <c r="A274" s="1" t="n">
+      <c r="A274" s="2" t="n">
         <v>45565</v>
       </c>
       <c r="B274" t="n">
@@ -8385,7 +8397,7 @@
       </c>
     </row>
     <row r="275">
-      <c r="A275" s="1" t="n">
+      <c r="A275" s="2" t="n">
         <v>45566</v>
       </c>
       <c r="B275" t="n">
@@ -8414,7 +8426,7 @@
       </c>
     </row>
     <row r="276">
-      <c r="A276" s="1" t="n">
+      <c r="A276" s="2" t="n">
         <v>45567</v>
       </c>
       <c r="B276" t="n">
@@ -8443,7 +8455,7 @@
       </c>
     </row>
     <row r="277">
-      <c r="A277" s="1" t="n">
+      <c r="A277" s="2" t="n">
         <v>45568</v>
       </c>
       <c r="B277" t="n">
@@ -8472,7 +8484,7 @@
       </c>
     </row>
     <row r="278">
-      <c r="A278" s="1" t="n">
+      <c r="A278" s="2" t="n">
         <v>45569</v>
       </c>
       <c r="B278" t="n">
@@ -8501,7 +8513,7 @@
       </c>
     </row>
     <row r="279">
-      <c r="A279" s="1" t="n">
+      <c r="A279" s="2" t="n">
         <v>45570</v>
       </c>
       <c r="B279" t="n">
@@ -8530,7 +8542,7 @@
       </c>
     </row>
     <row r="280">
-      <c r="A280" s="1" t="n">
+      <c r="A280" s="2" t="n">
         <v>45571</v>
       </c>
       <c r="B280" t="n">
@@ -8559,7 +8571,7 @@
       </c>
     </row>
     <row r="281">
-      <c r="A281" s="1" t="n">
+      <c r="A281" s="2" t="n">
         <v>45572</v>
       </c>
       <c r="B281" t="n">
@@ -8588,7 +8600,7 @@
       </c>
     </row>
     <row r="282">
-      <c r="A282" s="1" t="n">
+      <c r="A282" s="2" t="n">
         <v>45573</v>
       </c>
       <c r="B282" t="n">
@@ -8617,7 +8629,7 @@
       </c>
     </row>
     <row r="283">
-      <c r="A283" s="1" t="n">
+      <c r="A283" s="2" t="n">
         <v>45574</v>
       </c>
       <c r="B283" t="n">
@@ -8646,7 +8658,7 @@
       </c>
     </row>
     <row r="284">
-      <c r="A284" s="1" t="n">
+      <c r="A284" s="2" t="n">
         <v>45575</v>
       </c>
       <c r="B284" t="n">
@@ -8675,7 +8687,7 @@
       </c>
     </row>
     <row r="285">
-      <c r="A285" s="1" t="n">
+      <c r="A285" s="2" t="n">
         <v>45576</v>
       </c>
       <c r="B285" t="n">
@@ -8704,7 +8716,7 @@
       </c>
     </row>
     <row r="286">
-      <c r="A286" s="1" t="n">
+      <c r="A286" s="2" t="n">
         <v>45577</v>
       </c>
       <c r="B286" t="n">
@@ -8733,7 +8745,7 @@
       </c>
     </row>
     <row r="287">
-      <c r="A287" s="1" t="n">
+      <c r="A287" s="2" t="n">
         <v>45578</v>
       </c>
       <c r="B287" t="n">
@@ -8762,7 +8774,7 @@
       </c>
     </row>
     <row r="288">
-      <c r="A288" s="1" t="n">
+      <c r="A288" s="2" t="n">
         <v>45579</v>
       </c>
       <c r="B288" t="n">
@@ -8791,7 +8803,7 @@
       </c>
     </row>
     <row r="289">
-      <c r="A289" s="1" t="n">
+      <c r="A289" s="2" t="n">
         <v>45580</v>
       </c>
       <c r="B289" t="n">
@@ -8820,7 +8832,7 @@
       </c>
     </row>
     <row r="290">
-      <c r="A290" s="1" t="n">
+      <c r="A290" s="2" t="n">
         <v>45581</v>
       </c>
       <c r="B290" t="n">
@@ -8849,7 +8861,7 @@
       </c>
     </row>
     <row r="291">
-      <c r="A291" s="1" t="n">
+      <c r="A291" s="2" t="n">
         <v>45582</v>
       </c>
       <c r="B291" t="n">
@@ -8878,7 +8890,7 @@
       </c>
     </row>
     <row r="292">
-      <c r="A292" s="1" t="n">
+      <c r="A292" s="2" t="n">
         <v>45583</v>
       </c>
       <c r="B292" t="n">
@@ -8907,7 +8919,7 @@
       </c>
     </row>
     <row r="293">
-      <c r="A293" s="1" t="n">
+      <c r="A293" s="2" t="n">
         <v>45584</v>
       </c>
       <c r="B293" t="n">
@@ -8936,7 +8948,7 @@
       </c>
     </row>
     <row r="294">
-      <c r="A294" s="1" t="n">
+      <c r="A294" s="2" t="n">
         <v>45585</v>
       </c>
       <c r="B294" t="n">
@@ -8965,7 +8977,7 @@
       </c>
     </row>
     <row r="295">
-      <c r="A295" s="1" t="n">
+      <c r="A295" s="2" t="n">
         <v>45586</v>
       </c>
       <c r="B295" t="n">
@@ -8994,7 +9006,7 @@
       </c>
     </row>
     <row r="296">
-      <c r="A296" s="1" t="n">
+      <c r="A296" s="2" t="n">
         <v>45587</v>
       </c>
       <c r="B296" t="n">
@@ -9023,7 +9035,7 @@
       </c>
     </row>
     <row r="297">
-      <c r="A297" s="1" t="n">
+      <c r="A297" s="2" t="n">
         <v>45588</v>
       </c>
       <c r="B297" t="n">
@@ -9052,7 +9064,7 @@
       </c>
     </row>
     <row r="298">
-      <c r="A298" s="1" t="n">
+      <c r="A298" s="2" t="n">
         <v>45589</v>
       </c>
       <c r="B298" t="n">
@@ -9081,7 +9093,7 @@
       </c>
     </row>
     <row r="299">
-      <c r="A299" s="1" t="n">
+      <c r="A299" s="2" t="n">
         <v>45590</v>
       </c>
       <c r="B299" t="n">
@@ -9110,7 +9122,7 @@
       </c>
     </row>
     <row r="300">
-      <c r="A300" s="1" t="n">
+      <c r="A300" s="2" t="n">
         <v>45591</v>
       </c>
       <c r="B300" t="n">
@@ -9139,7 +9151,7 @@
       </c>
     </row>
     <row r="301">
-      <c r="A301" s="1" t="n">
+      <c r="A301" s="2" t="n">
         <v>45592</v>
       </c>
       <c r="B301" t="n">
@@ -9168,7 +9180,7 @@
       </c>
     </row>
     <row r="302">
-      <c r="A302" s="1" t="n">
+      <c r="A302" s="2" t="n">
         <v>45593</v>
       </c>
       <c r="B302" t="n">
@@ -9197,7 +9209,7 @@
       </c>
     </row>
     <row r="303">
-      <c r="A303" s="1" t="n">
+      <c r="A303" s="2" t="n">
         <v>45594</v>
       </c>
       <c r="B303" t="n">
@@ -9226,7 +9238,7 @@
       </c>
     </row>
     <row r="304">
-      <c r="A304" s="1" t="n">
+      <c r="A304" s="2" t="n">
         <v>45595</v>
       </c>
       <c r="B304" t="n">
@@ -9255,7 +9267,7 @@
       </c>
     </row>
     <row r="305">
-      <c r="A305" s="1" t="n">
+      <c r="A305" s="2" t="n">
         <v>45596</v>
       </c>
       <c r="B305" t="n">
@@ -9284,7 +9296,7 @@
       </c>
     </row>
     <row r="306">
-      <c r="A306" s="1" t="n">
+      <c r="A306" s="2" t="n">
         <v>45597</v>
       </c>
       <c r="B306" t="n">
@@ -9313,7 +9325,7 @@
       </c>
     </row>
     <row r="307">
-      <c r="A307" s="1" t="n">
+      <c r="A307" s="2" t="n">
         <v>45598</v>
       </c>
       <c r="B307" t="n">
@@ -9342,7 +9354,7 @@
       </c>
     </row>
     <row r="308">
-      <c r="A308" s="1" t="n">
+      <c r="A308" s="2" t="n">
         <v>45599</v>
       </c>
       <c r="B308" t="n">
@@ -9371,7 +9383,7 @@
       </c>
     </row>
     <row r="309">
-      <c r="A309" s="1" t="n">
+      <c r="A309" s="2" t="n">
         <v>45600</v>
       </c>
       <c r="B309" t="n">
@@ -9400,7 +9412,7 @@
       </c>
     </row>
     <row r="310">
-      <c r="A310" s="1" t="n">
+      <c r="A310" s="2" t="n">
         <v>45601</v>
       </c>
       <c r="B310" t="n">
@@ -9429,7 +9441,7 @@
       </c>
     </row>
     <row r="311">
-      <c r="A311" s="1" t="n">
+      <c r="A311" s="2" t="n">
         <v>45602</v>
       </c>
       <c r="B311" t="n">
@@ -9458,7 +9470,7 @@
       </c>
     </row>
     <row r="312">
-      <c r="A312" s="1" t="n">
+      <c r="A312" s="2" t="n">
         <v>45603</v>
       </c>
       <c r="B312" t="n">
@@ -9487,7 +9499,7 @@
       </c>
     </row>
     <row r="313">
-      <c r="A313" s="1" t="n">
+      <c r="A313" s="2" t="n">
         <v>45604</v>
       </c>
       <c r="B313" t="n">
@@ -9516,7 +9528,7 @@
       </c>
     </row>
     <row r="314">
-      <c r="A314" s="1" t="n">
+      <c r="A314" s="2" t="n">
         <v>45605</v>
       </c>
       <c r="B314" t="n">
@@ -9545,7 +9557,7 @@
       </c>
     </row>
     <row r="315">
-      <c r="A315" s="1" t="n">
+      <c r="A315" s="2" t="n">
         <v>45606</v>
       </c>
       <c r="B315" t="n">
@@ -9574,7 +9586,7 @@
       </c>
     </row>
     <row r="316">
-      <c r="A316" s="1" t="n">
+      <c r="A316" s="2" t="n">
         <v>45607</v>
       </c>
       <c r="B316" t="n">
@@ -9603,7 +9615,7 @@
       </c>
     </row>
     <row r="317">
-      <c r="A317" s="1" t="n">
+      <c r="A317" s="2" t="n">
         <v>45608</v>
       </c>
       <c r="B317" t="n">
@@ -9632,7 +9644,7 @@
       </c>
     </row>
     <row r="318">
-      <c r="A318" s="1" t="n">
+      <c r="A318" s="2" t="n">
         <v>45609</v>
       </c>
       <c r="B318" t="n">
@@ -9661,7 +9673,7 @@
       </c>
     </row>
     <row r="319">
-      <c r="A319" s="1" t="n">
+      <c r="A319" s="2" t="n">
         <v>45610</v>
       </c>
       <c r="B319" t="n">
@@ -9690,7 +9702,7 @@
       </c>
     </row>
     <row r="320">
-      <c r="A320" s="1" t="n">
+      <c r="A320" s="2" t="n">
         <v>45611</v>
       </c>
       <c r="B320" t="n">
@@ -9719,7 +9731,7 @@
       </c>
     </row>
     <row r="321">
-      <c r="A321" s="1" t="n">
+      <c r="A321" s="2" t="n">
         <v>45612</v>
       </c>
       <c r="B321" t="n">
@@ -9748,7 +9760,7 @@
       </c>
     </row>
     <row r="322">
-      <c r="A322" s="1" t="n">
+      <c r="A322" s="2" t="n">
         <v>45613</v>
       </c>
       <c r="B322" t="n">
@@ -9777,7 +9789,7 @@
       </c>
     </row>
     <row r="323">
-      <c r="A323" s="1" t="n">
+      <c r="A323" s="2" t="n">
         <v>45614</v>
       </c>
       <c r="B323" t="n">
@@ -9806,7 +9818,7 @@
       </c>
     </row>
     <row r="324">
-      <c r="A324" s="1" t="n">
+      <c r="A324" s="2" t="n">
         <v>45615</v>
       </c>
       <c r="B324" t="n">
@@ -9835,7 +9847,7 @@
       </c>
     </row>
     <row r="325">
-      <c r="A325" s="1" t="n">
+      <c r="A325" s="2" t="n">
         <v>45616</v>
       </c>
       <c r="B325" t="n">
@@ -9864,7 +9876,7 @@
       </c>
     </row>
     <row r="326">
-      <c r="A326" s="1" t="n">
+      <c r="A326" s="2" t="n">
         <v>45617</v>
       </c>
       <c r="B326" t="n">
@@ -9893,7 +9905,7 @@
       </c>
     </row>
     <row r="327">
-      <c r="A327" s="1" t="n">
+      <c r="A327" s="2" t="n">
         <v>45618</v>
       </c>
       <c r="B327" t="n">
@@ -9922,7 +9934,7 @@
       </c>
     </row>
     <row r="328">
-      <c r="A328" s="1" t="n">
+      <c r="A328" s="2" t="n">
         <v>45619</v>
       </c>
       <c r="B328" t="n">
@@ -9951,7 +9963,7 @@
       </c>
     </row>
     <row r="329">
-      <c r="A329" s="1" t="n">
+      <c r="A329" s="2" t="n">
         <v>45620</v>
       </c>
       <c r="B329" t="n">
@@ -9980,7 +9992,7 @@
       </c>
     </row>
     <row r="330">
-      <c r="A330" s="1" t="n">
+      <c r="A330" s="2" t="n">
         <v>45621</v>
       </c>
       <c r="B330" t="n">
@@ -10009,7 +10021,7 @@
       </c>
     </row>
     <row r="331">
-      <c r="A331" s="1" t="n">
+      <c r="A331" s="2" t="n">
         <v>45622</v>
       </c>
       <c r="B331" t="n">
@@ -10038,7 +10050,7 @@
       </c>
     </row>
     <row r="332">
-      <c r="A332" s="1" t="n">
+      <c r="A332" s="2" t="n">
         <v>45623</v>
       </c>
       <c r="B332" t="n">
@@ -10067,7 +10079,7 @@
       </c>
     </row>
     <row r="333">
-      <c r="A333" s="1" t="n">
+      <c r="A333" s="2" t="n">
         <v>45624</v>
       </c>
       <c r="B333" t="n">
@@ -10096,7 +10108,7 @@
       </c>
     </row>
     <row r="334">
-      <c r="A334" s="1" t="n">
+      <c r="A334" s="2" t="n">
         <v>45625</v>
       </c>
       <c r="B334" t="n">
@@ -10125,7 +10137,7 @@
       </c>
     </row>
     <row r="335">
-      <c r="A335" s="1" t="n">
+      <c r="A335" s="2" t="n">
         <v>45626</v>
       </c>
       <c r="B335" t="n">
@@ -10154,7 +10166,7 @@
       </c>
     </row>
     <row r="336">
-      <c r="A336" s="1" t="n">
+      <c r="A336" s="2" t="n">
         <v>45627</v>
       </c>
       <c r="B336" t="n">
@@ -10183,7 +10195,7 @@
       </c>
     </row>
     <row r="337">
-      <c r="A337" s="1" t="n">
+      <c r="A337" s="2" t="n">
         <v>45628</v>
       </c>
       <c r="B337" t="n">
@@ -10212,7 +10224,7 @@
       </c>
     </row>
     <row r="338">
-      <c r="A338" s="1" t="n">
+      <c r="A338" s="2" t="n">
         <v>45629</v>
       </c>
       <c r="B338" t="n">
@@ -10241,7 +10253,7 @@
       </c>
     </row>
     <row r="339">
-      <c r="A339" s="1" t="n">
+      <c r="A339" s="2" t="n">
         <v>45630</v>
       </c>
       <c r="B339" t="n">
@@ -10270,7 +10282,7 @@
       </c>
     </row>
     <row r="340">
-      <c r="A340" s="1" t="n">
+      <c r="A340" s="2" t="n">
         <v>45631</v>
       </c>
       <c r="B340" t="n">
@@ -10299,7 +10311,7 @@
       </c>
     </row>
     <row r="341">
-      <c r="A341" s="1" t="n">
+      <c r="A341" s="2" t="n">
         <v>45632</v>
       </c>
       <c r="B341" t="n">
@@ -10328,7 +10340,7 @@
       </c>
     </row>
     <row r="342">
-      <c r="A342" s="1" t="n">
+      <c r="A342" s="2" t="n">
         <v>45633</v>
       </c>
       <c r="B342" t="n">
@@ -10357,7 +10369,7 @@
       </c>
     </row>
     <row r="343">
-      <c r="A343" s="1" t="n">
+      <c r="A343" s="2" t="n">
         <v>45634</v>
       </c>
       <c r="B343" t="n">
@@ -10386,7 +10398,7 @@
       </c>
     </row>
     <row r="344">
-      <c r="A344" s="1" t="n">
+      <c r="A344" s="2" t="n">
         <v>45635</v>
       </c>
       <c r="B344" t="n">
@@ -10415,7 +10427,7 @@
       </c>
     </row>
     <row r="345">
-      <c r="A345" s="1" t="n">
+      <c r="A345" s="2" t="n">
         <v>45636</v>
       </c>
       <c r="B345" t="n">
@@ -10444,7 +10456,7 @@
       </c>
     </row>
     <row r="346">
-      <c r="A346" s="1" t="n">
+      <c r="A346" s="2" t="n">
         <v>45637</v>
       </c>
       <c r="B346" t="n">
@@ -10473,7 +10485,7 @@
       </c>
     </row>
     <row r="347">
-      <c r="A347" s="1" t="n">
+      <c r="A347" s="2" t="n">
         <v>45638</v>
       </c>
       <c r="B347" t="n">
@@ -10502,7 +10514,7 @@
       </c>
     </row>
     <row r="348">
-      <c r="A348" s="1" t="n">
+      <c r="A348" s="2" t="n">
         <v>45639</v>
       </c>
       <c r="B348" t="n">
@@ -10531,7 +10543,7 @@
       </c>
     </row>
     <row r="349">
-      <c r="A349" s="1" t="n">
+      <c r="A349" s="2" t="n">
         <v>45640</v>
       </c>
       <c r="B349" t="n">
@@ -10560,7 +10572,7 @@
       </c>
     </row>
     <row r="350">
-      <c r="A350" s="1" t="n">
+      <c r="A350" s="2" t="n">
         <v>45641</v>
       </c>
       <c r="B350" t="n">
@@ -10589,7 +10601,7 @@
       </c>
     </row>
     <row r="351">
-      <c r="A351" s="1" t="n">
+      <c r="A351" s="2" t="n">
         <v>45642</v>
       </c>
       <c r="B351" t="n">
@@ -10618,7 +10630,7 @@
       </c>
     </row>
     <row r="352">
-      <c r="A352" s="1" t="n">
+      <c r="A352" s="2" t="n">
         <v>45643</v>
       </c>
       <c r="B352" t="n">
@@ -10647,7 +10659,7 @@
       </c>
     </row>
     <row r="353">
-      <c r="A353" s="1" t="n">
+      <c r="A353" s="2" t="n">
         <v>45644</v>
       </c>
       <c r="B353" t="n">
@@ -10676,7 +10688,7 @@
       </c>
     </row>
     <row r="354">
-      <c r="A354" s="1" t="n">
+      <c r="A354" s="2" t="n">
         <v>45645</v>
       </c>
       <c r="B354" t="n">
@@ -10705,7 +10717,7 @@
       </c>
     </row>
     <row r="355">
-      <c r="A355" s="1" t="n">
+      <c r="A355" s="2" t="n">
         <v>45646</v>
       </c>
       <c r="B355" t="n">
@@ -10734,7 +10746,7 @@
       </c>
     </row>
     <row r="356">
-      <c r="A356" s="1" t="n">
+      <c r="A356" s="2" t="n">
         <v>45647</v>
       </c>
       <c r="B356" t="n">
@@ -10763,7 +10775,7 @@
       </c>
     </row>
     <row r="357">
-      <c r="A357" s="1" t="n">
+      <c r="A357" s="2" t="n">
         <v>45648</v>
       </c>
       <c r="B357" t="n">
@@ -10792,7 +10804,7 @@
       </c>
     </row>
     <row r="358">
-      <c r="A358" s="1" t="n">
+      <c r="A358" s="2" t="n">
         <v>45649</v>
       </c>
       <c r="B358" t="n">
@@ -10821,7 +10833,7 @@
       </c>
     </row>
     <row r="359">
-      <c r="A359" s="1" t="n">
+      <c r="A359" s="2" t="n">
         <v>45650</v>
       </c>
       <c r="B359" t="n">
@@ -10850,7 +10862,7 @@
       </c>
     </row>
     <row r="360">
-      <c r="A360" s="1" t="n">
+      <c r="A360" s="2" t="n">
         <v>45651</v>
       </c>
       <c r="B360" t="n">
@@ -10879,7 +10891,7 @@
       </c>
     </row>
     <row r="361">
-      <c r="A361" s="1" t="n">
+      <c r="A361" s="2" t="n">
         <v>45652</v>
       </c>
       <c r="B361" t="n">
@@ -10908,7 +10920,7 @@
       </c>
     </row>
     <row r="362">
-      <c r="A362" s="1" t="n">
+      <c r="A362" s="2" t="n">
         <v>45653</v>
       </c>
       <c r="B362" t="n">
@@ -10937,7 +10949,7 @@
       </c>
     </row>
     <row r="363">
-      <c r="A363" s="1" t="n">
+      <c r="A363" s="2" t="n">
         <v>45654</v>
       </c>
       <c r="B363" t="n">
@@ -10966,7 +10978,7 @@
       </c>
     </row>
     <row r="364">
-      <c r="A364" s="1" t="n">
+      <c r="A364" s="2" t="n">
         <v>45655</v>
       </c>
       <c r="B364" t="n">
@@ -10995,7 +11007,7 @@
       </c>
     </row>
     <row r="365">
-      <c r="A365" s="1" t="n">
+      <c r="A365" s="2" t="n">
         <v>45656</v>
       </c>
       <c r="B365" t="n">
@@ -11024,7 +11036,7 @@
       </c>
     </row>
     <row r="366">
-      <c r="A366" s="1" t="n">
+      <c r="A366" s="2" t="n">
         <v>45657</v>
       </c>
       <c r="B366" t="n">
@@ -11053,7 +11065,7 @@
       </c>
     </row>
     <row r="367">
-      <c r="A367" s="1" t="n">
+      <c r="A367" s="2" t="n">
         <v>45658</v>
       </c>
       <c r="B367" t="n">
@@ -11082,7 +11094,7 @@
       </c>
     </row>
     <row r="368">
-      <c r="A368" s="1" t="n">
+      <c r="A368" s="2" t="n">
         <v>45659</v>
       </c>
       <c r="B368" t="n">
@@ -11111,7 +11123,7 @@
       </c>
     </row>
     <row r="369">
-      <c r="A369" s="1" t="n">
+      <c r="A369" s="2" t="n">
         <v>45660</v>
       </c>
       <c r="B369" t="n">
@@ -11140,7 +11152,7 @@
       </c>
     </row>
     <row r="370">
-      <c r="A370" s="1" t="n">
+      <c r="A370" s="2" t="n">
         <v>45661</v>
       </c>
       <c r="B370" t="n">
@@ -11169,7 +11181,7 @@
       </c>
     </row>
     <row r="371">
-      <c r="A371" s="1" t="n">
+      <c r="A371" s="2" t="n">
         <v>45662</v>
       </c>
       <c r="B371" t="n">
@@ -11198,7 +11210,7 @@
       </c>
     </row>
     <row r="372">
-      <c r="A372" s="1" t="n">
+      <c r="A372" s="2" t="n">
         <v>45663</v>
       </c>
       <c r="B372" t="n">
@@ -11227,7 +11239,7 @@
       </c>
     </row>
     <row r="373">
-      <c r="A373" s="1" t="n">
+      <c r="A373" s="2" t="n">
         <v>45664</v>
       </c>
       <c r="B373" t="n">
@@ -11256,7 +11268,7 @@
       </c>
     </row>
     <row r="374">
-      <c r="A374" s="1" t="n">
+      <c r="A374" s="2" t="n">
         <v>45665</v>
       </c>
       <c r="B374" t="n">
@@ -11285,7 +11297,7 @@
       </c>
     </row>
     <row r="375">
-      <c r="A375" s="1" t="n">
+      <c r="A375" s="2" t="n">
         <v>45666</v>
       </c>
       <c r="B375" t="n">
@@ -11314,7 +11326,7 @@
       </c>
     </row>
     <row r="376">
-      <c r="A376" s="1" t="n">
+      <c r="A376" s="2" t="n">
         <v>45667</v>
       </c>
       <c r="B376" t="n">
@@ -11343,7 +11355,7 @@
       </c>
     </row>
     <row r="377">
-      <c r="A377" s="1" t="n">
+      <c r="A377" s="2" t="n">
         <v>45668</v>
       </c>
       <c r="B377" t="n">
@@ -11372,7 +11384,7 @@
       </c>
     </row>
     <row r="378">
-      <c r="A378" s="1" t="n">
+      <c r="A378" s="2" t="n">
         <v>45669</v>
       </c>
       <c r="B378" t="n">
@@ -11401,7 +11413,7 @@
       </c>
     </row>
     <row r="379">
-      <c r="A379" s="1" t="n">
+      <c r="A379" s="2" t="n">
         <v>45670</v>
       </c>
       <c r="B379" t="n">
@@ -11430,7 +11442,7 @@
       </c>
     </row>
     <row r="380">
-      <c r="A380" s="1" t="n">
+      <c r="A380" s="2" t="n">
         <v>45671</v>
       </c>
       <c r="B380" t="n">
@@ -11459,7 +11471,7 @@
       </c>
     </row>
     <row r="381">
-      <c r="A381" s="1" t="n">
+      <c r="A381" s="2" t="n">
         <v>45672</v>
       </c>
       <c r="B381" t="n">
@@ -11488,7 +11500,7 @@
       </c>
     </row>
     <row r="382">
-      <c r="A382" s="1" t="n">
+      <c r="A382" s="2" t="n">
         <v>45673</v>
       </c>
       <c r="B382" t="n">
@@ -11517,7 +11529,7 @@
       </c>
     </row>
     <row r="383">
-      <c r="A383" s="1" t="n">
+      <c r="A383" s="2" t="n">
         <v>45674</v>
       </c>
       <c r="B383" t="n">
@@ -11546,7 +11558,7 @@
       </c>
     </row>
     <row r="384">
-      <c r="A384" s="1" t="n">
+      <c r="A384" s="2" t="n">
         <v>45675</v>
       </c>
       <c r="B384" t="n">
@@ -11575,7 +11587,7 @@
       </c>
     </row>
     <row r="385">
-      <c r="A385" s="1" t="n">
+      <c r="A385" s="2" t="n">
         <v>45676</v>
       </c>
       <c r="B385" t="n">
@@ -11604,7 +11616,7 @@
       </c>
     </row>
     <row r="386">
-      <c r="A386" s="1" t="n">
+      <c r="A386" s="2" t="n">
         <v>45677</v>
       </c>
       <c r="B386" t="n">
@@ -11633,7 +11645,7 @@
       </c>
     </row>
     <row r="387">
-      <c r="A387" s="1" t="n">
+      <c r="A387" s="2" t="n">
         <v>45678</v>
       </c>
       <c r="B387" t="n">
@@ -11662,7 +11674,7 @@
       </c>
     </row>
     <row r="388">
-      <c r="A388" s="1" t="n">
+      <c r="A388" s="2" t="n">
         <v>45679</v>
       </c>
       <c r="B388" t="n">
@@ -11691,7 +11703,7 @@
       </c>
     </row>
     <row r="389">
-      <c r="A389" s="1" t="n">
+      <c r="A389" s="2" t="n">
         <v>45680</v>
       </c>
       <c r="B389" t="n">
@@ -11720,7 +11732,7 @@
       </c>
     </row>
     <row r="390">
-      <c r="A390" s="1" t="n">
+      <c r="A390" s="2" t="n">
         <v>45681</v>
       </c>
       <c r="B390" t="n">
@@ -11749,7 +11761,7 @@
       </c>
     </row>
     <row r="391">
-      <c r="A391" s="1" t="n">
+      <c r="A391" s="2" t="n">
         <v>45682</v>
       </c>
       <c r="B391" t="n">
@@ -11778,7 +11790,7 @@
       </c>
     </row>
     <row r="392">
-      <c r="A392" s="1" t="n">
+      <c r="A392" s="2" t="n">
         <v>45683</v>
       </c>
       <c r="B392" t="n">
@@ -11807,7 +11819,7 @@
       </c>
     </row>
     <row r="393">
-      <c r="A393" s="1" t="n">
+      <c r="A393" s="2" t="n">
         <v>45684</v>
       </c>
       <c r="B393" t="n">
@@ -11836,7 +11848,7 @@
       </c>
     </row>
     <row r="394">
-      <c r="A394" s="1" t="n">
+      <c r="A394" s="2" t="n">
         <v>45685</v>
       </c>
       <c r="B394" t="n">
@@ -11865,7 +11877,7 @@
       </c>
     </row>
     <row r="395">
-      <c r="A395" s="1" t="n">
+      <c r="A395" s="2" t="n">
         <v>45686</v>
       </c>
       <c r="B395" t="n">
@@ -11894,7 +11906,7 @@
       </c>
     </row>
     <row r="396">
-      <c r="A396" s="1" t="n">
+      <c r="A396" s="2" t="n">
         <v>45687</v>
       </c>
       <c r="B396" t="n">
@@ -11923,7 +11935,7 @@
       </c>
     </row>
     <row r="397">
-      <c r="A397" s="1" t="n">
+      <c r="A397" s="2" t="n">
         <v>45688</v>
       </c>
       <c r="B397" t="n">
@@ -11952,7 +11964,7 @@
       </c>
     </row>
     <row r="398">
-      <c r="A398" s="1" t="n">
+      <c r="A398" s="2" t="n">
         <v>45689</v>
       </c>
       <c r="B398" t="n">
@@ -11981,7 +11993,7 @@
       </c>
     </row>
     <row r="399">
-      <c r="A399" s="1" t="n">
+      <c r="A399" s="2" t="n">
         <v>45690</v>
       </c>
       <c r="B399" t="n">
@@ -12010,7 +12022,7 @@
       </c>
     </row>
     <row r="400">
-      <c r="A400" s="1" t="n">
+      <c r="A400" s="2" t="n">
         <v>45691</v>
       </c>
       <c r="B400" t="n">
@@ -12039,7 +12051,7 @@
       </c>
     </row>
     <row r="401">
-      <c r="A401" s="1" t="n">
+      <c r="A401" s="2" t="n">
         <v>45692</v>
       </c>
       <c r="B401" t="n">
@@ -12068,7 +12080,7 @@
       </c>
     </row>
     <row r="402">
-      <c r="A402" s="1" t="n">
+      <c r="A402" s="2" t="n">
         <v>45693</v>
       </c>
       <c r="B402" t="n">
@@ -12097,7 +12109,7 @@
       </c>
     </row>
     <row r="403">
-      <c r="A403" s="1" t="n">
+      <c r="A403" s="2" t="n">
         <v>45694</v>
       </c>
       <c r="B403" t="n">
@@ -12126,7 +12138,7 @@
       </c>
     </row>
     <row r="404">
-      <c r="A404" s="1" t="n">
+      <c r="A404" s="2" t="n">
         <v>45695</v>
       </c>
       <c r="B404" t="n">
@@ -12155,7 +12167,7 @@
       </c>
     </row>
     <row r="405">
-      <c r="A405" s="1" t="n">
+      <c r="A405" s="2" t="n">
         <v>45696</v>
       </c>
       <c r="B405" t="n">
@@ -12184,7 +12196,7 @@
       </c>
     </row>
     <row r="406">
-      <c r="A406" s="1" t="n">
+      <c r="A406" s="2" t="n">
         <v>45697</v>
       </c>
       <c r="B406" t="n">
@@ -12213,7 +12225,7 @@
       </c>
     </row>
     <row r="407">
-      <c r="A407" s="1" t="n">
+      <c r="A407" s="2" t="n">
         <v>45698</v>
       </c>
       <c r="B407" t="n">
@@ -12242,7 +12254,7 @@
       </c>
     </row>
     <row r="408">
-      <c r="A408" s="1" t="n">
+      <c r="A408" s="2" t="n">
         <v>45699</v>
       </c>
       <c r="B408" t="n">
@@ -12271,7 +12283,7 @@
       </c>
     </row>
     <row r="409">
-      <c r="A409" s="1" t="n">
+      <c r="A409" s="2" t="n">
         <v>45700</v>
       </c>
       <c r="B409" t="n">
@@ -12300,7 +12312,7 @@
       </c>
     </row>
     <row r="410">
-      <c r="A410" s="1" t="n">
+      <c r="A410" s="2" t="n">
         <v>45701</v>
       </c>
       <c r="B410" t="n">
@@ -12329,7 +12341,7 @@
       </c>
     </row>
     <row r="411">
-      <c r="A411" s="1" t="n">
+      <c r="A411" s="2" t="n">
         <v>45702</v>
       </c>
       <c r="B411" t="n">
@@ -12358,7 +12370,7 @@
       </c>
     </row>
     <row r="412">
-      <c r="A412" s="1" t="n">
+      <c r="A412" s="2" t="n">
         <v>45703</v>
       </c>
       <c r="B412" t="n">
@@ -12387,7 +12399,7 @@
       </c>
     </row>
     <row r="413">
-      <c r="A413" s="1" t="n">
+      <c r="A413" s="2" t="n">
         <v>45704</v>
       </c>
       <c r="B413" t="n">
@@ -12416,7 +12428,7 @@
       </c>
     </row>
     <row r="414">
-      <c r="A414" s="1" t="n">
+      <c r="A414" s="2" t="n">
         <v>45705</v>
       </c>
       <c r="B414" t="n">
@@ -12445,7 +12457,7 @@
       </c>
     </row>
     <row r="415">
-      <c r="A415" s="1" t="n">
+      <c r="A415" s="2" t="n">
         <v>45706</v>
       </c>
       <c r="B415" t="n">
@@ -12474,7 +12486,7 @@
       </c>
     </row>
     <row r="416">
-      <c r="A416" s="1" t="n">
+      <c r="A416" s="2" t="n">
         <v>45707</v>
       </c>
       <c r="B416" t="n">
@@ -12503,7 +12515,7 @@
       </c>
     </row>
     <row r="417">
-      <c r="A417" s="1" t="n">
+      <c r="A417" s="2" t="n">
         <v>45708</v>
       </c>
       <c r="B417" t="n">
@@ -12532,7 +12544,7 @@
       </c>
     </row>
     <row r="418">
-      <c r="A418" s="1" t="n">
+      <c r="A418" s="2" t="n">
         <v>45709</v>
       </c>
       <c r="B418" t="n">
@@ -12561,7 +12573,7 @@
       </c>
     </row>
     <row r="419">
-      <c r="A419" s="1" t="n">
+      <c r="A419" s="2" t="n">
         <v>45710</v>
       </c>
       <c r="B419" t="n">
@@ -12590,7 +12602,7 @@
       </c>
     </row>
     <row r="420">
-      <c r="A420" s="1" t="n">
+      <c r="A420" s="2" t="n">
         <v>45711</v>
       </c>
       <c r="B420" t="n">
@@ -12619,7 +12631,7 @@
       </c>
     </row>
     <row r="421">
-      <c r="A421" s="1" t="n">
+      <c r="A421" s="2" t="n">
         <v>45712</v>
       </c>
       <c r="B421" t="n">
@@ -12648,7 +12660,7 @@
       </c>
     </row>
     <row r="422">
-      <c r="A422" s="1" t="n">
+      <c r="A422" s="2" t="n">
         <v>45713</v>
       </c>
       <c r="B422" t="n">
@@ -12677,7 +12689,7 @@
       </c>
     </row>
     <row r="423">
-      <c r="A423" s="1" t="n">
+      <c r="A423" s="2" t="n">
         <v>45714</v>
       </c>
       <c r="B423" t="n">
@@ -12706,7 +12718,7 @@
       </c>
     </row>
     <row r="424">
-      <c r="A424" s="1" t="n">
+      <c r="A424" s="2" t="n">
         <v>45715</v>
       </c>
       <c r="B424" t="n">
@@ -12735,7 +12747,7 @@
       </c>
     </row>
     <row r="425">
-      <c r="A425" s="1" t="n">
+      <c r="A425" s="2" t="n">
         <v>45716</v>
       </c>
       <c r="B425" t="n">
@@ -12764,7 +12776,7 @@
       </c>
     </row>
     <row r="426">
-      <c r="A426" s="1" t="n">
+      <c r="A426" s="2" t="n">
         <v>45717</v>
       </c>
       <c r="B426" t="n">
@@ -12793,7 +12805,7 @@
       </c>
     </row>
     <row r="427">
-      <c r="A427" s="1" t="n">
+      <c r="A427" s="2" t="n">
         <v>45718</v>
       </c>
       <c r="B427" t="n">
@@ -12822,7 +12834,7 @@
       </c>
     </row>
     <row r="428">
-      <c r="A428" s="1" t="n">
+      <c r="A428" s="2" t="n">
         <v>45719</v>
       </c>
       <c r="B428" t="n">
@@ -12851,7 +12863,7 @@
       </c>
     </row>
     <row r="429">
-      <c r="A429" s="1" t="n">
+      <c r="A429" s="2" t="n">
         <v>45720</v>
       </c>
       <c r="B429" t="n">
@@ -12880,7 +12892,7 @@
       </c>
     </row>
     <row r="430">
-      <c r="A430" s="1" t="n">
+      <c r="A430" s="2" t="n">
         <v>45721</v>
       </c>
       <c r="B430" t="n">
@@ -12909,7 +12921,7 @@
       </c>
     </row>
     <row r="431">
-      <c r="A431" s="1" t="n">
+      <c r="A431" s="2" t="n">
         <v>45722</v>
       </c>
       <c r="B431" t="n">
@@ -12938,7 +12950,7 @@
       </c>
     </row>
     <row r="432">
-      <c r="A432" s="1" t="n">
+      <c r="A432" s="2" t="n">
         <v>45723</v>
       </c>
       <c r="B432" t="n">
@@ -12967,7 +12979,7 @@
       </c>
     </row>
     <row r="433">
-      <c r="A433" s="1" t="n">
+      <c r="A433" s="2" t="n">
         <v>45724</v>
       </c>
       <c r="B433" t="n">
@@ -12996,7 +13008,7 @@
       </c>
     </row>
     <row r="434">
-      <c r="A434" s="1" t="n">
+      <c r="A434" s="2" t="n">
         <v>45725</v>
       </c>
       <c r="B434" t="n">
@@ -13025,7 +13037,7 @@
       </c>
     </row>
     <row r="435">
-      <c r="A435" s="1" t="n">
+      <c r="A435" s="2" t="n">
         <v>45726</v>
       </c>
       <c r="B435" t="n">
@@ -13054,7 +13066,7 @@
       </c>
     </row>
     <row r="436">
-      <c r="A436" s="1" t="n">
+      <c r="A436" s="2" t="n">
         <v>45727</v>
       </c>
       <c r="B436" t="n">
@@ -13083,7 +13095,7 @@
       </c>
     </row>
     <row r="437">
-      <c r="A437" s="1" t="n">
+      <c r="A437" s="2" t="n">
         <v>45728</v>
       </c>
       <c r="B437" t="n">
@@ -13112,7 +13124,7 @@
       </c>
     </row>
     <row r="438">
-      <c r="A438" s="1" t="n">
+      <c r="A438" s="2" t="n">
         <v>45729</v>
       </c>
       <c r="B438" t="n">
@@ -13141,7 +13153,7 @@
       </c>
     </row>
     <row r="439">
-      <c r="A439" s="1" t="n">
+      <c r="A439" s="2" t="n">
         <v>45730</v>
       </c>
       <c r="B439" t="n">
@@ -13170,7 +13182,7 @@
       </c>
     </row>
     <row r="440">
-      <c r="A440" s="1" t="n">
+      <c r="A440" s="2" t="n">
         <v>45731</v>
       </c>
       <c r="B440" t="n">
@@ -13199,7 +13211,7 @@
       </c>
     </row>
     <row r="441">
-      <c r="A441" s="1" t="n">
+      <c r="A441" s="2" t="n">
         <v>45732</v>
       </c>
       <c r="B441" t="n">
@@ -13228,7 +13240,7 @@
       </c>
     </row>
     <row r="442">
-      <c r="A442" s="1" t="n">
+      <c r="A442" s="2" t="n">
         <v>45733</v>
       </c>
       <c r="B442" t="n">
@@ -13257,7 +13269,7 @@
       </c>
     </row>
     <row r="443">
-      <c r="A443" s="1" t="n">
+      <c r="A443" s="2" t="n">
         <v>45734</v>
       </c>
       <c r="B443" t="n">
@@ -13286,7 +13298,7 @@
       </c>
     </row>
     <row r="444">
-      <c r="A444" s="1" t="n">
+      <c r="A444" s="2" t="n">
         <v>45735</v>
       </c>
       <c r="B444" t="n">
@@ -13315,7 +13327,7 @@
       </c>
     </row>
     <row r="445">
-      <c r="A445" s="1" t="n">
+      <c r="A445" s="2" t="n">
         <v>45736</v>
       </c>
       <c r="B445" t="n">
@@ -13344,7 +13356,7 @@
       </c>
     </row>
     <row r="446">
-      <c r="A446" s="1" t="n">
+      <c r="A446" s="2" t="n">
         <v>45737</v>
       </c>
       <c r="B446" t="n">
@@ -13373,7 +13385,7 @@
       </c>
     </row>
     <row r="447">
-      <c r="A447" s="1" t="n">
+      <c r="A447" s="2" t="n">
         <v>45738</v>
       </c>
       <c r="B447" t="n">
@@ -13402,7 +13414,7 @@
       </c>
     </row>
     <row r="448">
-      <c r="A448" s="1" t="n">
+      <c r="A448" s="2" t="n">
         <v>45739</v>
       </c>
       <c r="B448" t="n">
@@ -13431,7 +13443,7 @@
       </c>
     </row>
     <row r="449">
-      <c r="A449" s="1" t="n">
+      <c r="A449" s="2" t="n">
         <v>45740</v>
       </c>
       <c r="B449" t="n">
@@ -13460,7 +13472,7 @@
       </c>
     </row>
     <row r="450">
-      <c r="A450" s="1" t="n">
+      <c r="A450" s="2" t="n">
         <v>45741</v>
       </c>
       <c r="B450" t="n">
@@ -13489,7 +13501,7 @@
       </c>
     </row>
     <row r="451">
-      <c r="A451" s="1" t="n">
+      <c r="A451" s="2" t="n">
         <v>45742</v>
       </c>
       <c r="B451" t="n">
@@ -13518,7 +13530,7 @@
       </c>
     </row>
     <row r="452">
-      <c r="A452" s="1" t="n">
+      <c r="A452" s="2" t="n">
         <v>45743</v>
       </c>
       <c r="B452" t="n">
@@ -13547,7 +13559,7 @@
       </c>
     </row>
     <row r="453">
-      <c r="A453" s="1" t="n">
+      <c r="A453" s="2" t="n">
         <v>45744</v>
       </c>
       <c r="B453" t="n">
@@ -13576,7 +13588,7 @@
       </c>
     </row>
     <row r="454">
-      <c r="A454" s="1" t="n">
+      <c r="A454" s="2" t="n">
         <v>45745</v>
       </c>
       <c r="B454" t="n">
@@ -13605,7 +13617,7 @@
       </c>
     </row>
     <row r="455">
-      <c r="A455" s="1" t="n">
+      <c r="A455" s="2" t="n">
         <v>45746</v>
       </c>
       <c r="B455" t="n">
@@ -13634,7 +13646,7 @@
       </c>
     </row>
     <row r="456">
-      <c r="A456" s="1" t="n">
+      <c r="A456" s="2" t="n">
         <v>45747</v>
       </c>
       <c r="B456" t="n">
@@ -13663,7 +13675,7 @@
       </c>
     </row>
     <row r="457">
-      <c r="A457" s="1" t="n">
+      <c r="A457" s="2" t="n">
         <v>45748</v>
       </c>
       <c r="B457" t="n">
@@ -13692,7 +13704,7 @@
       </c>
     </row>
     <row r="458">
-      <c r="A458" s="1" t="n">
+      <c r="A458" s="2" t="n">
         <v>45749</v>
       </c>
       <c r="B458" t="n">
@@ -13721,7 +13733,7 @@
       </c>
     </row>
     <row r="459">
-      <c r="A459" s="1" t="n">
+      <c r="A459" s="2" t="n">
         <v>45750</v>
       </c>
       <c r="B459" t="n">
@@ -13750,7 +13762,7 @@
       </c>
     </row>
     <row r="460">
-      <c r="A460" s="1" t="n">
+      <c r="A460" s="2" t="n">
         <v>45751</v>
       </c>
       <c r="B460" t="n">
@@ -13779,7 +13791,7 @@
       </c>
     </row>
     <row r="461">
-      <c r="A461" s="1" t="n">
+      <c r="A461" s="2" t="n">
         <v>45752</v>
       </c>
       <c r="B461" t="n">
@@ -13808,7 +13820,7 @@
       </c>
     </row>
     <row r="462">
-      <c r="A462" s="1" t="n">
+      <c r="A462" s="2" t="n">
         <v>45753</v>
       </c>
       <c r="B462" t="n">
@@ -13837,7 +13849,7 @@
       </c>
     </row>
     <row r="463">
-      <c r="A463" s="1" t="n">
+      <c r="A463" s="2" t="n">
         <v>45754</v>
       </c>
       <c r="B463" t="n">
@@ -13866,7 +13878,7 @@
       </c>
     </row>
     <row r="464">
-      <c r="A464" s="1" t="n">
+      <c r="A464" s="2" t="n">
         <v>45755</v>
       </c>
       <c r="B464" t="n">
@@ -13895,7 +13907,7 @@
       </c>
     </row>
     <row r="465">
-      <c r="A465" s="1" t="n">
+      <c r="A465" s="2" t="n">
         <v>45756</v>
       </c>
       <c r="B465" t="n">
@@ -13924,7 +13936,7 @@
       </c>
     </row>
     <row r="466">
-      <c r="A466" s="1" t="n">
+      <c r="A466" s="2" t="n">
         <v>45757</v>
       </c>
       <c r="B466" t="n">
@@ -13953,7 +13965,7 @@
       </c>
     </row>
     <row r="467">
-      <c r="A467" s="1" t="n">
+      <c r="A467" s="2" t="n">
         <v>45758</v>
       </c>
       <c r="B467" t="n">
@@ -13982,7 +13994,7 @@
       </c>
     </row>
     <row r="468">
-      <c r="A468" s="1" t="n">
+      <c r="A468" s="2" t="n">
         <v>45759</v>
       </c>
       <c r="B468" t="n">
@@ -14011,7 +14023,7 @@
       </c>
     </row>
     <row r="469">
-      <c r="A469" s="1" t="n">
+      <c r="A469" s="2" t="n">
         <v>45760</v>
       </c>
       <c r="B469" t="n">
@@ -14040,7 +14052,7 @@
       </c>
     </row>
     <row r="470">
-      <c r="A470" s="1" t="n">
+      <c r="A470" s="2" t="n">
         <v>45761</v>
       </c>
       <c r="B470" t="n">
@@ -14069,7 +14081,7 @@
       </c>
     </row>
     <row r="471">
-      <c r="A471" s="1" t="n">
+      <c r="A471" s="2" t="n">
         <v>45762</v>
       </c>
       <c r="B471" t="n">
@@ -14098,7 +14110,7 @@
       </c>
     </row>
     <row r="472">
-      <c r="A472" s="1" t="n">
+      <c r="A472" s="2" t="n">
         <v>45763</v>
       </c>
       <c r="B472" t="n">
@@ -14127,7 +14139,7 @@
       </c>
     </row>
     <row r="473">
-      <c r="A473" s="1" t="n">
+      <c r="A473" s="2" t="n">
         <v>45764</v>
       </c>
       <c r="B473" t="n">
@@ -14156,7 +14168,7 @@
       </c>
     </row>
     <row r="474">
-      <c r="A474" s="1" t="n">
+      <c r="A474" s="2" t="n">
         <v>45765</v>
       </c>
       <c r="B474" t="n">
@@ -14185,7 +14197,7 @@
       </c>
     </row>
     <row r="475">
-      <c r="A475" s="1" t="n">
+      <c r="A475" s="2" t="n">
         <v>45766</v>
       </c>
       <c r="B475" t="n">
@@ -14214,7 +14226,7 @@
       </c>
     </row>
     <row r="476">
-      <c r="A476" s="1" t="n">
+      <c r="A476" s="2" t="n">
         <v>45767</v>
       </c>
       <c r="B476" t="n">
@@ -14243,7 +14255,7 @@
       </c>
     </row>
     <row r="477">
-      <c r="A477" s="1" t="n">
+      <c r="A477" s="2" t="n">
         <v>45768</v>
       </c>
       <c r="B477" t="n">
@@ -14272,7 +14284,7 @@
       </c>
     </row>
     <row r="478">
-      <c r="A478" s="1" t="n">
+      <c r="A478" s="2" t="n">
         <v>45769</v>
       </c>
       <c r="B478" t="n">
@@ -14301,7 +14313,7 @@
       </c>
     </row>
     <row r="479">
-      <c r="A479" s="1" t="n">
+      <c r="A479" s="2" t="n">
         <v>45770</v>
       </c>
       <c r="B479" t="n">
@@ -14330,7 +14342,7 @@
       </c>
     </row>
     <row r="480">
-      <c r="A480" s="1" t="n">
+      <c r="A480" s="2" t="n">
         <v>45771</v>
       </c>
       <c r="B480" t="n">
@@ -14359,7 +14371,7 @@
       </c>
     </row>
     <row r="481">
-      <c r="A481" s="1" t="n">
+      <c r="A481" s="2" t="n">
         <v>45772</v>
       </c>
       <c r="B481" t="n">
@@ -14388,7 +14400,7 @@
       </c>
     </row>
     <row r="482">
-      <c r="A482" s="1" t="n">
+      <c r="A482" s="2" t="n">
         <v>45773</v>
       </c>
       <c r="B482" t="n">
@@ -14417,7 +14429,7 @@
       </c>
     </row>
     <row r="483">
-      <c r="A483" s="1" t="n">
+      <c r="A483" s="2" t="n">
         <v>45774</v>
       </c>
       <c r="B483" t="n">
@@ -14446,7 +14458,7 @@
       </c>
     </row>
     <row r="484">
-      <c r="A484" s="1" t="n">
+      <c r="A484" s="2" t="n">
         <v>45775</v>
       </c>
       <c r="B484" t="n">
@@ -14475,7 +14487,7 @@
       </c>
     </row>
     <row r="485">
-      <c r="A485" s="1" t="n">
+      <c r="A485" s="2" t="n">
         <v>45776</v>
       </c>
       <c r="B485" t="n">
@@ -14504,7 +14516,7 @@
       </c>
     </row>
     <row r="486">
-      <c r="A486" s="1" t="n">
+      <c r="A486" s="2" t="n">
         <v>45777</v>
       </c>
       <c r="B486" t="n">
@@ -14533,7 +14545,7 @@
       </c>
     </row>
     <row r="487">
-      <c r="A487" s="1" t="n">
+      <c r="A487" s="2" t="n">
         <v>45778</v>
       </c>
       <c r="B487" t="n">
@@ -14562,7 +14574,7 @@
       </c>
     </row>
     <row r="488">
-      <c r="A488" s="1" t="n">
+      <c r="A488" s="2" t="n">
         <v>45779</v>
       </c>
       <c r="B488" t="n">
@@ -14591,7 +14603,7 @@
       </c>
     </row>
     <row r="489">
-      <c r="A489" s="1" t="n">
+      <c r="A489" s="2" t="n">
         <v>45780</v>
       </c>
       <c r="B489" t="n">
@@ -14620,7 +14632,7 @@
       </c>
     </row>
     <row r="490">
-      <c r="A490" s="1" t="n">
+      <c r="A490" s="2" t="n">
         <v>45781</v>
       </c>
       <c r="B490" t="n">
@@ -14649,7 +14661,7 @@
       </c>
     </row>
     <row r="491">
-      <c r="A491" s="1" t="n">
+      <c r="A491" s="2" t="n">
         <v>45782</v>
       </c>
       <c r="B491" t="n">
@@ -14678,7 +14690,7 @@
       </c>
     </row>
     <row r="492">
-      <c r="A492" s="1" t="n">
+      <c r="A492" s="2" t="n">
         <v>45783</v>
       </c>
       <c r="B492" t="n">
@@ -14707,7 +14719,7 @@
       </c>
     </row>
     <row r="493">
-      <c r="A493" s="1" t="n">
+      <c r="A493" s="2" t="n">
         <v>45784</v>
       </c>
       <c r="B493" t="n">
@@ -14736,7 +14748,7 @@
       </c>
     </row>
     <row r="494">
-      <c r="A494" s="1" t="n">
+      <c r="A494" s="2" t="n">
         <v>45785</v>
       </c>
       <c r="B494" t="n">
@@ -14765,7 +14777,7 @@
       </c>
     </row>
     <row r="495">
-      <c r="A495" s="1" t="n">
+      <c r="A495" s="2" t="n">
         <v>45786</v>
       </c>
       <c r="B495" t="n">
@@ -14794,7 +14806,7 @@
       </c>
     </row>
     <row r="496">
-      <c r="A496" s="1" t="n">
+      <c r="A496" s="2" t="n">
         <v>45787</v>
       </c>
       <c r="B496" t="n">
@@ -14823,7 +14835,7 @@
       </c>
     </row>
     <row r="497">
-      <c r="A497" s="1" t="n">
+      <c r="A497" s="2" t="n">
         <v>45788</v>
       </c>
       <c r="B497" t="n">
@@ -14852,7 +14864,7 @@
       </c>
     </row>
     <row r="498">
-      <c r="A498" s="1" t="n">
+      <c r="A498" s="2" t="n">
         <v>45789</v>
       </c>
       <c r="B498" t="n">
@@ -14881,7 +14893,7 @@
       </c>
     </row>
     <row r="499">
-      <c r="A499" s="1" t="n">
+      <c r="A499" s="2" t="n">
         <v>45790</v>
       </c>
       <c r="B499" t="n">
@@ -14910,7 +14922,7 @@
       </c>
     </row>
     <row r="500">
-      <c r="A500" s="1" t="n">
+      <c r="A500" s="2" t="n">
         <v>45791</v>
       </c>
       <c r="B500" t="n">
@@ -14939,7 +14951,7 @@
       </c>
     </row>
     <row r="501">
-      <c r="A501" s="1" t="n">
+      <c r="A501" s="2" t="n">
         <v>45792</v>
       </c>
       <c r="B501" t="n">
@@ -14968,7 +14980,7 @@
       </c>
     </row>
     <row r="502">
-      <c r="A502" s="1" t="n">
+      <c r="A502" s="2" t="n">
         <v>45793</v>
       </c>
       <c r="B502" t="n">
@@ -14997,7 +15009,7 @@
       </c>
     </row>
     <row r="503">
-      <c r="A503" s="1" t="n">
+      <c r="A503" s="2" t="n">
         <v>45794</v>
       </c>
       <c r="B503" t="n">
@@ -15026,7 +15038,7 @@
       </c>
     </row>
     <row r="504">
-      <c r="A504" s="1" t="n">
+      <c r="A504" s="2" t="n">
         <v>45795</v>
       </c>
       <c r="B504" t="n">
@@ -15055,7 +15067,7 @@
       </c>
     </row>
     <row r="505">
-      <c r="A505" s="1" t="n">
+      <c r="A505" s="2" t="n">
         <v>45796</v>
       </c>
       <c r="B505" t="n">
@@ -15084,7 +15096,7 @@
       </c>
     </row>
     <row r="506">
-      <c r="A506" s="1" t="n">
+      <c r="A506" s="2" t="n">
         <v>45797</v>
       </c>
       <c r="B506" t="n">
@@ -15113,7 +15125,7 @@
       </c>
     </row>
     <row r="507">
-      <c r="A507" s="1" t="n">
+      <c r="A507" s="2" t="n">
         <v>45798</v>
       </c>
       <c r="B507" t="n">
@@ -15142,7 +15154,7 @@
       </c>
     </row>
     <row r="508">
-      <c r="A508" s="1" t="n">
+      <c r="A508" s="2" t="n">
         <v>45799</v>
       </c>
       <c r="B508" t="n">
@@ -15171,7 +15183,7 @@
       </c>
     </row>
     <row r="509">
-      <c r="A509" s="1" t="n">
+      <c r="A509" s="2" t="n">
         <v>45800</v>
       </c>
       <c r="B509" t="n">
@@ -15200,7 +15212,7 @@
       </c>
     </row>
     <row r="510">
-      <c r="A510" s="1" t="n">
+      <c r="A510" s="2" t="n">
         <v>45801</v>
       </c>
       <c r="B510" t="n">
@@ -15229,7 +15241,7 @@
       </c>
     </row>
     <row r="511">
-      <c r="A511" s="1" t="n">
+      <c r="A511" s="2" t="n">
         <v>45802</v>
       </c>
       <c r="B511" t="n">
@@ -15258,7 +15270,7 @@
       </c>
     </row>
     <row r="512">
-      <c r="A512" s="1" t="n">
+      <c r="A512" s="2" t="n">
         <v>45803</v>
       </c>
       <c r="B512" t="n">
@@ -15287,7 +15299,7 @@
       </c>
     </row>
     <row r="513">
-      <c r="A513" s="1" t="n">
+      <c r="A513" s="2" t="n">
         <v>45804</v>
       </c>
       <c r="B513" t="n">
@@ -15316,7 +15328,7 @@
       </c>
     </row>
     <row r="514">
-      <c r="A514" s="1" t="n">
+      <c r="A514" s="2" t="n">
         <v>45805</v>
       </c>
       <c r="B514" t="n">
@@ -15345,7 +15357,7 @@
       </c>
     </row>
     <row r="515">
-      <c r="A515" s="1" t="n">
+      <c r="A515" s="2" t="n">
         <v>45806</v>
       </c>
       <c r="B515" t="n">
@@ -15374,7 +15386,7 @@
       </c>
     </row>
     <row r="516">
-      <c r="A516" s="1" t="n">
+      <c r="A516" s="2" t="n">
         <v>45807</v>
       </c>
       <c r="B516" t="n">
@@ -15403,7 +15415,7 @@
       </c>
     </row>
     <row r="517">
-      <c r="A517" s="1" t="n">
+      <c r="A517" s="2" t="n">
         <v>45808</v>
       </c>
       <c r="B517" t="n">
@@ -15432,7 +15444,7 @@
       </c>
     </row>
     <row r="518">
-      <c r="A518" s="1" t="n">
+      <c r="A518" s="2" t="n">
         <v>45809</v>
       </c>
       <c r="B518" t="n">
@@ -15461,7 +15473,7 @@
       </c>
     </row>
     <row r="519">
-      <c r="A519" s="1" t="n">
+      <c r="A519" s="2" t="n">
         <v>45810</v>
       </c>
       <c r="B519" t="n">
@@ -15490,7 +15502,7 @@
       </c>
     </row>
     <row r="520">
-      <c r="A520" s="1" t="n">
+      <c r="A520" s="2" t="n">
         <v>45811</v>
       </c>
       <c r="B520" t="n">
@@ -15519,7 +15531,7 @@
       </c>
     </row>
     <row r="521">
-      <c r="A521" s="1" t="n">
+      <c r="A521" s="2" t="n">
         <v>45812</v>
       </c>
       <c r="B521" t="n">
@@ -15548,7 +15560,7 @@
       </c>
     </row>
     <row r="522">
-      <c r="A522" s="1" t="n">
+      <c r="A522" s="2" t="n">
         <v>45813</v>
       </c>
       <c r="B522" t="n">
@@ -15577,7 +15589,7 @@
       </c>
     </row>
     <row r="523">
-      <c r="A523" s="1" t="n">
+      <c r="A523" s="2" t="n">
         <v>45814</v>
       </c>
       <c r="B523" t="n">
@@ -15606,7 +15618,7 @@
       </c>
     </row>
     <row r="524">
-      <c r="A524" s="1" t="n">
+      <c r="A524" s="2" t="n">
         <v>45815</v>
       </c>
       <c r="B524" t="n">
@@ -15635,7 +15647,7 @@
       </c>
     </row>
     <row r="525">
-      <c r="A525" s="1" t="n">
+      <c r="A525" s="2" t="n">
         <v>45816</v>
       </c>
       <c r="B525" t="n">
@@ -15664,7 +15676,7 @@
       </c>
     </row>
     <row r="526">
-      <c r="A526" s="1" t="n">
+      <c r="A526" s="2" t="n">
         <v>45817</v>
       </c>
       <c r="B526" t="n">
@@ -15693,7 +15705,7 @@
       </c>
     </row>
     <row r="527">
-      <c r="A527" s="1" t="n">
+      <c r="A527" s="2" t="n">
         <v>45818</v>
       </c>
       <c r="B527" t="n">
@@ -15722,7 +15734,7 @@
       </c>
     </row>
     <row r="528">
-      <c r="A528" s="1" t="n">
+      <c r="A528" s="2" t="n">
         <v>45819</v>
       </c>
       <c r="B528" t="n">
@@ -15751,7 +15763,7 @@
       </c>
     </row>
     <row r="529">
-      <c r="A529" s="1" t="n">
+      <c r="A529" s="2" t="n">
         <v>45820</v>
       </c>
       <c r="B529" t="n">
@@ -15780,7 +15792,7 @@
       </c>
     </row>
     <row r="530">
-      <c r="A530" s="1" t="n">
+      <c r="A530" s="2" t="n">
         <v>45821</v>
       </c>
       <c r="B530" t="n">
@@ -15809,7 +15821,7 @@
       </c>
     </row>
     <row r="531">
-      <c r="A531" s="1" t="n">
+      <c r="A531" s="2" t="n">
         <v>45822</v>
       </c>
       <c r="B531" t="n">
@@ -15838,7 +15850,7 @@
       </c>
     </row>
     <row r="532">
-      <c r="A532" s="1" t="n">
+      <c r="A532" s="2" t="n">
         <v>45823</v>
       </c>
       <c r="B532" t="n">
@@ -15867,7 +15879,7 @@
       </c>
     </row>
     <row r="533">
-      <c r="A533" s="1" t="n">
+      <c r="A533" s="2" t="n">
         <v>45824</v>
       </c>
       <c r="B533" t="n">
@@ -15896,7 +15908,7 @@
       </c>
     </row>
     <row r="534">
-      <c r="A534" s="1" t="n">
+      <c r="A534" s="2" t="n">
         <v>45825</v>
       </c>
       <c r="B534" t="n">
@@ -15925,7 +15937,7 @@
       </c>
     </row>
     <row r="535">
-      <c r="A535" s="1" t="n">
+      <c r="A535" s="2" t="n">
         <v>45826</v>
       </c>
       <c r="B535" t="n">
@@ -15954,7 +15966,7 @@
       </c>
     </row>
     <row r="536">
-      <c r="A536" s="1" t="n">
+      <c r="A536" s="2" t="n">
         <v>45827</v>
       </c>
       <c r="B536" t="n">
@@ -15983,7 +15995,7 @@
       </c>
     </row>
     <row r="537">
-      <c r="A537" s="1" t="n">
+      <c r="A537" s="2" t="n">
         <v>45828</v>
       </c>
       <c r="B537" t="n">
@@ -16012,7 +16024,7 @@
       </c>
     </row>
     <row r="538">
-      <c r="A538" s="1" t="n">
+      <c r="A538" s="2" t="n">
         <v>45829</v>
       </c>
       <c r="B538" t="n">
@@ -16041,7 +16053,7 @@
       </c>
     </row>
     <row r="539">
-      <c r="A539" s="1" t="n">
+      <c r="A539" s="2" t="n">
         <v>45830</v>
       </c>
       <c r="B539" t="n">
@@ -16070,7 +16082,7 @@
       </c>
     </row>
     <row r="540">
-      <c r="A540" s="1" t="n">
+      <c r="A540" s="2" t="n">
         <v>45831</v>
       </c>
       <c r="B540" t="n">
@@ -16099,7 +16111,7 @@
       </c>
     </row>
     <row r="541">
-      <c r="A541" s="1" t="n">
+      <c r="A541" s="2" t="n">
         <v>45832</v>
       </c>
       <c r="B541" t="n">
@@ -16128,7 +16140,7 @@
       </c>
     </row>
     <row r="542">
-      <c r="A542" s="1" t="n">
+      <c r="A542" s="2" t="n">
         <v>45833</v>
       </c>
       <c r="B542" t="n">
@@ -16157,7 +16169,7 @@
       </c>
     </row>
     <row r="543">
-      <c r="A543" s="1" t="n">
+      <c r="A543" s="2" t="n">
         <v>45834</v>
       </c>
       <c r="B543" t="n">
@@ -16186,7 +16198,7 @@
       </c>
     </row>
     <row r="544">
-      <c r="A544" s="1" t="n">
+      <c r="A544" s="2" t="n">
         <v>45835</v>
       </c>
       <c r="B544" t="n">
@@ -16215,7 +16227,7 @@
       </c>
     </row>
     <row r="545">
-      <c r="A545" s="1" t="n">
+      <c r="A545" s="2" t="n">
         <v>45836</v>
       </c>
       <c r="B545" t="n">
@@ -16244,7 +16256,7 @@
       </c>
     </row>
     <row r="546">
-      <c r="A546" s="1" t="n">
+      <c r="A546" s="2" t="n">
         <v>45837</v>
       </c>
       <c r="B546" t="n">
@@ -16273,7 +16285,7 @@
       </c>
     </row>
     <row r="547">
-      <c r="A547" s="1" t="n">
+      <c r="A547" s="2" t="n">
         <v>45838</v>
       </c>
       <c r="B547" t="n">
@@ -16302,7 +16314,7 @@
       </c>
     </row>
     <row r="548">
-      <c r="A548" s="1" t="n">
+      <c r="A548" s="2" t="n">
         <v>45839</v>
       </c>
       <c r="B548" t="n">
@@ -16331,7 +16343,7 @@
       </c>
     </row>
     <row r="549">
-      <c r="A549" s="1" t="n">
+      <c r="A549" s="2" t="n">
         <v>45840</v>
       </c>
       <c r="B549" t="n">
@@ -16360,7 +16372,7 @@
       </c>
     </row>
     <row r="550">
-      <c r="A550" s="1" t="n">
+      <c r="A550" s="2" t="n">
         <v>45841</v>
       </c>
       <c r="B550" t="n">
@@ -16389,7 +16401,7 @@
       </c>
     </row>
     <row r="551">
-      <c r="A551" s="1" t="n">
+      <c r="A551" s="2" t="n">
         <v>45842</v>
       </c>
       <c r="B551" t="n">
@@ -16418,7 +16430,7 @@
       </c>
     </row>
     <row r="552">
-      <c r="A552" s="1" t="n">
+      <c r="A552" s="2" t="n">
         <v>45843</v>
       </c>
       <c r="B552" t="n">
@@ -16447,7 +16459,7 @@
       </c>
     </row>
     <row r="553">
-      <c r="A553" s="1" t="n">
+      <c r="A553" s="2" t="n">
         <v>45844</v>
       </c>
       <c r="B553" t="n">
@@ -16476,7 +16488,7 @@
       </c>
     </row>
     <row r="554">
-      <c r="A554" s="1" t="n">
+      <c r="A554" s="2" t="n">
         <v>45845</v>
       </c>
       <c r="B554" t="n">
@@ -16505,7 +16517,7 @@
       </c>
     </row>
     <row r="555">
-      <c r="A555" s="1" t="n">
+      <c r="A555" s="2" t="n">
         <v>45846</v>
       </c>
       <c r="B555" t="n">
@@ -16534,7 +16546,7 @@
       </c>
     </row>
     <row r="556">
-      <c r="A556" s="1" t="n">
+      <c r="A556" s="2" t="n">
         <v>45847</v>
       </c>
       <c r="B556" t="n">
@@ -16563,7 +16575,7 @@
       </c>
     </row>
     <row r="557">
-      <c r="A557" s="1" t="n">
+      <c r="A557" s="2" t="n">
         <v>45848</v>
       </c>
       <c r="B557" t="n">
@@ -16592,7 +16604,7 @@
       </c>
     </row>
     <row r="558">
-      <c r="A558" s="1" t="n">
+      <c r="A558" s="2" t="n">
         <v>45849</v>
       </c>
       <c r="B558" t="n">
@@ -16621,7 +16633,7 @@
       </c>
     </row>
     <row r="559">
-      <c r="A559" s="1" t="n">
+      <c r="A559" s="2" t="n">
         <v>45850</v>
       </c>
       <c r="B559" t="n">
@@ -16650,7 +16662,7 @@
       </c>
     </row>
     <row r="560">
-      <c r="A560" s="1" t="n">
+      <c r="A560" s="2" t="n">
         <v>45851</v>
       </c>
       <c r="B560" t="n">
@@ -16679,7 +16691,7 @@
       </c>
     </row>
     <row r="561">
-      <c r="A561" s="1" t="n">
+      <c r="A561" s="2" t="n">
         <v>45852</v>
       </c>
       <c r="B561" t="n">
@@ -16708,7 +16720,7 @@
       </c>
     </row>
     <row r="562">
-      <c r="A562" s="1" t="n">
+      <c r="A562" s="2" t="n">
         <v>45853</v>
       </c>
       <c r="B562" t="n">
@@ -16737,7 +16749,7 @@
       </c>
     </row>
     <row r="563">
-      <c r="A563" s="1" t="n">
+      <c r="A563" s="2" t="n">
         <v>45854</v>
       </c>
       <c r="B563" t="n">
@@ -16766,7 +16778,7 @@
       </c>
     </row>
     <row r="564">
-      <c r="A564" s="1" t="n">
+      <c r="A564" s="2" t="n">
         <v>45855</v>
       </c>
       <c r="B564" t="n">
@@ -16795,7 +16807,7 @@
       </c>
     </row>
     <row r="565">
-      <c r="A565" s="1" t="n">
+      <c r="A565" s="2" t="n">
         <v>45856</v>
       </c>
       <c r="B565" t="n">
@@ -16824,7 +16836,7 @@
       </c>
     </row>
     <row r="566">
-      <c r="A566" s="1" t="n">
+      <c r="A566" s="2" t="n">
         <v>45857</v>
       </c>
       <c r="B566" t="n">
@@ -16853,7 +16865,7 @@
       </c>
     </row>
     <row r="567">
-      <c r="A567" s="1" t="n">
+      <c r="A567" s="2" t="n">
         <v>45858</v>
       </c>
       <c r="B567" t="n">
@@ -16882,7 +16894,7 @@
       </c>
     </row>
     <row r="568">
-      <c r="A568" s="1" t="n">
+      <c r="A568" s="2" t="n">
         <v>45859</v>
       </c>
       <c r="B568" t="n">
@@ -16911,7 +16923,7 @@
       </c>
     </row>
     <row r="569">
-      <c r="A569" s="1" t="n">
+      <c r="A569" s="2" t="n">
         <v>45860</v>
       </c>
       <c r="B569" t="n">
@@ -16940,7 +16952,7 @@
       </c>
     </row>
     <row r="570">
-      <c r="A570" s="1" t="n">
+      <c r="A570" s="2" t="n">
         <v>45861</v>
       </c>
       <c r="B570" t="n">
@@ -16969,7 +16981,7 @@
       </c>
     </row>
     <row r="571">
-      <c r="A571" s="1" t="n">
+      <c r="A571" s="2" t="n">
         <v>45862</v>
       </c>
       <c r="B571" t="n">
@@ -16998,7 +17010,7 @@
       </c>
     </row>
     <row r="572">
-      <c r="A572" s="1" t="n">
+      <c r="A572" s="2" t="n">
         <v>45863</v>
       </c>
       <c r="B572" t="n">
@@ -17027,7 +17039,7 @@
       </c>
     </row>
     <row r="573">
-      <c r="A573" s="1" t="n">
+      <c r="A573" s="2" t="n">
         <v>45864</v>
       </c>
       <c r="B573" t="n">
@@ -17056,7 +17068,7 @@
       </c>
     </row>
     <row r="574">
-      <c r="A574" s="1" t="n">
+      <c r="A574" s="2" t="n">
         <v>45865</v>
       </c>
       <c r="B574" t="n">
@@ -17085,7 +17097,7 @@
       </c>
     </row>
     <row r="575">
-      <c r="A575" s="1" t="n">
+      <c r="A575" s="2" t="n">
         <v>45866</v>
       </c>
       <c r="B575" t="n">
@@ -17114,7 +17126,7 @@
       </c>
     </row>
     <row r="576">
-      <c r="A576" s="1" t="n">
+      <c r="A576" s="2" t="n">
         <v>45867</v>
       </c>
       <c r="B576" t="n">
@@ -17143,7 +17155,7 @@
       </c>
     </row>
     <row r="577">
-      <c r="A577" s="1" t="n">
+      <c r="A577" s="2" t="n">
         <v>45868</v>
       </c>
       <c r="B577" t="n">
@@ -17172,7 +17184,7 @@
       </c>
     </row>
     <row r="578">
-      <c r="A578" s="1" t="n">
+      <c r="A578" s="2" t="n">
         <v>45869</v>
       </c>
       <c r="B578" t="n">
@@ -17201,7 +17213,7 @@
       </c>
     </row>
     <row r="579">
-      <c r="A579" s="1" t="n">
+      <c r="A579" s="2" t="n">
         <v>45870</v>
       </c>
       <c r="B579" t="n">
@@ -17230,7 +17242,7 @@
       </c>
     </row>
     <row r="580">
-      <c r="A580" s="1" t="n">
+      <c r="A580" s="2" t="n">
         <v>45871</v>
       </c>
       <c r="B580" t="n">
@@ -17259,7 +17271,7 @@
       </c>
     </row>
     <row r="581">
-      <c r="A581" s="1" t="n">
+      <c r="A581" s="2" t="n">
         <v>45872</v>
       </c>
       <c r="B581" t="n">
@@ -17288,7 +17300,7 @@
       </c>
     </row>
     <row r="582">
-      <c r="A582" s="1" t="n">
+      <c r="A582" s="2" t="n">
         <v>45873</v>
       </c>
       <c r="B582" t="n">
@@ -17317,7 +17329,7 @@
       </c>
     </row>
     <row r="583">
-      <c r="A583" s="1" t="n">
+      <c r="A583" s="2" t="n">
         <v>45874</v>
       </c>
       <c r="B583" t="n">
@@ -17346,7 +17358,7 @@
       </c>
     </row>
     <row r="584">
-      <c r="A584" s="1" t="n">
+      <c r="A584" s="2" t="n">
         <v>45875</v>
       </c>
       <c r="B584" t="n">
@@ -17375,7 +17387,7 @@
       </c>
     </row>
     <row r="585">
-      <c r="A585" s="1" t="n">
+      <c r="A585" s="2" t="n">
         <v>45876</v>
       </c>
       <c r="B585" t="n">
@@ -17404,7 +17416,7 @@
       </c>
     </row>
     <row r="586">
-      <c r="A586" s="1" t="n">
+      <c r="A586" s="2" t="n">
         <v>45877</v>
       </c>
       <c r="B586" t="n">
@@ -17433,7 +17445,7 @@
       </c>
     </row>
     <row r="587">
-      <c r="A587" s="1" t="n">
+      <c r="A587" s="2" t="n">
         <v>45878</v>
       </c>
       <c r="B587" t="n">
@@ -17462,7 +17474,7 @@
       </c>
     </row>
     <row r="588">
-      <c r="A588" s="1" t="n">
+      <c r="A588" s="2" t="n">
         <v>45879</v>
       </c>
       <c r="B588" t="n">
@@ -17491,7 +17503,7 @@
       </c>
     </row>
     <row r="589">
-      <c r="A589" s="1" t="n">
+      <c r="A589" s="2" t="n">
         <v>45880</v>
       </c>
       <c r="B589" t="n">
@@ -17520,7 +17532,7 @@
       </c>
     </row>
     <row r="590">
-      <c r="A590" s="1" t="n">
+      <c r="A590" s="2" t="n">
         <v>45881</v>
       </c>
       <c r="B590" t="n">
@@ -17549,7 +17561,7 @@
       </c>
     </row>
     <row r="591">
-      <c r="A591" s="1" t="n">
+      <c r="A591" s="2" t="n">
         <v>45882</v>
       </c>
       <c r="B591" t="n">
@@ -17578,7 +17590,7 @@
       </c>
     </row>
     <row r="592">
-      <c r="A592" s="1" t="n">
+      <c r="A592" s="2" t="n">
         <v>45883</v>
       </c>
       <c r="B592" t="n">
@@ -17607,7 +17619,7 @@
       </c>
     </row>
     <row r="593">
-      <c r="A593" s="1" t="n">
+      <c r="A593" s="2" t="n">
         <v>45884</v>
       </c>
       <c r="B593" t="n">
@@ -17636,7 +17648,7 @@
       </c>
     </row>
     <row r="594">
-      <c r="A594" s="1" t="n">
+      <c r="A594" s="2" t="n">
         <v>45885</v>
       </c>
       <c r="B594" t="n">
@@ -17665,7 +17677,7 @@
       </c>
     </row>
     <row r="595">
-      <c r="A595" s="1" t="n">
+      <c r="A595" s="2" t="n">
         <v>45886</v>
       </c>
       <c r="B595" t="n">
@@ -17694,7 +17706,7 @@
       </c>
     </row>
     <row r="596">
-      <c r="A596" s="1" t="n">
+      <c r="A596" s="2" t="n">
         <v>45887</v>
       </c>
       <c r="B596" t="n">
@@ -17723,7 +17735,7 @@
       </c>
     </row>
     <row r="597">
-      <c r="A597" s="1" t="n">
+      <c r="A597" s="2" t="n">
         <v>45888</v>
       </c>
       <c r="B597" t="n">
@@ -17752,7 +17764,7 @@
       </c>
     </row>
     <row r="598">
-      <c r="A598" s="1" t="n">
+      <c r="A598" s="2" t="n">
         <v>45889</v>
       </c>
       <c r="B598" t="n">
@@ -17781,7 +17793,7 @@
       </c>
     </row>
     <row r="599">
-      <c r="A599" s="1" t="n">
+      <c r="A599" s="2" t="n">
         <v>45890</v>
       </c>
       <c r="B599" t="n">
@@ -17810,7 +17822,7 @@
       </c>
     </row>
     <row r="600">
-      <c r="A600" s="1" t="n">
+      <c r="A600" s="2" t="n">
         <v>45891</v>
       </c>
       <c r="B600" t="n">
@@ -17839,7 +17851,7 @@
       </c>
     </row>
     <row r="601">
-      <c r="A601" s="1" t="n">
+      <c r="A601" s="2" t="n">
         <v>45892</v>
       </c>
       <c r="B601" t="n">
@@ -17868,7 +17880,7 @@
       </c>
     </row>
     <row r="602">
-      <c r="A602" s="1" t="n">
+      <c r="A602" s="2" t="n">
         <v>45893</v>
       </c>
       <c r="B602" t="n">
@@ -17897,7 +17909,7 @@
       </c>
     </row>
     <row r="603">
-      <c r="A603" s="1" t="n">
+      <c r="A603" s="2" t="n">
         <v>45894</v>
       </c>
       <c r="B603" t="n">
@@ -17926,7 +17938,7 @@
       </c>
     </row>
     <row r="604">
-      <c r="A604" s="1" t="n">
+      <c r="A604" s="2" t="n">
         <v>45895</v>
       </c>
       <c r="B604" t="n">
@@ -17955,7 +17967,7 @@
       </c>
     </row>
     <row r="605">
-      <c r="A605" s="1" t="n">
+      <c r="A605" s="2" t="n">
         <v>45896</v>
       </c>
       <c r="B605" t="n">
@@ -17984,7 +17996,7 @@
       </c>
     </row>
     <row r="606">
-      <c r="A606" s="1" t="n">
+      <c r="A606" s="2" t="n">
         <v>45897</v>
       </c>
       <c r="B606" t="n">
@@ -18013,7 +18025,7 @@
       </c>
     </row>
     <row r="607">
-      <c r="A607" s="1" t="n">
+      <c r="A607" s="2" t="n">
         <v>45898</v>
       </c>
       <c r="B607" t="n">
@@ -18042,7 +18054,7 @@
       </c>
     </row>
     <row r="608">
-      <c r="A608" s="1" t="n">
+      <c r="A608" s="2" t="n">
         <v>45899</v>
       </c>
       <c r="B608" t="n">
@@ -18071,7 +18083,7 @@
       </c>
     </row>
     <row r="609">
-      <c r="A609" s="1" t="n">
+      <c r="A609" s="2" t="n">
         <v>45900</v>
       </c>
       <c r="B609" t="n">
@@ -18100,7 +18112,7 @@
       </c>
     </row>
     <row r="610">
-      <c r="A610" s="1" t="n">
+      <c r="A610" s="2" t="n">
         <v>45901</v>
       </c>
       <c r="B610" t="n">
@@ -18129,7 +18141,7 @@
       </c>
     </row>
     <row r="611">
-      <c r="A611" s="1" t="n">
+      <c r="A611" s="2" t="n">
         <v>45902</v>
       </c>
       <c r="B611" t="n">
@@ -18158,7 +18170,7 @@
       </c>
     </row>
     <row r="612">
-      <c r="A612" s="1" t="n">
+      <c r="A612" s="2" t="n">
         <v>45903</v>
       </c>
       <c r="B612" t="n">
@@ -18187,7 +18199,7 @@
       </c>
     </row>
     <row r="613">
-      <c r="A613" s="1" t="n">
+      <c r="A613" s="2" t="n">
         <v>45904</v>
       </c>
       <c r="B613" t="n">
@@ -18216,7 +18228,7 @@
       </c>
     </row>
     <row r="614">
-      <c r="A614" s="1" t="n">
+      <c r="A614" s="2" t="n">
         <v>45905</v>
       </c>
       <c r="B614" t="n">
@@ -18245,7 +18257,7 @@
       </c>
     </row>
     <row r="615">
-      <c r="A615" s="1" t="n">
+      <c r="A615" s="2" t="n">
         <v>45906</v>
       </c>
       <c r="B615" t="n">
@@ -18274,7 +18286,7 @@
       </c>
     </row>
     <row r="616">
-      <c r="A616" s="1" t="n">
+      <c r="A616" s="2" t="n">
         <v>45907</v>
       </c>
       <c r="B616" t="n">
@@ -18303,7 +18315,7 @@
       </c>
     </row>
     <row r="617">
-      <c r="A617" s="1" t="n">
+      <c r="A617" s="2" t="n">
         <v>45908</v>
       </c>
       <c r="B617" t="n">
@@ -18332,7 +18344,7 @@
       </c>
     </row>
     <row r="618">
-      <c r="A618" s="1" t="n">
+      <c r="A618" s="2" t="n">
         <v>45909</v>
       </c>
       <c r="B618" t="n">
@@ -18361,7 +18373,7 @@
       </c>
     </row>
     <row r="619">
-      <c r="A619" s="1" t="n">
+      <c r="A619" s="2" t="n">
         <v>45910</v>
       </c>
       <c r="B619" t="n">
@@ -18390,7 +18402,7 @@
       </c>
     </row>
     <row r="620">
-      <c r="A620" s="1" t="n">
+      <c r="A620" s="2" t="n">
         <v>45911</v>
       </c>
       <c r="B620" t="n">
@@ -18419,7 +18431,7 @@
       </c>
     </row>
     <row r="621">
-      <c r="A621" s="1" t="n">
+      <c r="A621" s="2" t="n">
         <v>45912</v>
       </c>
       <c r="B621" t="n">
@@ -18448,7 +18460,7 @@
       </c>
     </row>
     <row r="622">
-      <c r="A622" s="1" t="n">
+      <c r="A622" s="2" t="n">
         <v>45913</v>
       </c>
       <c r="B622" t="n">
@@ -18477,7 +18489,7 @@
       </c>
     </row>
     <row r="623">
-      <c r="A623" s="1" t="n">
+      <c r="A623" s="2" t="n">
         <v>45914</v>
       </c>
       <c r="B623" t="n">
@@ -18506,7 +18518,7 @@
       </c>
     </row>
     <row r="624">
-      <c r="A624" s="1" t="n">
+      <c r="A624" s="2" t="n">
         <v>45915</v>
       </c>
       <c r="B624" t="n">
@@ -18535,7 +18547,7 @@
       </c>
     </row>
     <row r="625">
-      <c r="A625" s="1" t="n">
+      <c r="A625" s="2" t="n">
         <v>45916</v>
       </c>
       <c r="B625" t="n">
@@ -18564,7 +18576,7 @@
       </c>
     </row>
     <row r="626">
-      <c r="A626" s="1" t="n">
+      <c r="A626" s="2" t="n">
         <v>45917</v>
       </c>
       <c r="B626" t="n">
@@ -18593,7 +18605,7 @@
       </c>
     </row>
     <row r="627">
-      <c r="A627" s="1" t="n">
+      <c r="A627" s="2" t="n">
         <v>45918</v>
       </c>
       <c r="B627" t="n">
@@ -18622,7 +18634,7 @@
       </c>
     </row>
     <row r="628">
-      <c r="A628" s="1" t="n">
+      <c r="A628" s="2" t="n">
         <v>45919</v>
       </c>
       <c r="B628" t="n">
@@ -18651,7 +18663,7 @@
       </c>
     </row>
     <row r="629">
-      <c r="A629" s="1" t="n">
+      <c r="A629" s="2" t="n">
         <v>45920</v>
       </c>
       <c r="B629" t="n">
@@ -18680,7 +18692,7 @@
       </c>
     </row>
     <row r="630">
-      <c r="A630" s="1" t="n">
+      <c r="A630" s="2" t="n">
         <v>45921</v>
       </c>
       <c r="B630" t="n">
@@ -18709,7 +18721,7 @@
       </c>
     </row>
     <row r="631">
-      <c r="A631" s="1" t="n">
+      <c r="A631" s="2" t="n">
         <v>45922</v>
       </c>
       <c r="B631" t="n">
@@ -18738,7 +18750,7 @@
       </c>
     </row>
     <row r="632">
-      <c r="A632" s="1" t="n">
+      <c r="A632" s="2" t="n">
         <v>45923</v>
       </c>
       <c r="B632" t="n">
@@ -18767,7 +18779,7 @@
       </c>
     </row>
     <row r="633">
-      <c r="A633" s="1" t="n">
+      <c r="A633" s="2" t="n">
         <v>45924</v>
       </c>
       <c r="B633" t="n">
@@ -18796,7 +18808,7 @@
       </c>
     </row>
     <row r="634">
-      <c r="A634" s="1" t="n">
+      <c r="A634" s="2" t="n">
         <v>45925</v>
       </c>
       <c r="B634" t="n">
@@ -18825,7 +18837,7 @@
       </c>
     </row>
     <row r="635">
-      <c r="A635" s="1" t="n">
+      <c r="A635" s="2" t="n">
         <v>45926</v>
       </c>
       <c r="B635" t="n">
@@ -18854,7 +18866,7 @@
       </c>
     </row>
     <row r="636">
-      <c r="A636" s="1" t="n">
+      <c r="A636" s="2" t="n">
         <v>45927</v>
       </c>
       <c r="B636" t="n">
@@ -18883,7 +18895,7 @@
       </c>
     </row>
     <row r="637">
-      <c r="A637" s="1" t="n">
+      <c r="A637" s="2" t="n">
         <v>45928</v>
       </c>
       <c r="B637" t="n">
@@ -18912,7 +18924,7 @@
       </c>
     </row>
     <row r="638">
-      <c r="A638" s="1" t="n">
+      <c r="A638" s="2" t="n">
         <v>45929</v>
       </c>
       <c r="B638" t="n">
@@ -18941,7 +18953,7 @@
       </c>
     </row>
     <row r="639">
-      <c r="A639" s="1" t="n">
+      <c r="A639" s="2" t="n">
         <v>45930</v>
       </c>
       <c r="B639" t="n">
@@ -18970,7 +18982,7 @@
       </c>
     </row>
     <row r="640">
-      <c r="A640" s="1" t="n">
+      <c r="A640" s="2" t="n">
         <v>45931</v>
       </c>
       <c r="B640" t="n">
@@ -18999,7 +19011,7 @@
       </c>
     </row>
     <row r="641">
-      <c r="A641" s="1" t="n">
+      <c r="A641" s="2" t="n">
         <v>45932</v>
       </c>
       <c r="B641" t="n">
@@ -19028,7 +19040,7 @@
       </c>
     </row>
     <row r="642">
-      <c r="A642" s="1" t="n">
+      <c r="A642" s="2" t="n">
         <v>45933</v>
       </c>
       <c r="B642" t="n">
@@ -19057,7 +19069,7 @@
       </c>
     </row>
     <row r="643">
-      <c r="A643" s="1" t="n">
+      <c r="A643" s="2" t="n">
         <v>45934</v>
       </c>
       <c r="B643" t="n">
@@ -19086,7 +19098,7 @@
       </c>
     </row>
     <row r="644">
-      <c r="A644" s="1" t="n">
+      <c r="A644" s="2" t="n">
         <v>45935</v>
       </c>
       <c r="B644" t="n">
@@ -19115,7 +19127,7 @@
       </c>
     </row>
     <row r="645">
-      <c r="A645" s="1" t="n">
+      <c r="A645" s="2" t="n">
         <v>45936</v>
       </c>
       <c r="B645" t="n">
@@ -19144,7 +19156,7 @@
       </c>
     </row>
     <row r="646">
-      <c r="A646" s="1" t="n">
+      <c r="A646" s="2" t="n">
         <v>45937</v>
       </c>
       <c r="B646" t="n">
@@ -19173,7 +19185,7 @@
       </c>
     </row>
     <row r="647">
-      <c r="A647" s="1" t="n">
+      <c r="A647" s="2" t="n">
         <v>45938</v>
       </c>
       <c r="B647" t="n">
@@ -19202,7 +19214,7 @@
       </c>
     </row>
     <row r="648">
-      <c r="A648" s="1" t="n">
+      <c r="A648" s="2" t="n">
         <v>45939</v>
       </c>
       <c r="B648" t="n">
@@ -19231,7 +19243,7 @@
       </c>
     </row>
     <row r="649">
-      <c r="A649" s="1" t="n">
+      <c r="A649" s="2" t="n">
         <v>45940</v>
       </c>
       <c r="B649" t="n">
@@ -19260,7 +19272,7 @@
       </c>
     </row>
     <row r="650">
-      <c r="A650" s="1" t="n">
+      <c r="A650" s="2" t="n">
         <v>45941</v>
       </c>
       <c r="B650" t="n">
@@ -19289,7 +19301,7 @@
       </c>
     </row>
     <row r="651">
-      <c r="A651" s="1" t="n">
+      <c r="A651" s="2" t="n">
         <v>45942</v>
       </c>
       <c r="B651" t="n">
@@ -19318,7 +19330,7 @@
       </c>
     </row>
     <row r="652">
-      <c r="A652" s="1" t="n">
+      <c r="A652" s="2" t="n">
         <v>45943</v>
       </c>
       <c r="B652" t="n">
@@ -19347,7 +19359,7 @@
       </c>
     </row>
     <row r="653">
-      <c r="A653" s="1" t="n">
+      <c r="A653" s="2" t="n">
         <v>45944</v>
       </c>
       <c r="B653" t="n">
@@ -19376,7 +19388,7 @@
       </c>
     </row>
     <row r="654">
-      <c r="A654" s="1" t="n">
+      <c r="A654" s="2" t="n">
         <v>45945</v>
       </c>
       <c r="B654" t="n">
@@ -19405,7 +19417,7 @@
       </c>
     </row>
     <row r="655">
-      <c r="A655" s="1" t="n">
+      <c r="A655" s="2" t="n">
         <v>45946</v>
       </c>
       <c r="B655" t="n">
@@ -19434,7 +19446,7 @@
       </c>
     </row>
     <row r="656">
-      <c r="A656" s="1" t="n">
+      <c r="A656" s="2" t="n">
         <v>45947</v>
       </c>
       <c r="B656" t="n">
@@ -19463,7 +19475,7 @@
       </c>
     </row>
     <row r="657">
-      <c r="A657" s="1" t="n">
+      <c r="A657" s="2" t="n">
         <v>45948</v>
       </c>
       <c r="B657" t="n">
@@ -19492,7 +19504,7 @@
       </c>
     </row>
     <row r="658">
-      <c r="A658" s="1" t="n">
+      <c r="A658" s="2" t="n">
         <v>45949</v>
       </c>
       <c r="B658" t="n">
@@ -19521,7 +19533,7 @@
       </c>
     </row>
     <row r="659">
-      <c r="A659" s="1" t="n">
+      <c r="A659" s="2" t="n">
         <v>45950</v>
       </c>
       <c r="B659" t="n">
@@ -19550,7 +19562,7 @@
       </c>
     </row>
     <row r="660">
-      <c r="A660" s="1" t="n">
+      <c r="A660" s="2" t="n">
         <v>45951</v>
       </c>
       <c r="B660" t="n">
@@ -19579,7 +19591,7 @@
       </c>
     </row>
     <row r="661">
-      <c r="A661" s="1" t="n">
+      <c r="A661" s="2" t="n">
         <v>45952</v>
       </c>
       <c r="B661" t="n">
@@ -19608,7 +19620,7 @@
       </c>
     </row>
     <row r="662">
-      <c r="A662" s="1" t="n">
+      <c r="A662" s="2" t="n">
         <v>45953</v>
       </c>
       <c r="B662" t="n">
@@ -19637,7 +19649,7 @@
       </c>
     </row>
     <row r="663">
-      <c r="A663" s="1" t="n">
+      <c r="A663" s="2" t="n">
         <v>45954</v>
       </c>
       <c r="B663" t="n">
@@ -19666,7 +19678,7 @@
       </c>
     </row>
     <row r="664">
-      <c r="A664" s="1" t="n">
+      <c r="A664" s="2" t="n">
         <v>45955</v>
       </c>
       <c r="B664" t="n">
@@ -19695,7 +19707,7 @@
       </c>
     </row>
     <row r="665">
-      <c r="A665" s="1" t="n">
+      <c r="A665" s="2" t="n">
         <v>45956</v>
       </c>
       <c r="B665" t="n">
@@ -19724,7 +19736,7 @@
       </c>
     </row>
     <row r="666">
-      <c r="A666" s="1" t="n">
+      <c r="A666" s="2" t="n">
         <v>45957</v>
       </c>
       <c r="B666" t="n">
@@ -19753,7 +19765,7 @@
       </c>
     </row>
     <row r="667">
-      <c r="A667" s="1" t="n">
+      <c r="A667" s="2" t="n">
         <v>45958</v>
       </c>
       <c r="B667" t="n">
@@ -19782,7 +19794,7 @@
       </c>
     </row>
     <row r="668">
-      <c r="A668" s="1" t="n">
+      <c r="A668" s="2" t="n">
         <v>45959</v>
       </c>
       <c r="B668" t="n">
@@ -19811,7 +19823,7 @@
       </c>
     </row>
     <row r="669">
-      <c r="A669" s="1" t="n">
+      <c r="A669" s="2" t="n">
         <v>45960</v>
       </c>
       <c r="B669" t="n">
@@ -19840,7 +19852,7 @@
       </c>
     </row>
     <row r="670">
-      <c r="A670" s="1" t="n">
+      <c r="A670" s="2" t="n">
         <v>45961</v>
       </c>
       <c r="B670" t="n">
@@ -19869,7 +19881,7 @@
       </c>
     </row>
     <row r="671">
-      <c r="A671" s="1" t="n">
+      <c r="A671" s="2" t="n">
         <v>45962</v>
       </c>
       <c r="B671" t="n">
@@ -19898,7 +19910,7 @@
       </c>
     </row>
     <row r="672">
-      <c r="A672" s="1" t="n">
+      <c r="A672" s="2" t="n">
         <v>45963</v>
       </c>
       <c r="B672" t="n">
@@ -19927,7 +19939,7 @@
       </c>
     </row>
     <row r="673">
-      <c r="A673" s="1" t="n">
+      <c r="A673" s="2" t="n">
         <v>45964</v>
       </c>
       <c r="B673" t="n">
@@ -19956,7 +19968,7 @@
       </c>
     </row>
     <row r="674">
-      <c r="A674" s="1" t="n">
+      <c r="A674" s="2" t="n">
         <v>45965</v>
       </c>
       <c r="B674" t="n">
@@ -19985,7 +19997,7 @@
       </c>
     </row>
     <row r="675">
-      <c r="A675" s="1" t="n">
+      <c r="A675" s="2" t="n">
         <v>45966</v>
       </c>
       <c r="B675" t="n">
@@ -20014,7 +20026,7 @@
       </c>
     </row>
     <row r="676">
-      <c r="A676" s="1" t="n">
+      <c r="A676" s="2" t="n">
         <v>45967</v>
       </c>
       <c r="B676" t="n">
@@ -20043,7 +20055,7 @@
       </c>
     </row>
     <row r="677">
-      <c r="A677" s="1" t="n">
+      <c r="A677" s="2" t="n">
         <v>45968</v>
       </c>
       <c r="B677" t="n">
@@ -20072,7 +20084,7 @@
       </c>
     </row>
     <row r="678">
-      <c r="A678" s="1" t="n">
+      <c r="A678" s="2" t="n">
         <v>45969</v>
       </c>
       <c r="B678" t="n">
@@ -20101,7 +20113,7 @@
       </c>
     </row>
     <row r="679">
-      <c r="A679" s="1" t="n">
+      <c r="A679" s="2" t="n">
         <v>45970</v>
       </c>
       <c r="B679" t="n">
@@ -20130,7 +20142,7 @@
       </c>
     </row>
     <row r="680">
-      <c r="A680" s="1" t="n">
+      <c r="A680" s="2" t="n">
         <v>45971</v>
       </c>
       <c r="B680" t="n">
@@ -20159,7 +20171,7 @@
       </c>
     </row>
     <row r="681">
-      <c r="A681" s="1" t="n">
+      <c r="A681" s="2" t="n">
         <v>45972</v>
       </c>
       <c r="B681" t="n">
@@ -20188,7 +20200,7 @@
       </c>
     </row>
     <row r="682">
-      <c r="A682" s="1" t="n">
+      <c r="A682" s="2" t="n">
         <v>45973</v>
       </c>
       <c r="B682" t="n">
@@ -20217,7 +20229,7 @@
       </c>
     </row>
     <row r="683">
-      <c r="A683" s="1" t="n">
+      <c r="A683" s="2" t="n">
         <v>45974</v>
       </c>
       <c r="B683" t="n">
@@ -20246,7 +20258,7 @@
       </c>
     </row>
     <row r="684">
-      <c r="A684" s="1" t="n">
+      <c r="A684" s="2" t="n">
         <v>45975</v>
       </c>
       <c r="B684" t="n">
@@ -20275,7 +20287,7 @@
       </c>
     </row>
     <row r="685">
-      <c r="A685" s="1" t="n">
+      <c r="A685" s="2" t="n">
         <v>45976</v>
       </c>
       <c r="B685" t="n">
@@ -20304,7 +20316,7 @@
       </c>
     </row>
     <row r="686">
-      <c r="A686" s="1" t="n">
+      <c r="A686" s="2" t="n">
         <v>45977</v>
       </c>
       <c r="B686" t="n">
@@ -20333,7 +20345,7 @@
       </c>
     </row>
     <row r="687">
-      <c r="A687" s="1" t="n">
+      <c r="A687" s="2" t="n">
         <v>45978</v>
       </c>
       <c r="B687" t="n">
@@ -20362,7 +20374,7 @@
       </c>
     </row>
     <row r="688">
-      <c r="A688" s="1" t="n">
+      <c r="A688" s="2" t="n">
         <v>45979</v>
       </c>
       <c r="B688" t="n">
@@ -20391,7 +20403,7 @@
       </c>
     </row>
     <row r="689">
-      <c r="A689" s="1" t="n">
+      <c r="A689" s="2" t="n">
         <v>45980</v>
       </c>
       <c r="B689" t="n">
@@ -20420,7 +20432,7 @@
       </c>
     </row>
     <row r="690">
-      <c r="A690" s="1" t="n">
+      <c r="A690" s="2" t="n">
         <v>45981</v>
       </c>
       <c r="B690" t="n">
@@ -20449,7 +20461,7 @@
       </c>
     </row>
     <row r="691">
-      <c r="A691" s="1" t="n">
+      <c r="A691" s="2" t="n">
         <v>45982</v>
       </c>
       <c r="B691" t="n">
@@ -20478,7 +20490,7 @@
       </c>
     </row>
     <row r="692">
-      <c r="A692" s="1" t="n">
+      <c r="A692" s="2" t="n">
         <v>45983</v>
       </c>
       <c r="B692" t="n">
@@ -20507,7 +20519,7 @@
       </c>
     </row>
     <row r="693">
-      <c r="A693" s="1" t="n">
+      <c r="A693" s="2" t="n">
         <v>45984</v>
       </c>
       <c r="B693" t="n">
@@ -20536,7 +20548,7 @@
       </c>
     </row>
     <row r="694">
-      <c r="A694" s="1" t="n">
+      <c r="A694" s="2" t="n">
         <v>45985</v>
       </c>
       <c r="B694" t="n">
@@ -20565,7 +20577,7 @@
       </c>
     </row>
     <row r="695">
-      <c r="A695" s="1" t="n">
+      <c r="A695" s="2" t="n">
         <v>45986</v>
       </c>
       <c r="B695" t="n">
@@ -20594,7 +20606,7 @@
       </c>
     </row>
     <row r="696">
-      <c r="A696" s="1" t="n">
+      <c r="A696" s="2" t="n">
         <v>45987</v>
       </c>
       <c r="B696" t="n">
@@ -20623,7 +20635,7 @@
       </c>
     </row>
     <row r="697">
-      <c r="A697" s="1" t="n">
+      <c r="A697" s="2" t="n">
         <v>45988</v>
       </c>
       <c r="B697" t="n">
@@ -20652,7 +20664,7 @@
       </c>
     </row>
     <row r="698">
-      <c r="A698" s="1" t="n">
+      <c r="A698" s="2" t="n">
         <v>45989</v>
       </c>
       <c r="B698" t="n">
@@ -20681,7 +20693,7 @@
       </c>
     </row>
     <row r="699">
-      <c r="A699" s="1" t="n">
+      <c r="A699" s="2" t="n">
         <v>45990</v>
       </c>
       <c r="B699" t="n">
@@ -20710,7 +20722,7 @@
       </c>
     </row>
     <row r="700">
-      <c r="A700" s="1" t="n">
+      <c r="A700" s="2" t="n">
         <v>45991</v>
       </c>
       <c r="B700" t="n">
@@ -20739,7 +20751,7 @@
       </c>
     </row>
     <row r="701">
-      <c r="A701" s="1" t="n">
+      <c r="A701" s="2" t="n">
         <v>45992</v>
       </c>
       <c r="B701" t="n">
@@ -20768,7 +20780,7 @@
       </c>
     </row>
     <row r="702">
-      <c r="A702" s="1" t="n">
+      <c r="A702" s="2" t="n">
         <v>45993</v>
       </c>
       <c r="B702" t="n">
@@ -20797,7 +20809,7 @@
       </c>
     </row>
     <row r="703">
-      <c r="A703" s="1" t="n">
+      <c r="A703" s="2" t="n">
         <v>45994</v>
       </c>
       <c r="B703" t="n">
@@ -20826,7 +20838,7 @@
       </c>
     </row>
     <row r="704">
-      <c r="A704" s="1" t="n">
+      <c r="A704" s="2" t="n">
         <v>45995</v>
       </c>
       <c r="B704" t="n">
@@ -20855,7 +20867,7 @@
       </c>
     </row>
     <row r="705">
-      <c r="A705" s="1" t="n">
+      <c r="A705" s="2" t="n">
         <v>45996</v>
       </c>
       <c r="B705" t="n">
@@ -20884,7 +20896,7 @@
       </c>
     </row>
     <row r="706">
-      <c r="A706" s="1" t="n">
+      <c r="A706" s="2" t="n">
         <v>45997</v>
       </c>
       <c r="B706" t="n">
@@ -20913,7 +20925,7 @@
       </c>
     </row>
     <row r="707">
-      <c r="A707" s="1" t="n">
+      <c r="A707" s="2" t="n">
         <v>45998</v>
       </c>
       <c r="B707" t="n">
@@ -20942,7 +20954,7 @@
       </c>
     </row>
     <row r="708">
-      <c r="A708" s="1" t="n">
+      <c r="A708" s="2" t="n">
         <v>45999</v>
       </c>
       <c r="B708" t="n">
@@ -20971,7 +20983,7 @@
       </c>
     </row>
     <row r="709">
-      <c r="A709" s="1" t="n">
+      <c r="A709" s="2" t="n">
         <v>46000</v>
       </c>
       <c r="B709" t="n">
@@ -21000,7 +21012,7 @@
       </c>
     </row>
     <row r="710">
-      <c r="A710" s="1" t="n">
+      <c r="A710" s="2" t="n">
         <v>46001</v>
       </c>
       <c r="B710" t="n">
@@ -21029,7 +21041,7 @@
       </c>
     </row>
     <row r="711">
-      <c r="A711" s="1" t="n">
+      <c r="A711" s="2" t="n">
         <v>46002</v>
       </c>
       <c r="B711" t="n">
@@ -21058,7 +21070,7 @@
       </c>
     </row>
     <row r="712">
-      <c r="A712" s="1" t="n">
+      <c r="A712" s="2" t="n">
         <v>46003</v>
       </c>
       <c r="B712" t="n">
@@ -21087,7 +21099,7 @@
       </c>
     </row>
     <row r="713">
-      <c r="A713" s="1" t="n">
+      <c r="A713" s="2" t="n">
         <v>46004</v>
       </c>
       <c r="B713" t="n">
@@ -21116,7 +21128,7 @@
       </c>
     </row>
     <row r="714">
-      <c r="A714" s="1" t="n">
+      <c r="A714" s="2" t="n">
         <v>46005</v>
       </c>
       <c r="B714" t="n">
@@ -21145,7 +21157,7 @@
       </c>
     </row>
     <row r="715">
-      <c r="A715" s="1" t="n">
+      <c r="A715" s="2" t="n">
         <v>46006</v>
       </c>
       <c r="B715" t="n">
@@ -21174,7 +21186,7 @@
       </c>
     </row>
     <row r="716">
-      <c r="A716" s="1" t="n">
+      <c r="A716" s="2" t="n">
         <v>46007</v>
       </c>
       <c r="B716" t="n">
@@ -21203,7 +21215,7 @@
       </c>
     </row>
     <row r="717">
-      <c r="A717" s="1" t="n">
+      <c r="A717" s="2" t="n">
         <v>46008</v>
       </c>
       <c r="B717" t="n">
@@ -21232,7 +21244,7 @@
       </c>
     </row>
     <row r="718">
-      <c r="A718" s="1" t="n">
+      <c r="A718" s="2" t="n">
         <v>46009</v>
       </c>
       <c r="B718" t="n">
@@ -21261,7 +21273,7 @@
       </c>
     </row>
     <row r="719">
-      <c r="A719" s="1" t="n">
+      <c r="A719" s="2" t="n">
         <v>46010</v>
       </c>
       <c r="B719" t="n">
@@ -21290,7 +21302,7 @@
       </c>
     </row>
     <row r="720">
-      <c r="A720" s="1" t="n">
+      <c r="A720" s="2" t="n">
         <v>46011</v>
       </c>
       <c r="B720" t="n">
@@ -21319,7 +21331,7 @@
       </c>
     </row>
     <row r="721">
-      <c r="A721" s="1" t="n">
+      <c r="A721" s="2" t="n">
         <v>46012</v>
       </c>
       <c r="B721" t="n">
@@ -21348,7 +21360,7 @@
       </c>
     </row>
     <row r="722">
-      <c r="A722" s="1" t="n">
+      <c r="A722" s="2" t="n">
         <v>46013</v>
       </c>
       <c r="B722" t="n">
@@ -21377,7 +21389,7 @@
       </c>
     </row>
     <row r="723">
-      <c r="A723" s="1" t="n">
+      <c r="A723" s="2" t="n">
         <v>46014</v>
       </c>
       <c r="B723" t="n">
@@ -21406,7 +21418,7 @@
       </c>
     </row>
     <row r="724">
-      <c r="A724" s="1" t="n">
+      <c r="A724" s="2" t="n">
         <v>46015</v>
       </c>
       <c r="B724" t="n">
@@ -21435,7 +21447,7 @@
       </c>
     </row>
     <row r="725">
-      <c r="A725" s="1" t="n">
+      <c r="A725" s="2" t="n">
         <v>46016</v>
       </c>
       <c r="B725" t="n">
@@ -21464,7 +21476,7 @@
       </c>
     </row>
     <row r="726">
-      <c r="A726" s="1" t="n">
+      <c r="A726" s="2" t="n">
         <v>46017</v>
       </c>
       <c r="B726" t="n">
@@ -21493,7 +21505,7 @@
       </c>
     </row>
     <row r="727">
-      <c r="A727" s="1" t="n">
+      <c r="A727" s="2" t="n">
         <v>46018</v>
       </c>
       <c r="B727" t="n">
@@ -21522,7 +21534,7 @@
       </c>
     </row>
     <row r="728">
-      <c r="A728" s="1" t="n">
+      <c r="A728" s="2" t="n">
         <v>46019</v>
       </c>
       <c r="B728" t="n">
@@ -21551,7 +21563,7 @@
       </c>
     </row>
     <row r="729">
-      <c r="A729" s="1" t="n">
+      <c r="A729" s="2" t="n">
         <v>46020</v>
       </c>
       <c r="B729" t="n">
@@ -21580,7 +21592,7 @@
       </c>
     </row>
     <row r="730">
-      <c r="A730" s="1" t="n">
+      <c r="A730" s="2" t="n">
         <v>46021</v>
       </c>
       <c r="B730" t="n">
@@ -21609,7 +21621,7 @@
       </c>
     </row>
     <row r="731">
-      <c r="A731" s="1" t="n">
+      <c r="A731" s="2" t="n">
         <v>46022</v>
       </c>
       <c r="B731" t="n">
@@ -21638,7 +21650,7 @@
       </c>
     </row>
     <row r="732">
-      <c r="A732" s="1" t="n">
+      <c r="A732" s="2" t="n">
         <v>46023</v>
       </c>
       <c r="B732" t="n">
@@ -21667,7 +21679,7 @@
       </c>
     </row>
     <row r="733">
-      <c r="A733" s="1" t="n">
+      <c r="A733" s="2" t="n">
         <v>46024</v>
       </c>
       <c r="B733" t="n">
@@ -21696,7 +21708,7 @@
       </c>
     </row>
     <row r="734">
-      <c r="A734" s="1" t="n">
+      <c r="A734" s="2" t="n">
         <v>46025</v>
       </c>
       <c r="B734" t="n">
@@ -21725,7 +21737,7 @@
       </c>
     </row>
     <row r="735">
-      <c r="A735" s="1" t="n">
+      <c r="A735" s="2" t="n">
         <v>46026</v>
       </c>
       <c r="B735" t="n">
@@ -21754,7 +21766,7 @@
       </c>
     </row>
     <row r="736">
-      <c r="A736" s="1" t="n">
+      <c r="A736" s="2" t="n">
         <v>46027</v>
       </c>
       <c r="B736" t="n">
@@ -21783,7 +21795,7 @@
       </c>
     </row>
     <row r="737">
-      <c r="A737" s="1" t="n">
+      <c r="A737" s="2" t="n">
         <v>46028</v>
       </c>
       <c r="B737" t="n">
@@ -21812,7 +21824,7 @@
       </c>
     </row>
     <row r="738">
-      <c r="A738" s="1" t="n">
+      <c r="A738" s="2" t="n">
         <v>46029</v>
       </c>
       <c r="B738" t="n">
@@ -21841,7 +21853,7 @@
       </c>
     </row>
     <row r="739">
-      <c r="A739" s="1" t="n">
+      <c r="A739" s="2" t="n">
         <v>46030</v>
       </c>
       <c r="B739" t="n">
@@ -21870,7 +21882,7 @@
       </c>
     </row>
     <row r="740">
-      <c r="A740" s="1" t="n">
+      <c r="A740" s="2" t="n">
         <v>46031</v>
       </c>
       <c r="B740" t="n">
@@ -21899,7 +21911,7 @@
       </c>
     </row>
     <row r="741">
-      <c r="A741" s="1" t="n">
+      <c r="A741" s="2" t="n">
         <v>46032</v>
       </c>
       <c r="B741" t="n">
@@ -21928,7 +21940,7 @@
       </c>
     </row>
     <row r="742">
-      <c r="A742" s="1" t="n">
+      <c r="A742" s="2" t="n">
         <v>46033</v>
       </c>
       <c r="B742" t="n">
@@ -21957,7 +21969,7 @@
       </c>
     </row>
     <row r="743">
-      <c r="A743" s="1" t="n">
+      <c r="A743" s="2" t="n">
         <v>46034</v>
       </c>
       <c r="B743" t="n">
@@ -21986,7 +21998,7 @@
       </c>
     </row>
     <row r="744">
-      <c r="A744" s="1" t="n">
+      <c r="A744" s="2" t="n">
         <v>46035</v>
       </c>
       <c r="B744" t="n">
@@ -22015,7 +22027,7 @@
       </c>
     </row>
     <row r="745">
-      <c r="A745" s="1" t="n">
+      <c r="A745" s="2" t="n">
         <v>46036</v>
       </c>
       <c r="B745" t="n">
@@ -22044,7 +22056,7 @@
       </c>
     </row>
     <row r="746">
-      <c r="A746" s="1" t="n">
+      <c r="A746" s="2" t="n">
         <v>46037</v>
       </c>
       <c r="B746" t="n">
@@ -22073,7 +22085,7 @@
       </c>
     </row>
     <row r="747">
-      <c r="A747" s="1" t="n">
+      <c r="A747" s="2" t="n">
         <v>46038</v>
       </c>
       <c r="B747" t="n">
@@ -22102,7 +22114,7 @@
       </c>
     </row>
     <row r="748">
-      <c r="A748" s="1" t="n">
+      <c r="A748" s="2" t="n">
         <v>46039</v>
       </c>
       <c r="B748" t="n">
@@ -22131,7 +22143,7 @@
       </c>
     </row>
     <row r="749">
-      <c r="A749" s="1" t="n">
+      <c r="A749" s="2" t="n">
         <v>46040</v>
       </c>
       <c r="B749" t="n">
@@ -22160,7 +22172,7 @@
       </c>
     </row>
     <row r="750">
-      <c r="A750" s="1" t="n">
+      <c r="A750" s="2" t="n">
         <v>46041</v>
       </c>
       <c r="B750" t="n">
@@ -22189,7 +22201,7 @@
       </c>
     </row>
     <row r="751">
-      <c r="A751" s="1" t="n">
+      <c r="A751" s="2" t="n">
         <v>46042</v>
       </c>
       <c r="B751" t="n">
@@ -22218,7 +22230,7 @@
       </c>
     </row>
     <row r="752">
-      <c r="A752" s="1" t="n">
+      <c r="A752" s="2" t="n">
         <v>46043</v>
       </c>
       <c r="B752" t="n">
@@ -22247,7 +22259,7 @@
       </c>
     </row>
     <row r="753">
-      <c r="A753" s="1" t="n">
+      <c r="A753" s="2" t="n">
         <v>46044</v>
       </c>
       <c r="B753" t="n">
@@ -22276,7 +22288,7 @@
       </c>
     </row>
     <row r="754">
-      <c r="A754" s="1" t="n">
+      <c r="A754" s="2" t="n">
         <v>46045</v>
       </c>
       <c r="B754" t="n">
@@ -22305,7 +22317,7 @@
       </c>
     </row>
     <row r="755">
-      <c r="A755" s="1" t="n">
+      <c r="A755" s="2" t="n">
         <v>46046</v>
       </c>
       <c r="B755" t="n">
@@ -22334,7 +22346,7 @@
       </c>
     </row>
     <row r="756">
-      <c r="A756" s="1" t="n">
+      <c r="A756" s="2" t="n">
         <v>46047</v>
       </c>
       <c r="B756" t="n">
@@ -22363,7 +22375,7 @@
       </c>
     </row>
     <row r="757">
-      <c r="A757" s="1" t="n">
+      <c r="A757" s="2" t="n">
         <v>46048</v>
       </c>
       <c r="B757" t="n">
@@ -22392,7 +22404,7 @@
       </c>
     </row>
     <row r="758">
-      <c r="A758" s="1" t="n">
+      <c r="A758" s="2" t="n">
         <v>46049</v>
       </c>
       <c r="B758" t="n">
@@ -22421,7 +22433,7 @@
       </c>
     </row>
     <row r="759">
-      <c r="A759" s="1" t="n">
+      <c r="A759" s="2" t="n">
         <v>46050</v>
       </c>
       <c r="B759" t="n">
@@ -22450,7 +22462,7 @@
       </c>
     </row>
     <row r="760">
-      <c r="A760" s="1" t="n">
+      <c r="A760" s="2" t="n">
         <v>46051</v>
       </c>
       <c r="B760" t="n">
@@ -22479,7 +22491,7 @@
       </c>
     </row>
     <row r="761">
-      <c r="A761" s="1" t="n">
+      <c r="A761" s="2" t="n">
         <v>46052</v>
       </c>
       <c r="B761" t="n">
@@ -22508,7 +22520,7 @@
       </c>
     </row>
     <row r="762">
-      <c r="A762" s="1" t="n">
+      <c r="A762" s="2" t="n">
         <v>46053</v>
       </c>
       <c r="B762" t="n">
@@ -22537,7 +22549,7 @@
       </c>
     </row>
     <row r="763">
-      <c r="A763" s="1" t="n">
+      <c r="A763" s="2" t="n">
         <v>46054</v>
       </c>
       <c r="B763" t="n">
@@ -22566,7 +22578,7 @@
       </c>
     </row>
     <row r="764">
-      <c r="A764" s="1" t="n">
+      <c r="A764" s="2" t="n">
         <v>46055</v>
       </c>
       <c r="B764" t="n">
@@ -22595,7 +22607,7 @@
       </c>
     </row>
     <row r="765">
-      <c r="A765" s="1" t="n">
+      <c r="A765" s="2" t="n">
         <v>46056</v>
       </c>
       <c r="B765" t="n">
@@ -22624,7 +22636,7 @@
       </c>
     </row>
     <row r="766">
-      <c r="A766" s="1" t="n">
+      <c r="A766" s="2" t="n">
         <v>46057</v>
       </c>
       <c r="B766" t="n">
@@ -22653,7 +22665,7 @@
       </c>
     </row>
     <row r="767">
-      <c r="A767" s="1" t="n">
+      <c r="A767" s="2" t="n">
         <v>46058</v>
       </c>
       <c r="B767" t="n">
@@ -22682,7 +22694,7 @@
       </c>
     </row>
     <row r="768">
-      <c r="A768" s="1" t="n">
+      <c r="A768" s="2" t="n">
         <v>46059</v>
       </c>
       <c r="B768" t="n">
@@ -22711,7 +22723,7 @@
       </c>
     </row>
     <row r="769">
-      <c r="A769" s="1" t="n">
+      <c r="A769" s="2" t="n">
         <v>46060</v>
       </c>
       <c r="B769" t="n">
@@ -22740,7 +22752,7 @@
       </c>
     </row>
     <row r="770">
-      <c r="A770" s="1" t="n">
+      <c r="A770" s="2" t="n">
         <v>46061</v>
       </c>
       <c r="B770" t="n">
@@ -22769,7 +22781,7 @@
       </c>
     </row>
     <row r="771">
-      <c r="A771" s="1" t="n">
+      <c r="A771" s="2" t="n">
         <v>46062</v>
       </c>
       <c r="B771" t="n">
@@ -22798,7 +22810,7 @@
       </c>
     </row>
     <row r="772">
-      <c r="A772" s="1" t="n">
+      <c r="A772" s="2" t="n">
         <v>46063</v>
       </c>
       <c r="B772" t="n">
@@ -22827,7 +22839,7 @@
       </c>
     </row>
     <row r="773">
-      <c r="A773" s="1" t="n">
+      <c r="A773" s="2" t="n">
         <v>46064</v>
       </c>
       <c r="B773" t="n">
@@ -22856,7 +22868,7 @@
       </c>
     </row>
     <row r="774">
-      <c r="A774" s="1" t="n">
+      <c r="A774" s="2" t="n">
         <v>46065</v>
       </c>
       <c r="B774" t="n">
@@ -22885,7 +22897,7 @@
       </c>
     </row>
     <row r="775">
-      <c r="A775" s="1" t="n">
+      <c r="A775" s="2" t="n">
         <v>46066</v>
       </c>
       <c r="B775" t="n">
@@ -22914,7 +22926,7 @@
       </c>
     </row>
     <row r="776">
-      <c r="A776" s="1" t="n">
+      <c r="A776" s="2" t="n">
         <v>46067</v>
       </c>
       <c r="B776" t="n">
@@ -22943,7 +22955,7 @@
       </c>
     </row>
     <row r="777">
-      <c r="A777" s="1" t="n">
+      <c r="A777" s="2" t="n">
         <v>46068</v>
       </c>
       <c r="B777" t="n">
@@ -22972,7 +22984,7 @@
       </c>
     </row>
     <row r="778">
-      <c r="A778" s="1" t="n">
+      <c r="A778" s="2" t="n">
         <v>46069</v>
       </c>
       <c r="B778" t="n">
@@ -23001,7 +23013,7 @@
       </c>
     </row>
     <row r="779">
-      <c r="A779" s="1" t="n">
+      <c r="A779" s="2" t="n">
         <v>46071</v>
       </c>
       <c r="B779" t="n">
@@ -23030,7 +23042,7 @@
       </c>
     </row>
     <row r="780">
-      <c r="A780" s="1" t="n">
+      <c r="A780" s="2" t="n">
         <v>46072</v>
       </c>
       <c r="B780" t="n">
@@ -23059,7 +23071,7 @@
       </c>
     </row>
     <row r="781">
-      <c r="A781" s="1" t="n">
+      <c r="A781" s="2" t="n">
         <v>46073</v>
       </c>
       <c r="B781" t="n">
@@ -23088,7 +23100,7 @@
       </c>
     </row>
     <row r="782">
-      <c r="A782" s="1" t="n">
+      <c r="A782" s="2" t="n">
         <v>46074</v>
       </c>
       <c r="B782" t="n">
@@ -23117,7 +23129,7 @@
       </c>
     </row>
     <row r="783">
-      <c r="A783" s="1" t="n">
+      <c r="A783" s="2" t="n">
         <v>46075</v>
       </c>
       <c r="B783" t="n">
@@ -23146,7 +23158,7 @@
       </c>
     </row>
     <row r="784">
-      <c r="A784" s="1" t="n">
+      <c r="A784" s="2" t="n">
         <v>46076</v>
       </c>
       <c r="B784" t="n">
@@ -23175,7 +23187,7 @@
       </c>
     </row>
     <row r="785">
-      <c r="A785" s="1" t="n">
+      <c r="A785" s="2" t="n">
         <v>46077</v>
       </c>
       <c r="B785" t="n">
@@ -23204,7 +23216,7 @@
       </c>
     </row>
     <row r="786">
-      <c r="A786" s="1" t="n">
+      <c r="A786" s="2" t="n">
         <v>46078</v>
       </c>
       <c r="B786" t="n">
@@ -23233,7 +23245,7 @@
       </c>
     </row>
     <row r="787">
-      <c r="A787" s="1" t="n">
+      <c r="A787" s="2" t="n">
         <v>46079</v>
       </c>
       <c r="B787" t="n">
@@ -23262,7 +23274,7 @@
       </c>
     </row>
     <row r="788">
-      <c r="A788" s="1" t="n">
+      <c r="A788" s="2" t="n">
         <v>46080</v>
       </c>
       <c r="B788" t="n">
@@ -23291,7 +23303,7 @@
       </c>
     </row>
     <row r="789">
-      <c r="A789" s="1" t="n">
+      <c r="A789" s="2" t="n">
         <v>46081</v>
       </c>
       <c r="B789" t="n">
@@ -23320,7 +23332,7 @@
       </c>
     </row>
     <row r="790">
-      <c r="A790" s="1" t="n">
+      <c r="A790" s="2" t="n">
         <v>46082</v>
       </c>
       <c r="B790" t="n">
@@ -23349,7 +23361,7 @@
       </c>
     </row>
     <row r="791">
-      <c r="A791" s="1" t="n">
+      <c r="A791" s="2" t="n">
         <v>46083</v>
       </c>
       <c r="B791" t="n">
@@ -23378,7 +23390,7 @@
       </c>
     </row>
     <row r="792">
-      <c r="A792" s="1" t="n">
+      <c r="A792" s="2" t="n">
         <v>46084</v>
       </c>
       <c r="B792" t="n">
@@ -23407,7 +23419,7 @@
       </c>
     </row>
     <row r="793">
-      <c r="A793" s="1" t="n">
+      <c r="A793" s="2" t="n">
         <v>46085</v>
       </c>
       <c r="B793" t="n">
@@ -23436,7 +23448,7 @@
       </c>
     </row>
     <row r="794">
-      <c r="A794" s="1" t="n">
+      <c r="A794" s="2" t="n">
         <v>46086</v>
       </c>
       <c r="B794" t="n">
@@ -23465,7 +23477,7 @@
       </c>
     </row>
     <row r="795">
-      <c r="A795" s="1" t="n">
+      <c r="A795" s="2" t="n">
         <v>46087</v>
       </c>
       <c r="B795" t="n">
@@ -23494,7 +23506,7 @@
       </c>
     </row>
     <row r="796">
-      <c r="A796" s="1" t="n">
+      <c r="A796" s="2" t="n">
         <v>46088</v>
       </c>
       <c r="B796" t="n">
@@ -23523,7 +23535,7 @@
       </c>
     </row>
     <row r="797">
-      <c r="A797" s="1" t="n">
+      <c r="A797" s="2" t="n">
         <v>46089</v>
       </c>
       <c r="B797" t="n">
@@ -23552,7 +23564,7 @@
       </c>
     </row>
     <row r="798">
-      <c r="A798" s="1" t="n">
+      <c r="A798" s="2" t="n">
         <v>46090</v>
       </c>
       <c r="B798" t="n">
@@ -23581,7 +23593,7 @@
       </c>
     </row>
     <row r="799">
-      <c r="A799" s="1" t="n">
+      <c r="A799" s="2" t="n">
         <v>46091</v>
       </c>
       <c r="B799" t="n">
@@ -23610,7 +23622,7 @@
       </c>
     </row>
     <row r="800">
-      <c r="A800" s="1" t="n">
+      <c r="A800" s="2" t="n">
         <v>46092</v>
       </c>
       <c r="B800" t="n">
@@ -23639,7 +23651,7 @@
       </c>
     </row>
     <row r="801">
-      <c r="A801" s="1" t="n">
+      <c r="A801" s="2" t="n">
         <v>46093</v>
       </c>
       <c r="B801" t="n">
@@ -23668,7 +23680,7 @@
       </c>
     </row>
     <row r="802">
-      <c r="A802" s="1" t="n">
+      <c r="A802" s="2" t="n">
         <v>46094</v>
       </c>
       <c r="B802" t="n">
@@ -23697,7 +23709,7 @@
       </c>
     </row>
     <row r="803">
-      <c r="A803" s="1" t="n">
+      <c r="A803" s="2" t="n">
         <v>46095</v>
       </c>
       <c r="B803" t="n">
@@ -23726,7 +23738,7 @@
       </c>
     </row>
     <row r="804">
-      <c r="A804" s="1" t="n">
+      <c r="A804" s="2" t="n">
         <v>46096</v>
       </c>
       <c r="B804" t="n">
@@ -23755,7 +23767,7 @@
       </c>
     </row>
     <row r="805">
-      <c r="A805" s="1" t="n">
+      <c r="A805" s="2" t="n">
         <v>46097</v>
       </c>
       <c r="B805" t="n">
@@ -23784,7 +23796,7 @@
       </c>
     </row>
     <row r="806">
-      <c r="A806" s="1" t="n">
+      <c r="A806" s="2" t="n">
         <v>46098</v>
       </c>
       <c r="B806" t="n">
@@ -23813,7 +23825,7 @@
       </c>
     </row>
     <row r="807">
-      <c r="A807" s="1" t="n">
+      <c r="A807" s="2" t="n">
         <v>46099</v>
       </c>
       <c r="B807" t="n">
@@ -23842,7 +23854,7 @@
       </c>
     </row>
     <row r="808">
-      <c r="A808" s="1" t="n">
+      <c r="A808" s="2" t="n">
         <v>46100</v>
       </c>
       <c r="B808" t="n">
@@ -23871,7 +23883,7 @@
       </c>
     </row>
     <row r="809">
-      <c r="A809" s="1" t="n">
+      <c r="A809" s="2" t="n">
         <v>46101</v>
       </c>
       <c r="B809" t="n">
@@ -23900,7 +23912,7 @@
       </c>
     </row>
     <row r="810">
-      <c r="A810" s="1" t="n">
+      <c r="A810" s="2" t="n">
         <v>46102</v>
       </c>
       <c r="B810" t="n">
@@ -23929,7 +23941,7 @@
       </c>
     </row>
     <row r="811">
-      <c r="A811" s="1" t="n">
+      <c r="A811" s="2" t="n">
         <v>46103</v>
       </c>
       <c r="B811" t="n">
@@ -23958,7 +23970,7 @@
       </c>
     </row>
     <row r="812">
-      <c r="A812" s="1" t="n">
+      <c r="A812" s="2" t="n">
         <v>46104</v>
       </c>
       <c r="B812" t="n">
@@ -23987,7 +23999,7 @@
       </c>
     </row>
     <row r="813">
-      <c r="A813" s="1" t="n">
+      <c r="A813" s="2" t="n">
         <v>46105</v>
       </c>
       <c r="B813" t="n">
@@ -24016,7 +24028,7 @@
       </c>
     </row>
     <row r="814">
-      <c r="A814" s="1" t="n">
+      <c r="A814" s="2" t="n">
         <v>46106</v>
       </c>
       <c r="B814" t="n">
@@ -24045,7 +24057,7 @@
       </c>
     </row>
     <row r="815">
-      <c r="A815" s="1" t="n">
+      <c r="A815" s="2" t="n">
         <v>46107</v>
       </c>
       <c r="B815" t="n">
@@ -24074,7 +24086,7 @@
       </c>
     </row>
     <row r="816">
-      <c r="A816" s="1" t="n">
+      <c r="A816" s="2" t="n">
         <v>46108</v>
       </c>
       <c r="B816" t="n">
@@ -24103,7 +24115,7 @@
       </c>
     </row>
     <row r="817">
-      <c r="A817" s="1" t="n">
+      <c r="A817" s="2" t="n">
         <v>46109</v>
       </c>
       <c r="B817" t="n">
@@ -24132,7 +24144,7 @@
       </c>
     </row>
     <row r="818">
-      <c r="A818" s="1" t="n">
+      <c r="A818" s="2" t="n">
         <v>46110</v>
       </c>
       <c r="B818" t="n">
@@ -24161,7 +24173,7 @@
       </c>
     </row>
     <row r="819">
-      <c r="A819" s="1" t="n">
+      <c r="A819" s="2" t="n">
         <v>46111</v>
       </c>
       <c r="B819" t="n">
@@ -24190,7 +24202,7 @@
       </c>
     </row>
     <row r="820">
-      <c r="A820" s="1" t="n">
+      <c r="A820" s="2" t="n">
         <v>46112</v>
       </c>
       <c r="B820" t="n">
@@ -24219,7 +24231,7 @@
       </c>
     </row>
     <row r="821">
-      <c r="A821" s="1" t="n">
+      <c r="A821" s="2" t="n">
         <v>46113</v>
       </c>
       <c r="B821" t="n">
@@ -24248,7 +24260,7 @@
       </c>
     </row>
     <row r="822">
-      <c r="A822" s="1" t="n">
+      <c r="A822" s="2" t="n">
         <v>46114</v>
       </c>
       <c r="B822" t="n">
@@ -24277,7 +24289,7 @@
       </c>
     </row>
     <row r="823">
-      <c r="A823" s="1" t="n">
+      <c r="A823" s="2" t="n">
         <v>46115</v>
       </c>
       <c r="B823" t="n">
@@ -24306,7 +24318,7 @@
       </c>
     </row>
     <row r="824">
-      <c r="A824" s="1" t="n">
+      <c r="A824" s="2" t="n">
         <v>46116</v>
       </c>
       <c r="B824" t="n">
@@ -24335,7 +24347,7 @@
       </c>
     </row>
     <row r="825">
-      <c r="A825" s="1" t="n">
+      <c r="A825" s="2" t="n">
         <v>46117</v>
       </c>
       <c r="B825" t="n">
@@ -24364,7 +24376,7 @@
       </c>
     </row>
     <row r="826">
-      <c r="A826" s="1" t="n">
+      <c r="A826" s="2" t="n">
         <v>46118</v>
       </c>
       <c r="B826" t="n">
@@ -24393,7 +24405,7 @@
       </c>
     </row>
     <row r="827">
-      <c r="A827" s="1" t="n">
+      <c r="A827" s="2" t="n">
         <v>46119</v>
       </c>
       <c r="B827" t="n">
@@ -24422,7 +24434,7 @@
       </c>
     </row>
     <row r="828">
-      <c r="A828" s="1" t="n">
+      <c r="A828" s="2" t="n">
         <v>46120</v>
       </c>
       <c r="B828" t="n">
@@ -24451,7 +24463,7 @@
       </c>
     </row>
     <row r="829">
-      <c r="A829" s="1" t="n">
+      <c r="A829" s="2" t="n">
         <v>46121</v>
       </c>
       <c r="B829" t="n">
@@ -24480,7 +24492,7 @@
       </c>
     </row>
     <row r="830">
-      <c r="A830" s="1" t="n">
+      <c r="A830" s="2" t="n">
         <v>46122</v>
       </c>
       <c r="B830" t="n">
@@ -24509,7 +24521,7 @@
       </c>
     </row>
     <row r="831">
-      <c r="A831" s="1" t="n">
+      <c r="A831" s="2" t="n">
         <v>46123</v>
       </c>
       <c r="B831" t="n">
@@ -24538,7 +24550,7 @@
       </c>
     </row>
     <row r="832">
-      <c r="A832" s="1" t="n">
+      <c r="A832" s="2" t="n">
         <v>46124</v>
       </c>
       <c r="B832" t="n">
@@ -24567,7 +24579,7 @@
       </c>
     </row>
     <row r="833">
-      <c r="A833" s="1" t="n">
+      <c r="A833" s="2" t="n">
         <v>46125</v>
       </c>
       <c r="B833" t="n">
@@ -24596,7 +24608,7 @@
       </c>
     </row>
     <row r="834">
-      <c r="A834" s="1" t="n">
+      <c r="A834" s="2" t="n">
         <v>46126</v>
       </c>
       <c r="B834" t="n">
@@ -24625,7 +24637,7 @@
       </c>
     </row>
     <row r="835">
-      <c r="A835" s="1" t="n">
+      <c r="A835" s="2" t="n">
         <v>46127</v>
       </c>
       <c r="B835" t="n">
@@ -24654,7 +24666,7 @@
       </c>
     </row>
     <row r="836">
-      <c r="A836" s="1" t="n">
+      <c r="A836" s="2" t="n">
         <v>46128</v>
       </c>
       <c r="B836" t="n">
@@ -24683,7 +24695,7 @@
       </c>
     </row>
     <row r="837">
-      <c r="A837" s="1" t="n">
+      <c r="A837" s="2" t="n">
         <v>46129</v>
       </c>
       <c r="B837" t="n">
@@ -24712,7 +24724,7 @@
       </c>
     </row>
     <row r="838">
-      <c r="A838" s="1" t="n">
+      <c r="A838" s="2" t="n">
         <v>46130</v>
       </c>
       <c r="B838" t="n">
@@ -24741,7 +24753,7 @@
       </c>
     </row>
     <row r="839">
-      <c r="A839" s="1" t="n">
+      <c r="A839" s="2" t="n">
         <v>46131</v>
       </c>
       <c r="B839" t="n">
@@ -24770,7 +24782,7 @@
       </c>
     </row>
     <row r="840">
-      <c r="A840" s="1" t="n">
+      <c r="A840" s="2" t="n">
         <v>46132</v>
       </c>
       <c r="B840" t="n">
@@ -24799,7 +24811,7 @@
       </c>
     </row>
     <row r="841">
-      <c r="A841" s="1" t="n">
+      <c r="A841" s="2" t="n">
         <v>46133</v>
       </c>
       <c r="B841" t="n">
@@ -24828,7 +24840,7 @@
       </c>
     </row>
     <row r="842">
-      <c r="A842" s="1" t="n">
+      <c r="A842" s="2" t="n">
         <v>46134</v>
       </c>
       <c r="B842" t="n">
@@ -24857,7 +24869,7 @@
       </c>
     </row>
     <row r="843">
-      <c r="A843" s="1" t="n">
+      <c r="A843" s="2" t="n">
         <v>46135</v>
       </c>
       <c r="B843" t="n">
@@ -24886,7 +24898,7 @@
       </c>
     </row>
     <row r="844">
-      <c r="A844" s="1" t="n">
+      <c r="A844" s="2" t="n">
         <v>46136</v>
       </c>
       <c r="B844" t="n">
@@ -24915,7 +24927,7 @@
       </c>
     </row>
     <row r="845">
-      <c r="A845" s="1" t="n">
+      <c r="A845" s="2" t="n">
         <v>46137</v>
       </c>
       <c r="B845" t="n">
@@ -24944,7 +24956,7 @@
       </c>
     </row>
     <row r="846">
-      <c r="A846" s="1" t="n">
+      <c r="A846" s="2" t="n">
         <v>46138</v>
       </c>
       <c r="B846" t="n">
@@ -24973,7 +24985,7 @@
       </c>
     </row>
     <row r="847">
-      <c r="A847" s="1" t="n">
+      <c r="A847" s="2" t="n">
         <v>46139</v>
       </c>
       <c r="B847" t="n">
@@ -25002,7 +25014,7 @@
       </c>
     </row>
     <row r="848">
-      <c r="A848" s="1" t="n">
+      <c r="A848" s="2" t="n">
         <v>46140</v>
       </c>
       <c r="B848" t="n">
@@ -25031,7 +25043,7 @@
       </c>
     </row>
     <row r="849">
-      <c r="A849" s="1" t="n">
+      <c r="A849" s="2" t="n">
         <v>46141</v>
       </c>
       <c r="B849" t="n">
@@ -25060,7 +25072,7 @@
       </c>
     </row>
     <row r="850">
-      <c r="A850" s="1" t="n">
+      <c r="A850" s="2" t="n">
         <v>46142</v>
       </c>
       <c r="B850" t="n">
@@ -25089,7 +25101,7 @@
       </c>
     </row>
     <row r="851">
-      <c r="A851" s="1" t="n">
+      <c r="A851" s="2" t="n">
         <v>46143</v>
       </c>
       <c r="B851" t="n">
@@ -25118,7 +25130,7 @@
       </c>
     </row>
     <row r="852">
-      <c r="A852" s="1" t="n">
+      <c r="A852" s="2" t="n">
         <v>46144</v>
       </c>
       <c r="B852" t="n">
@@ -25147,7 +25159,7 @@
       </c>
     </row>
     <row r="853">
-      <c r="A853" s="1" t="n">
+      <c r="A853" s="2" t="n">
         <v>46145</v>
       </c>
       <c r="B853" t="n">
@@ -25176,11 +25188,11 @@
       </c>
     </row>
     <row r="854">
-      <c r="A854" s="1" t="n">
+      <c r="A854" s="2" t="n">
         <v>46146</v>
       </c>
       <c r="B854" t="n">
-        <v>18629</v>
+        <v>18628</v>
       </c>
       <c r="C854" t="n">
         <v>6033</v>
@@ -25195,7 +25207,7 @@
         <v>1181</v>
       </c>
       <c r="G854" t="n">
-        <v>2953</v>
+        <v>2952</v>
       </c>
       <c r="H854" t="n">
         <v>12764</v>
@@ -25205,11 +25217,11 @@
       </c>
     </row>
     <row r="855">
-      <c r="A855" s="1" t="n">
+      <c r="A855" s="2" t="n">
         <v>46147</v>
       </c>
       <c r="B855" t="n">
-        <v>11227</v>
+        <v>11226</v>
       </c>
       <c r="C855" t="n">
         <v>5420</v>
@@ -25224,21 +25236,21 @@
         <v>0</v>
       </c>
       <c r="G855" t="n">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="H855" t="n">
         <v>10835</v>
       </c>
       <c r="I855" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="856">
-      <c r="A856" s="1" t="n">
+      <c r="A856" s="2" t="n">
         <v>46148</v>
       </c>
       <c r="B856" t="n">
-        <v>17487</v>
+        <v>17486</v>
       </c>
       <c r="C856" t="n">
         <v>5999</v>
@@ -25253,7 +25265,7 @@
         <v>748</v>
       </c>
       <c r="G856" t="n">
-        <v>2658</v>
+        <v>2657</v>
       </c>
       <c r="H856" t="n">
         <v>12586</v>
@@ -25263,11 +25275,11 @@
       </c>
     </row>
     <row r="857">
-      <c r="A857" s="1" t="n">
+      <c r="A857" s="2" t="n">
         <v>46149</v>
       </c>
       <c r="B857" t="n">
-        <v>19576</v>
+        <v>19575</v>
       </c>
       <c r="C857" t="n">
         <v>6835</v>
@@ -25282,7 +25294,7 @@
         <v>2268</v>
       </c>
       <c r="G857" t="n">
-        <v>1861</v>
+        <v>1860</v>
       </c>
       <c r="H857" t="n">
         <v>14511</v>
@@ -25292,11 +25304,11 @@
       </c>
     </row>
     <row r="858">
-      <c r="A858" s="1" t="n">
+      <c r="A858" s="2" t="n">
         <v>46150</v>
       </c>
       <c r="B858" t="n">
-        <v>18717</v>
+        <v>18716</v>
       </c>
       <c r="C858" t="n">
         <v>7240</v>
@@ -25311,7 +25323,7 @@
         <v>1518</v>
       </c>
       <c r="G858" t="n">
-        <v>1334</v>
+        <v>1333</v>
       </c>
       <c r="H858" t="n">
         <v>14915</v>
@@ -25321,7 +25333,7 @@
       </c>
     </row>
     <row r="859">
-      <c r="A859" s="1" t="n">
+      <c r="A859" s="2" t="n">
         <v>46151</v>
       </c>
       <c r="B859" t="n">
@@ -25350,7 +25362,7 @@
       </c>
     </row>
     <row r="860">
-      <c r="A860" s="1" t="n">
+      <c r="A860" s="2" t="n">
         <v>46152</v>
       </c>
       <c r="B860" t="n">
@@ -25379,11 +25391,11 @@
       </c>
     </row>
     <row r="861">
-      <c r="A861" s="1" t="n">
+      <c r="A861" s="2" t="n">
         <v>46153</v>
       </c>
       <c r="B861" t="n">
-        <v>19305</v>
+        <v>19304</v>
       </c>
       <c r="C861" t="n">
         <v>6459</v>
@@ -25398,7 +25410,7 @@
         <v>2149</v>
       </c>
       <c r="G861" t="n">
-        <v>2619</v>
+        <v>2618</v>
       </c>
       <c r="H861" t="n">
         <v>13106</v>
@@ -25408,7 +25420,7 @@
       </c>
     </row>
     <row r="862">
-      <c r="A862" s="1" t="n">
+      <c r="A862" s="2" t="n">
         <v>46154</v>
       </c>
       <c r="B862" t="n">
@@ -25437,11 +25449,11 @@
       </c>
     </row>
     <row r="863">
-      <c r="A863" s="1" t="n">
+      <c r="A863" s="2" t="n">
         <v>46155</v>
       </c>
       <c r="B863" t="n">
-        <v>21643</v>
+        <v>21642</v>
       </c>
       <c r="C863" t="n">
         <v>8287</v>
@@ -25456,7 +25468,7 @@
         <v>834</v>
       </c>
       <c r="G863" t="n">
-        <v>2152</v>
+        <v>2151</v>
       </c>
       <c r="H863" t="n">
         <v>17395</v>
@@ -25466,11 +25478,11 @@
       </c>
     </row>
     <row r="864">
-      <c r="A864" s="1" t="n">
+      <c r="A864" s="2" t="n">
         <v>46156</v>
       </c>
       <c r="B864" t="n">
-        <v>22482</v>
+        <v>22481</v>
       </c>
       <c r="C864" t="n">
         <v>7660</v>
@@ -25485,7 +25497,7 @@
         <v>601</v>
       </c>
       <c r="G864" t="n">
-        <v>2583</v>
+        <v>2582</v>
       </c>
       <c r="H864" t="n">
         <v>18276</v>
@@ -25495,7 +25507,7 @@
       </c>
     </row>
     <row r="865">
-      <c r="A865" s="1" t="n">
+      <c r="A865" s="2" t="n">
         <v>46157</v>
       </c>
       <c r="B865" t="n">
@@ -25524,11 +25536,11 @@
       </c>
     </row>
     <row r="866">
-      <c r="A866" s="1" t="n">
+      <c r="A866" s="2" t="n">
         <v>46158</v>
       </c>
       <c r="B866" t="n">
-        <v>15616</v>
+        <v>15615</v>
       </c>
       <c r="C866" t="n">
         <v>7543</v>
@@ -25543,21 +25555,21 @@
         <v>0</v>
       </c>
       <c r="G866" t="n">
-        <v>771</v>
+        <v>770</v>
       </c>
       <c r="H866" t="n">
         <v>14497</v>
       </c>
       <c r="I866" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="867">
-      <c r="A867" s="1" t="n">
+      <c r="A867" s="2" t="n">
         <v>46159</v>
       </c>
       <c r="B867" t="n">
-        <v>13093</v>
+        <v>13091</v>
       </c>
       <c r="C867" t="n">
         <v>6881</v>
@@ -25572,46 +25584,46 @@
         <v>0</v>
       </c>
       <c r="G867" t="n">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="H867" t="n">
         <v>12808</v>
       </c>
       <c r="I867" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
     </row>
     <row r="868">
-      <c r="A868" s="1" t="n">
+      <c r="A868" s="2" t="n">
         <v>46160</v>
       </c>
       <c r="B868" t="n">
-        <v>23728</v>
+        <v>23628</v>
       </c>
       <c r="C868" t="n">
-        <v>8213</v>
+        <v>8200</v>
       </c>
       <c r="D868" t="n">
-        <v>7963</v>
+        <v>7944</v>
       </c>
       <c r="E868" t="n">
-        <v>1703</v>
+        <v>1698</v>
       </c>
       <c r="F868" t="n">
-        <v>1114</v>
+        <v>1109</v>
       </c>
       <c r="G868" t="n">
-        <v>4735</v>
+        <v>4677</v>
       </c>
       <c r="H868" t="n">
-        <v>16176</v>
+        <v>16144</v>
       </c>
       <c r="I868" t="n">
         <v>23</v>
       </c>
     </row>
     <row r="869">
-      <c r="A869" s="1" t="n">
+      <c r="A869" s="2" t="n">
         <v>46161</v>
       </c>
       <c r="B869" t="n">
@@ -25640,69 +25652,69 @@
       </c>
     </row>
     <row r="870">
-      <c r="A870" s="1" t="n">
+      <c r="A870" s="2" t="n">
         <v>46162</v>
       </c>
       <c r="B870" t="n">
-        <v>21985</v>
+        <v>21801</v>
       </c>
       <c r="C870" t="n">
-        <v>8171</v>
+        <v>8153</v>
       </c>
       <c r="D870" t="n">
-        <v>9268</v>
+        <v>9249</v>
       </c>
       <c r="E870" t="n">
-        <v>1023</v>
+        <v>1019</v>
       </c>
       <c r="F870" t="n">
-        <v>463</v>
+        <v>460</v>
       </c>
       <c r="G870" t="n">
-        <v>3060</v>
+        <v>2920</v>
       </c>
       <c r="H870" t="n">
-        <v>17439</v>
+        <v>17402</v>
       </c>
       <c r="I870" t="n">
         <v>24</v>
       </c>
     </row>
     <row r="871">
-      <c r="A871" s="1" t="n">
+      <c r="A871" s="2" t="n">
         <v>46163</v>
       </c>
       <c r="B871" t="n">
-        <v>23700</v>
+        <v>23563</v>
       </c>
       <c r="C871" t="n">
-        <v>9139</v>
+        <v>9128</v>
       </c>
       <c r="D871" t="n">
-        <v>10441</v>
+        <v>10419</v>
       </c>
       <c r="E871" t="n">
-        <v>1003</v>
+        <v>1002</v>
       </c>
       <c r="F871" t="n">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="G871" t="n">
-        <v>2824</v>
+        <v>2722</v>
       </c>
       <c r="H871" t="n">
-        <v>19580</v>
+        <v>19547</v>
       </c>
       <c r="I871" t="n">
         <v>24</v>
       </c>
     </row>
     <row r="872">
-      <c r="A872" s="1" t="n">
+      <c r="A872" s="2" t="n">
         <v>46164</v>
       </c>
       <c r="B872" t="n">
-        <v>23222</v>
+        <v>23221</v>
       </c>
       <c r="C872" t="n">
         <v>8983</v>
@@ -25717,7 +25729,7 @@
         <v>295</v>
       </c>
       <c r="G872" t="n">
-        <v>2584</v>
+        <v>2583</v>
       </c>
       <c r="H872" t="n">
         <v>19634</v>
@@ -25727,11 +25739,11 @@
       </c>
     </row>
     <row r="873">
-      <c r="A873" s="1" t="n">
+      <c r="A873" s="2" t="n">
         <v>46165</v>
       </c>
       <c r="B873" t="n">
-        <v>16511</v>
+        <v>16510</v>
       </c>
       <c r="C873" t="n">
         <v>7479</v>
@@ -25746,21 +25758,21 @@
         <v>2</v>
       </c>
       <c r="G873" t="n">
-        <v>910</v>
+        <v>909</v>
       </c>
       <c r="H873" t="n">
         <v>15375</v>
       </c>
       <c r="I873" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="874">
-      <c r="A874" s="1" t="n">
+      <c r="A874" s="2" t="n">
         <v>46166</v>
       </c>
       <c r="B874" t="n">
-        <v>13110</v>
+        <v>13109</v>
       </c>
       <c r="C874" t="n">
         <v>6828</v>
@@ -25775,21 +25787,21 @@
         <v>1</v>
       </c>
       <c r="G874" t="n">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="H874" t="n">
         <v>12983</v>
       </c>
       <c r="I874" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="875">
-      <c r="A875" s="1" t="n">
+      <c r="A875" s="2" t="n">
         <v>46167</v>
       </c>
       <c r="B875" t="n">
-        <v>14816</v>
+        <v>14815</v>
       </c>
       <c r="C875" t="n">
         <v>7463</v>
@@ -25804,21 +25816,21 @@
         <v>1</v>
       </c>
       <c r="G875" t="n">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="H875" t="n">
         <v>14418</v>
       </c>
       <c r="I875" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="876">
-      <c r="A876" s="1" t="n">
+      <c r="A876" s="2" t="n">
         <v>46168</v>
       </c>
       <c r="B876" t="n">
-        <v>23965</v>
+        <v>23917</v>
       </c>
       <c r="C876" t="n">
         <v>8115</v>
@@ -25827,18 +25839,627 @@
         <v>7818</v>
       </c>
       <c r="E876" t="n">
-        <v>1556</v>
+        <v>1517</v>
       </c>
       <c r="F876" t="n">
         <v>1272</v>
       </c>
       <c r="G876" t="n">
-        <v>5204</v>
+        <v>5195</v>
       </c>
       <c r="H876" t="n">
         <v>15933</v>
       </c>
       <c r="I876" t="n">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="877">
+      <c r="A877" s="2" t="n">
+        <v>46169</v>
+      </c>
+      <c r="B877" t="n">
+        <v>22326</v>
+      </c>
+      <c r="C877" t="n">
+        <v>7348</v>
+      </c>
+      <c r="D877" t="n">
+        <v>9052</v>
+      </c>
+      <c r="E877" t="n">
+        <v>967</v>
+      </c>
+      <c r="F877" t="n">
+        <v>333</v>
+      </c>
+      <c r="G877" t="n">
+        <v>4626</v>
+      </c>
+      <c r="H877" t="n">
+        <v>16400</v>
+      </c>
+      <c r="I877" t="n">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="878">
+      <c r="A878" s="2" t="n">
+        <v>46170</v>
+      </c>
+      <c r="B878" t="n">
+        <v>22535</v>
+      </c>
+      <c r="C878" t="n">
+        <v>8594</v>
+      </c>
+      <c r="D878" t="n">
+        <v>10048</v>
+      </c>
+      <c r="E878" t="n">
+        <v>953</v>
+      </c>
+      <c r="F878" t="n">
+        <v>4</v>
+      </c>
+      <c r="G878" t="n">
+        <v>2936</v>
+      </c>
+      <c r="H878" t="n">
+        <v>18642</v>
+      </c>
+      <c r="I878" t="n">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="879">
+      <c r="A879" s="2" t="n">
+        <v>46171</v>
+      </c>
+      <c r="B879" t="n">
+        <v>23480</v>
+      </c>
+      <c r="C879" t="n">
+        <v>8806</v>
+      </c>
+      <c r="D879" t="n">
+        <v>10865</v>
+      </c>
+      <c r="E879" t="n">
+        <v>875</v>
+      </c>
+      <c r="F879" t="n">
+        <v>3</v>
+      </c>
+      <c r="G879" t="n">
+        <v>2931</v>
+      </c>
+      <c r="H879" t="n">
+        <v>19671</v>
+      </c>
+      <c r="I879" t="n">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="880">
+      <c r="A880" s="2" t="n">
+        <v>46172</v>
+      </c>
+      <c r="B880" t="n">
+        <v>15391</v>
+      </c>
+      <c r="C880" t="n">
+        <v>6940</v>
+      </c>
+      <c r="D880" t="n">
+        <v>7308</v>
+      </c>
+      <c r="E880" t="n">
+        <v>237</v>
+      </c>
+      <c r="F880" t="n">
+        <v>1</v>
+      </c>
+      <c r="G880" t="n">
+        <v>905</v>
+      </c>
+      <c r="H880" t="n">
+        <v>14248</v>
+      </c>
+      <c r="I880" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="881">
+      <c r="A881" s="2" t="n">
+        <v>46173</v>
+      </c>
+      <c r="B881" t="n">
+        <v>12138</v>
+      </c>
+      <c r="C881" t="n">
+        <v>6879</v>
+      </c>
+      <c r="D881" t="n">
+        <v>4971</v>
+      </c>
+      <c r="E881" t="n">
+        <v>154</v>
+      </c>
+      <c r="F881" t="n">
+        <v>1</v>
+      </c>
+      <c r="G881" t="n">
+        <v>133</v>
+      </c>
+      <c r="H881" t="n">
+        <v>11850</v>
+      </c>
+      <c r="I881" t="n">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="882">
+      <c r="A882" s="2" t="n">
+        <v>46174</v>
+      </c>
+      <c r="B882" t="n">
+        <v>22473</v>
+      </c>
+      <c r="C882" t="n">
+        <v>9655</v>
+      </c>
+      <c r="D882" t="n">
+        <v>7910</v>
+      </c>
+      <c r="E882" t="n">
+        <v>1395</v>
+      </c>
+      <c r="F882" t="n">
+        <v>1</v>
+      </c>
+      <c r="G882" t="n">
+        <v>3512</v>
+      </c>
+      <c r="H882" t="n">
+        <v>17565</v>
+      </c>
+      <c r="I882" t="n">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="883">
+      <c r="A883" s="2" t="n">
+        <v>46175</v>
+      </c>
+      <c r="B883" t="n">
+        <v>26730</v>
+      </c>
+      <c r="C883" t="n">
+        <v>9023</v>
+      </c>
+      <c r="D883" t="n">
+        <v>13676</v>
+      </c>
+      <c r="E883" t="n">
+        <v>824</v>
+      </c>
+      <c r="F883" t="n">
+        <v>1</v>
+      </c>
+      <c r="G883" t="n">
+        <v>3206</v>
+      </c>
+      <c r="H883" t="n">
+        <v>22699</v>
+      </c>
+      <c r="I883" t="n">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="884">
+      <c r="A884" s="2" t="n">
+        <v>46176</v>
+      </c>
+      <c r="B884" t="n">
+        <v>23589</v>
+      </c>
+      <c r="C884" t="n">
+        <v>13593</v>
+      </c>
+      <c r="D884" t="n">
+        <v>9378</v>
+      </c>
+      <c r="E884" t="n">
+        <v>411</v>
+      </c>
+      <c r="F884" t="n">
+        <v>1</v>
+      </c>
+      <c r="G884" t="n">
+        <v>206</v>
+      </c>
+      <c r="H884" t="n">
+        <v>22971</v>
+      </c>
+      <c r="I884" t="n">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="885">
+      <c r="A885" s="2" t="n">
+        <v>46177</v>
+      </c>
+      <c r="B885" t="n">
+        <v>22952</v>
+      </c>
+      <c r="C885" t="n">
+        <v>9485</v>
+      </c>
+      <c r="D885" t="n">
+        <v>8649</v>
+      </c>
+      <c r="E885" t="n">
+        <v>1362</v>
+      </c>
+      <c r="F885" t="n">
+        <v>1</v>
+      </c>
+      <c r="G885" t="n">
+        <v>3455</v>
+      </c>
+      <c r="H885" t="n">
+        <v>18134</v>
+      </c>
+      <c r="I885" t="n">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="886">
+      <c r="A886" s="2" t="n">
+        <v>46178</v>
+      </c>
+      <c r="B886" t="n">
+        <v>21336</v>
+      </c>
+      <c r="C886" t="n">
+        <v>9277</v>
+      </c>
+      <c r="D886" t="n">
+        <v>8475</v>
+      </c>
+      <c r="E886" t="n">
+        <v>791</v>
+      </c>
+      <c r="F886" t="n">
+        <v>1</v>
+      </c>
+      <c r="G886" t="n">
+        <v>2792</v>
+      </c>
+      <c r="H886" t="n">
+        <v>17752</v>
+      </c>
+      <c r="I886" t="n">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="887">
+      <c r="A887" s="2" t="n">
+        <v>46179</v>
+      </c>
+      <c r="B887" t="n">
+        <v>12475</v>
+      </c>
+      <c r="C887" t="n">
+        <v>6851</v>
+      </c>
+      <c r="D887" t="n">
+        <v>5390</v>
+      </c>
+      <c r="E887" t="n">
+        <v>67</v>
+      </c>
+      <c r="F887" t="n">
+        <v>1</v>
+      </c>
+      <c r="G887" t="n">
+        <v>166</v>
+      </c>
+      <c r="H887" t="n">
+        <v>12241</v>
+      </c>
+      <c r="I887" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="888">
+      <c r="A888" s="2" t="n">
+        <v>46180</v>
+      </c>
+      <c r="B888" t="n">
+        <v>11282</v>
+      </c>
+      <c r="C888" t="n">
+        <v>6041</v>
+      </c>
+      <c r="D888" t="n">
+        <v>4946</v>
+      </c>
+      <c r="E888" t="n">
+        <v>166</v>
+      </c>
+      <c r="F888" t="n">
+        <v>1</v>
+      </c>
+      <c r="G888" t="n">
+        <v>128</v>
+      </c>
+      <c r="H888" t="n">
+        <v>10987</v>
+      </c>
+      <c r="I888" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="889">
+      <c r="A889" s="2" t="n">
+        <v>46181</v>
+      </c>
+      <c r="B889" t="n">
+        <v>17834</v>
+      </c>
+      <c r="C889" t="n">
+        <v>6691</v>
+      </c>
+      <c r="D889" t="n">
+        <v>6142</v>
+      </c>
+      <c r="E889" t="n">
+        <v>1348</v>
+      </c>
+      <c r="F889" t="n">
+        <v>1</v>
+      </c>
+      <c r="G889" t="n">
+        <v>3652</v>
+      </c>
+      <c r="H889" t="n">
+        <v>12833</v>
+      </c>
+      <c r="I889" t="n">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="890">
+      <c r="A890" s="2" t="n">
+        <v>46182</v>
+      </c>
+      <c r="B890" t="n">
+        <v>17758</v>
+      </c>
+      <c r="C890" t="n">
+        <v>7484</v>
+      </c>
+      <c r="D890" t="n">
+        <v>6782</v>
+      </c>
+      <c r="E890" t="n">
+        <v>976</v>
+      </c>
+      <c r="F890" t="n">
+        <v>1</v>
+      </c>
+      <c r="G890" t="n">
+        <v>2515</v>
+      </c>
+      <c r="H890" t="n">
+        <v>14266</v>
+      </c>
+      <c r="I890" t="n">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="891">
+      <c r="A891" s="2" t="n">
+        <v>46183</v>
+      </c>
+      <c r="B891" t="n">
+        <v>20250</v>
+      </c>
+      <c r="C891" t="n">
+        <v>5744</v>
+      </c>
+      <c r="D891" t="n">
+        <v>11261</v>
+      </c>
+      <c r="E891" t="n">
+        <v>850</v>
+      </c>
+      <c r="F891" t="n">
+        <v>1</v>
+      </c>
+      <c r="G891" t="n">
+        <v>2394</v>
+      </c>
+      <c r="H891" t="n">
+        <v>17005</v>
+      </c>
+      <c r="I891" t="n">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="892">
+      <c r="A892" s="2" t="n">
+        <v>46184</v>
+      </c>
+      <c r="B892" t="n">
+        <v>24476</v>
+      </c>
+      <c r="C892" t="n">
+        <v>10974</v>
+      </c>
+      <c r="D892" t="n">
+        <v>9748</v>
+      </c>
+      <c r="E892" t="n">
+        <v>1052</v>
+      </c>
+      <c r="F892" t="n">
+        <v>1</v>
+      </c>
+      <c r="G892" t="n">
+        <v>2701</v>
+      </c>
+      <c r="H892" t="n">
+        <v>20722</v>
+      </c>
+      <c r="I892" t="n">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="893">
+      <c r="A893" s="2" t="n">
+        <v>46185</v>
+      </c>
+      <c r="B893" t="n">
+        <v>21939</v>
+      </c>
+      <c r="C893" t="n">
+        <v>9859</v>
+      </c>
+      <c r="D893" t="n">
+        <v>8875</v>
+      </c>
+      <c r="E893" t="n">
+        <v>879</v>
+      </c>
+      <c r="F893" t="n">
+        <v>1</v>
+      </c>
+      <c r="G893" t="n">
+        <v>2325</v>
+      </c>
+      <c r="H893" t="n">
+        <v>18734</v>
+      </c>
+      <c r="I893" t="n">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="894">
+      <c r="A894" s="2" t="n">
+        <v>46186</v>
+      </c>
+      <c r="B894" t="n">
+        <v>12855</v>
+      </c>
+      <c r="C894" t="n">
+        <v>6496</v>
+      </c>
+      <c r="D894" t="n">
+        <v>5152</v>
+      </c>
+      <c r="E894" t="n">
+        <v>255</v>
+      </c>
+      <c r="F894" t="n">
+        <v>1</v>
+      </c>
+      <c r="G894" t="n">
+        <v>951</v>
+      </c>
+      <c r="H894" t="n">
+        <v>11648</v>
+      </c>
+      <c r="I894" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="895">
+      <c r="A895" s="2" t="n">
+        <v>46187</v>
+      </c>
+      <c r="B895" t="n">
+        <v>11303</v>
+      </c>
+      <c r="C895" t="n">
+        <v>6145</v>
+      </c>
+      <c r="D895" t="n">
+        <v>4872</v>
+      </c>
+      <c r="E895" t="n">
+        <v>154</v>
+      </c>
+      <c r="F895" t="n">
+        <v>1</v>
+      </c>
+      <c r="G895" t="n">
+        <v>131</v>
+      </c>
+      <c r="H895" t="n">
+        <v>11017</v>
+      </c>
+      <c r="I895" t="n">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="896">
+      <c r="A896" s="2" t="n">
+        <v>46188</v>
+      </c>
+      <c r="B896" t="n">
+        <v>22438</v>
+      </c>
+      <c r="C896" t="n">
+        <v>8702</v>
+      </c>
+      <c r="D896" t="n">
+        <v>7992</v>
+      </c>
+      <c r="E896" t="n">
+        <v>1334</v>
+      </c>
+      <c r="F896" t="n">
+        <v>1</v>
+      </c>
+      <c r="G896" t="n">
+        <v>4409</v>
+      </c>
+      <c r="H896" t="n">
+        <v>16694</v>
+      </c>
+      <c r="I896" t="n">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="897">
+      <c r="A897" s="2" t="n">
+        <v>46189</v>
+      </c>
+      <c r="B897" t="n">
+        <v>29203</v>
+      </c>
+      <c r="C897" t="n">
+        <v>10693</v>
+      </c>
+      <c r="D897" t="n">
+        <v>14816</v>
+      </c>
+      <c r="E897" t="n">
+        <v>946</v>
+      </c>
+      <c r="F897" t="n">
+        <v>1</v>
+      </c>
+      <c r="G897" t="n">
+        <v>2747</v>
+      </c>
+      <c r="H897" t="n">
+        <v>25509</v>
+      </c>
+      <c r="I897" t="n">
         <v>23</v>
       </c>
     </row>
